--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -1,32 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\practica 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\Practica 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E94603B-99B4-46E3-8C2B-96DA00A00A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F36DD1-3C4E-4A38-B51C-8EE7D69021F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FF8BD292-BC82-4648-93FB-5EF5760864FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF8BD292-BC82-4648-93FB-5EF5760864FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Contribuyente" sheetId="1" r:id="rId1"/>
     <sheet name="Ordenanza" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="689">
   <si>
     <t>Nombre</t>
   </si>
@@ -541,6 +552,9 @@
     <t>Chen</t>
   </si>
   <si>
+    <t>71393354C</t>
+  </si>
+  <si>
     <t>09611066X</t>
   </si>
   <si>
@@ -559,12 +573,18 @@
     <t>09689676Y</t>
   </si>
   <si>
+    <t>09570285P</t>
+  </si>
+  <si>
     <t>09570262P</t>
   </si>
   <si>
     <t>09548827D</t>
   </si>
   <si>
+    <t>09548486J</t>
+  </si>
+  <si>
     <t>24304263W</t>
   </si>
   <si>
@@ -580,6 +600,9 @@
     <t>71393396Q</t>
   </si>
   <si>
+    <t>71406027C</t>
+  </si>
+  <si>
     <t>09548451R</t>
   </si>
   <si>
@@ -595,6 +618,9 @@
     <t>09548317M</t>
   </si>
   <si>
+    <t>12649208J</t>
+  </si>
+  <si>
     <t>09758365V</t>
   </si>
   <si>
@@ -610,6 +636,12 @@
     <t>09548501M</t>
   </si>
   <si>
+    <t>09548290R</t>
+  </si>
+  <si>
+    <t>09626048L</t>
+  </si>
+  <si>
     <t>24571671N</t>
   </si>
   <si>
@@ -637,6 +669,9 @@
     <t>09545570H</t>
   </si>
   <si>
+    <t>71393411P</t>
+  </si>
+  <si>
     <t>71393352H</t>
   </si>
   <si>
@@ -646,6 +681,9 @@
     <t>71878948S</t>
   </si>
   <si>
+    <t>X3387K</t>
+  </si>
+  <si>
     <t>09634700T</t>
   </si>
   <si>
@@ -733,6 +771,9 @@
     <t>FechaBaja</t>
   </si>
   <si>
+    <t>24561937521546497521</t>
+  </si>
+  <si>
     <t>36520125638451012515</t>
   </si>
   <si>
@@ -745,6 +786,9 @@
     <t>20960043043554600000</t>
   </si>
   <si>
+    <t>23215465315456411515</t>
+  </si>
+  <si>
     <t>20910936583000000000</t>
   </si>
   <si>
@@ -757,6 +801,9 @@
     <t>34698752714600549403</t>
   </si>
   <si>
+    <t>66649444162310000255</t>
+  </si>
+  <si>
     <t>21508149175421346497</t>
   </si>
   <si>
@@ -796,6 +843,9 @@
     <t>36585214290025478551</t>
   </si>
   <si>
+    <t>31624561042546920007</t>
+  </si>
+  <si>
     <t>36154231712500312566</t>
   </si>
   <si>
@@ -847,6 +897,24 @@
     <t>52198484752100515144</t>
   </si>
   <si>
+    <t>32541112811220000588</t>
+  </si>
+  <si>
+    <t>26221011628048788896</t>
+  </si>
+  <si>
+    <t>12548521518742146695</t>
+  </si>
+  <si>
+    <t>01826530120201560000</t>
+  </si>
+  <si>
+    <t>21651651812511133551</t>
+  </si>
+  <si>
+    <t>51651487910005118185</t>
+  </si>
+  <si>
     <t>DK</t>
   </si>
   <si>
@@ -1282,9 +1350,24 @@
     <t>20960043052159000011</t>
   </si>
   <si>
+    <t>25415</t>
+  </si>
+  <si>
+    <t>x71563258p</t>
+  </si>
+  <si>
     <t>1234567890</t>
   </si>
   <si>
+    <t>10150</t>
+  </si>
+  <si>
+    <t>a56783</t>
+  </si>
+  <si>
+    <t>07815963256</t>
+  </si>
+  <si>
     <t>kg incluidos</t>
   </si>
   <si>
@@ -1339,6 +1422,15 @@
     <t>kg generados</t>
   </si>
   <si>
+    <t>12345678Z</t>
+  </si>
+  <si>
+    <t>71393419Q</t>
+  </si>
+  <si>
+    <t>09548283V</t>
+  </si>
+  <si>
     <t>71425232C</t>
   </si>
   <si>
@@ -1348,6 +1440,9 @@
     <t>15823658A</t>
   </si>
   <si>
+    <t>96523658H</t>
+  </si>
+  <si>
     <t>82145896Q</t>
   </si>
   <si>
@@ -1360,6 +1455,9 @@
     <t>26551681807651415636</t>
   </si>
   <si>
+    <t>62541122421110105611</t>
+  </si>
+  <si>
     <t>31645124443461205100</t>
   </si>
   <si>
@@ -1408,12 +1506,45 @@
     <t>20012541150023365296</t>
   </si>
   <si>
+    <t>31245164156597845172</t>
+  </si>
+  <si>
+    <t>31215643855060225039</t>
+  </si>
+  <si>
     <t>65645150865168448846</t>
   </si>
   <si>
     <t>51556584221251000242</t>
   </si>
   <si>
+    <t>55065688761051056112</t>
+  </si>
+  <si>
+    <t>36250012804785523317</t>
+  </si>
+  <si>
+    <t>22515651915640081019</t>
+  </si>
+  <si>
+    <t>2158497690215465548</t>
+  </si>
+  <si>
+    <t>0075018431070251000</t>
+  </si>
+  <si>
+    <t>2096004304309620001</t>
+  </si>
+  <si>
+    <t>6457894674005151640</t>
+  </si>
+  <si>
+    <t>A4587946032003165464</t>
+  </si>
+  <si>
+    <t>E6552211148855332200</t>
+  </si>
+  <si>
     <t>32154697195423121012</t>
   </si>
   <si>
@@ -1450,162 +1581,51 @@
     <t>85550564726165145618</t>
   </si>
   <si>
-    <t>12 13 14 25</t>
-  </si>
-  <si>
-    <t>16 17 18 19</t>
-  </si>
-  <si>
-    <t>23432</t>
-  </si>
-  <si>
-    <t>345344</t>
-  </si>
-  <si>
-    <t>43532</t>
-  </si>
-  <si>
-    <t>445454</t>
-  </si>
-  <si>
-    <t>54332</t>
-  </si>
-  <si>
-    <t>234322</t>
-  </si>
-  <si>
-    <t>74635623</t>
-  </si>
-  <si>
-    <t>x8465783</t>
-  </si>
-  <si>
-    <t>83647564</t>
-  </si>
-  <si>
-    <t>83948128</t>
-  </si>
-  <si>
-    <t>92736981</t>
-  </si>
-  <si>
-    <t>a8276465</t>
-  </si>
-  <si>
-    <t>J7364567B</t>
-  </si>
-  <si>
-    <t>25147854</t>
-  </si>
-  <si>
-    <t>12345678</t>
-  </si>
-  <si>
-    <t>25632</t>
-  </si>
-  <si>
-    <t>2563254178</t>
-  </si>
-  <si>
-    <t>12345679</t>
-  </si>
-  <si>
-    <t>12345670</t>
-  </si>
-  <si>
-    <t>87635467891625345671</t>
-  </si>
-  <si>
-    <t>84729478104857627845</t>
-  </si>
-  <si>
-    <t>87457619027384957654</t>
-  </si>
-  <si>
-    <t>87457619024384957654</t>
-  </si>
-  <si>
-    <t>87457619027384957657</t>
-  </si>
-  <si>
-    <t>87457619027384957658</t>
-  </si>
-  <si>
-    <t>87457619027384957659</t>
-  </si>
-  <si>
-    <t>87457619027384957651</t>
-  </si>
-  <si>
-    <t>87457619027384957653</t>
-  </si>
-  <si>
-    <t>87457619027384957617</t>
-  </si>
-  <si>
-    <t>87457619027384957619</t>
-  </si>
-  <si>
-    <t>87457619027384957621</t>
-  </si>
-  <si>
-    <t>21584976902154655485</t>
-  </si>
-  <si>
-    <t>20960043043096200013</t>
-  </si>
-  <si>
-    <t>00750184310702510003</t>
-  </si>
-  <si>
-    <t>64578946740051516403</t>
-  </si>
-  <si>
-    <t>75647586987564758698</t>
-  </si>
-  <si>
-    <t>245619375215464975</t>
-  </si>
-  <si>
-    <t>2321546531545641151567</t>
-  </si>
-  <si>
-    <t>E6664944416231000025</t>
-  </si>
-  <si>
-    <t>3162456104254692000A</t>
-  </si>
-  <si>
     <t>31645124453461205100</t>
   </si>
   <si>
+    <t>DK8231645124453461205100</t>
+  </si>
+  <si>
+    <t>jmd00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>65614874115615445600</t>
   </si>
   <si>
+    <t>ES4865614874115615445600</t>
+  </si>
+  <si>
+    <t>rfm00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>32569523086220165100</t>
   </si>
   <si>
+    <t>DE7424561937521546497521</t>
+  </si>
+  <si>
+    <t>aln00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>MC6436520125638451012515</t>
   </si>
   <si>
     <t>rgo00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>21584976912154655485</t>
-  </si>
-  <si>
-    <t>ES9621584976912154655485</t>
-  </si>
-  <si>
-    <t>sdo00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>GR9420125003305201112544</t>
   </si>
   <si>
     <t>vdo00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>ES2821651484690980008984</t>
+  </si>
+  <si>
+    <t>vbp00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>FI5620960043043554600000</t>
   </si>
   <si>
@@ -1621,58 +1641,13 @@
     <t>acp00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>00750184350702510003</t>
-  </si>
-  <si>
-    <t>74635623W</t>
-  </si>
-  <si>
-    <t>SM1325894363415485700777</t>
-  </si>
-  <si>
-    <t>lbr00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>X8465783N</t>
-  </si>
-  <si>
-    <t>ES0396431245188150005111</t>
-  </si>
-  <si>
-    <t>sbr00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>83647564Z</t>
-  </si>
-  <si>
     <t>25030000194574745400</t>
   </si>
   <si>
-    <t>AT7125030000194574745400</t>
-  </si>
-  <si>
-    <t>agr00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>83948128Z</t>
-  </si>
-  <si>
-    <t>IT2115953684881254695211</t>
-  </si>
-  <si>
-    <t>dgr00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>92736981S</t>
-  </si>
-  <si>
-    <t>20960043033096200013</t>
-  </si>
-  <si>
-    <t>ES6520960043033096200013</t>
-  </si>
-  <si>
-    <t>pgs00@tasabasura2026.com</t>
+    <t>DK2500750184330702510011</t>
+  </si>
+  <si>
+    <t>cis00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES7423455254983263234411</t>
@@ -1714,16 +1689,16 @@
     <t>cgm00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>64578946720051516403</t>
-  </si>
-  <si>
     <t>ES4534698752714600549403</t>
   </si>
   <si>
     <t>csn00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>25147854E</t>
+    <t>ES2766649444162310000255</t>
+  </si>
+  <si>
+    <t>alo00@tasabasura2026.com</t>
   </si>
   <si>
     <t>23185484415641685908</t>
@@ -1747,9 +1722,6 @@
     <t>ccp00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>12345678Z</t>
-  </si>
-  <si>
     <t>ES7225187786311225455548</t>
   </si>
   <si>
@@ -1768,21 +1740,18 @@
     <t>dlr00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>75647586157564758698</t>
-  </si>
-  <si>
-    <t>FI6775647586157564758698</t>
-  </si>
-  <si>
-    <t>har00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>ES5020960043073071400000</t>
   </si>
   <si>
     <t>spr00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>ES8220960043042158800000</t>
+  </si>
+  <si>
+    <t>gpr00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>ES7521654587985156484454</t>
   </si>
   <si>
@@ -1795,12 +1764,6 @@
     <t>bfs00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES4675647586157564758698</t>
-  </si>
-  <si>
-    <t>dfg00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>GB9720910936583000000000</t>
   </si>
   <si>
@@ -1813,10 +1776,16 @@
     <t>mlg00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>DE7822631245526916432102</t>
+  </si>
+  <si>
+    <t>iag00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>ES2120960043043075700000</t>
   </si>
   <si>
-    <t>iag00@tasabasura2026.com</t>
+    <t>iag01@tasabasura2026.com</t>
   </si>
   <si>
     <t>25635478301002541233</t>
@@ -1849,6 +1818,18 @@
     <t>20960043073000100018</t>
   </si>
   <si>
+    <t>ES2520960043073000100018</t>
+  </si>
+  <si>
+    <t>apm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>GB0836585214290025478551</t>
+  </si>
+  <si>
+    <t>gmm02@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>12548523445214585218</t>
   </si>
   <si>
@@ -1858,6 +1839,12 @@
     <t>alm00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>ES6931624561042546920007</t>
+  </si>
+  <si>
+    <t>ldm00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>ES1436154231712500312566</t>
   </si>
   <si>
@@ -1891,12 +1878,6 @@
     <t>dgg00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES0725165151118666365191</t>
-  </si>
-  <si>
-    <t>rog00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>20960043023000100021</t>
   </si>
   <si>
@@ -1906,6 +1887,12 @@
     <t>sog00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>PT3536952365020014425254</t>
+  </si>
+  <si>
+    <t>vvg00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>65168874681561561522</t>
   </si>
   <si>
@@ -1930,27 +1917,9 @@
     <t>cbg00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>12345670Y</t>
-  </si>
-  <si>
-    <t>LU0932628484504115151115</t>
-  </si>
-  <si>
-    <t>msh00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>12345679S</t>
-  </si>
-  <si>
     <t>20960056143231500032</t>
   </si>
   <si>
-    <t>ES6620960056143231500032</t>
-  </si>
-  <si>
-    <t>fdl00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>63516541858944000993</t>
   </si>
   <si>
@@ -2014,10 +1983,10 @@
     <t>ngc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87635467511625345671</t>
-  </si>
-  <si>
-    <t>ES2987635467511625345671</t>
+    <t>31245164126597845172</t>
+  </si>
+  <si>
+    <t>ES3331245164126597845172</t>
   </si>
   <si>
     <t>mlc00@tasabasura2026.com</t>
@@ -2038,10 +2007,10 @@
     <t>cfc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>84729478014857627845</t>
-  </si>
-  <si>
-    <t>ES7884729478014857627845</t>
+    <t>31215643895060225039</t>
+  </si>
+  <si>
+    <t>ES9831215643895060225039</t>
   </si>
   <si>
     <t>cgc00@tasabasura2026.com</t>
@@ -2083,76 +2052,55 @@
     <t>IE4751556584261251000242</t>
   </si>
   <si>
-    <t>gmm02@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>87457619137384957654</t>
-  </si>
-  <si>
-    <t>87457619164384957654</t>
-  </si>
-  <si>
-    <t>LT1687457619164384957654</t>
+    <t>gmm03@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>LT9362541122421110105611</t>
   </si>
   <si>
     <t>dmc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87457619177384957657</t>
-  </si>
-  <si>
-    <t>ES9587457619177384957657</t>
+    <t>55065688711051056112</t>
+  </si>
+  <si>
+    <t>ES9255065688711051056112</t>
   </si>
   <si>
     <t>ebc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87457619117384957658</t>
-  </si>
-  <si>
-    <t>87457619167384957659</t>
-  </si>
-  <si>
-    <t>ES0687457619167384957659</t>
+    <t>ES9712548521518742146695</t>
   </si>
   <si>
     <t>msc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87457619117384957651</t>
-  </si>
-  <si>
-    <t>ES4787457619117384957651</t>
+    <t>ES9001826530120201560000</t>
   </si>
   <si>
     <t>mdc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87457619197384957653</t>
-  </si>
-  <si>
-    <t>ES7987457619197384957653</t>
+    <t>ES9021651651812511133551</t>
   </si>
   <si>
     <t>mfc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87457619187384957617</t>
-  </si>
-  <si>
-    <t>ES4687457619187384957617</t>
+    <t>ES6851651487910005118185</t>
   </si>
   <si>
     <t>cdd00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>87457619177384957619</t>
-  </si>
-  <si>
-    <t>87457619187384957621</t>
-  </si>
-  <si>
-    <t>AT6887457619187384957621</t>
+    <t>36250012834785523317</t>
+  </si>
+  <si>
+    <t>22515651985640081019</t>
+  </si>
+  <si>
+    <t>AT5422515651985640081019</t>
   </si>
   <si>
     <t>hpd00@tasabasura2026.com</t>
@@ -2234,9 +2182,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2274,7 +2222,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2380,7 +2328,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2522,7 +2470,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2530,7 +2478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C6ACB8-7F34-425E-9257-91AD8B97F35F}">
-  <dimension ref="A1:R152"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.140625"/>
@@ -2546,7 +2494,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>5</v>
@@ -2579,30 +2527,30 @@
         <v>10</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>93</v>
@@ -2611,13 +2559,19 @@
         <v>128</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>515</v>
+      </c>
+      <c r="J2" t="s" s="0">
         <v>516</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L2" s="0">
         <v>0</v>
@@ -2628,22 +2582,19 @@
       <c r="N2" s="7">
         <v>45294</v>
       </c>
-      <c r="O2" s="7">
-        <v>45717</v>
-      </c>
       <c r="P2" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>12</v>
@@ -2655,13 +2606,19 @@
         <v>133</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>517</v>
       </c>
+      <c r="I3" t="s" s="0">
+        <v>518</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>519</v>
+      </c>
       <c r="K3" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -2672,20 +2629,19 @@
       <c r="N3" s="7">
         <v>38267</v>
       </c>
-      <c r="O3" s="7"/>
       <c r="P3" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>13</v>
@@ -2697,13 +2653,13 @@
         <v>134</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L4" s="0">
         <v>50</v>
@@ -2714,22 +2670,19 @@
       <c r="N4" s="7">
         <v>39682</v>
       </c>
-      <c r="O4" s="7">
-        <v>45719</v>
-      </c>
       <c r="P4" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>13</v>
@@ -2741,13 +2694,19 @@
         <v>135</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>512</v>
+        <v>244</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>521</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>522</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="L5" s="0">
         <v>0</v>
@@ -2758,22 +2717,19 @@
       <c r="N5" s="7">
         <v>38765</v>
       </c>
-      <c r="O5" s="7">
-        <v>45720</v>
-      </c>
       <c r="P5" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>14</v>
@@ -2785,19 +2741,19 @@
         <v>136</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L6" s="0">
         <v>25</v>
@@ -2808,22 +2764,19 @@
       <c r="N6" s="7">
         <v>38646</v>
       </c>
-      <c r="O6" s="7">
-        <v>45721</v>
-      </c>
       <c r="P6" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>15</v>
@@ -2835,19 +2788,13 @@
         <v>137</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="I7" t="s" s="0">
-        <v>522</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L7" s="0">
         <v>0</v>
@@ -2858,22 +2805,19 @@
       <c r="N7" s="7">
         <v>41039</v>
       </c>
-      <c r="O7" s="7">
-        <v>45722</v>
-      </c>
       <c r="P7" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>16</v>
@@ -2885,19 +2829,19 @@
         <v>118</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L8" s="0">
         <v>25</v>
@@ -2908,22 +2852,19 @@
       <c r="N8" s="7">
         <v>45738</v>
       </c>
-      <c r="O8" s="7">
-        <v>45723</v>
-      </c>
       <c r="P8" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>16</v>
@@ -2935,13 +2876,19 @@
         <v>138</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>528</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L9" s="0">
         <v>0</v>
@@ -2952,22 +2899,19 @@
       <c r="N9" s="7">
         <v>45739</v>
       </c>
-      <c r="O9" s="7">
-        <v>45724</v>
-      </c>
       <c r="P9" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>17</v>
@@ -2979,19 +2923,19 @@
         <v>139</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K10" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L10" s="0">
         <v>0</v>
@@ -3002,22 +2946,19 @@
       <c r="N10" s="7">
         <v>45740</v>
       </c>
-      <c r="O10" s="7">
-        <v>45725</v>
-      </c>
       <c r="P10" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>18</v>
@@ -3029,13 +2970,13 @@
         <v>125</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L11" s="0">
         <v>25</v>
@@ -3046,22 +2987,19 @@
       <c r="N11" s="7">
         <v>45709</v>
       </c>
-      <c r="O11" s="7">
-        <v>45726</v>
-      </c>
       <c r="P11" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>19</v>
@@ -3073,19 +3011,19 @@
         <v>140</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K12" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L12" s="0">
         <v>0</v>
@@ -3096,20 +3034,19 @@
       <c r="N12" s="7">
         <v>45710</v>
       </c>
-      <c r="O12" s="7"/>
       <c r="P12" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>20</v>
@@ -3121,13 +3058,13 @@
         <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>513</v>
+        <v>249</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L13" s="0">
         <v>0</v>
@@ -3138,22 +3075,19 @@
       <c r="N13" s="7">
         <v>45873</v>
       </c>
-      <c r="O13" s="7">
-        <v>45728</v>
-      </c>
       <c r="P13" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>21</v>
@@ -3165,13 +3099,13 @@
         <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>410</v>
+        <v>429</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>531</v>
+        <v>497</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L14" s="0">
         <v>25</v>
@@ -3182,9 +3116,8 @@
       <c r="N14" s="7">
         <v>45976</v>
       </c>
-      <c r="O14" s="7"/>
       <c r="P14" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -3195,13 +3128,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>22</v>
@@ -3213,19 +3146,13 @@
         <v>141</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>532</v>
+        <v>437</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="I16" t="s" s="0">
-        <v>533</v>
-      </c>
-      <c r="J16" t="s" s="0">
-        <v>534</v>
+        <v>431</v>
       </c>
       <c r="K16" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L16" s="0">
         <v>0</v>
@@ -3236,20 +3163,19 @@
       <c r="N16" s="7">
         <v>40637</v>
       </c>
-      <c r="O16" s="7"/>
       <c r="P16" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>23</v>
@@ -3261,19 +3187,13 @@
         <v>141</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>535</v>
+        <v>438</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="I17" t="s" s="0">
-        <v>536</v>
-      </c>
-      <c r="J17" t="s" s="0">
-        <v>537</v>
+        <v>432</v>
       </c>
       <c r="K17" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L17" s="0">
         <v>0</v>
@@ -3284,20 +3204,19 @@
       <c r="N17" s="7">
         <v>45810</v>
       </c>
-      <c r="O17" s="7"/>
       <c r="P17" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>24</v>
@@ -3309,19 +3228,13 @@
         <v>142</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>538</v>
+        <v>439</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="I18" t="s" s="0">
-        <v>540</v>
-      </c>
-      <c r="J18" t="s" s="0">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="K18" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L18" s="0">
         <v>0</v>
@@ -3332,20 +3245,19 @@
       <c r="N18" s="7">
         <v>45939</v>
       </c>
-      <c r="O18" s="7"/>
       <c r="P18" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>25</v>
@@ -3357,19 +3269,13 @@
         <v>142</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>542</v>
+        <v>440</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="I19" t="s" s="0">
-        <v>543</v>
-      </c>
-      <c r="J19" t="s" s="0">
-        <v>544</v>
+        <v>433</v>
       </c>
       <c r="K19" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L19" s="0">
         <v>25</v>
@@ -3380,20 +3286,19 @@
       <c r="N19" s="7">
         <v>45946</v>
       </c>
-      <c r="O19" s="7"/>
       <c r="P19" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>26</v>
@@ -3405,19 +3310,13 @@
         <v>143</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>545</v>
+        <v>441</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="I20" t="s" s="0">
-        <v>547</v>
-      </c>
-      <c r="J20" t="s" s="0">
-        <v>548</v>
+        <v>498</v>
       </c>
       <c r="K20" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L20" s="0">
         <v>0</v>
@@ -3428,20 +3327,19 @@
       <c r="N20" s="7">
         <v>45778</v>
       </c>
-      <c r="O20" s="7"/>
       <c r="P20" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>27</v>
@@ -3453,13 +3351,19 @@
         <v>95</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>487</v>
+        <v>171</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>415</v>
+        <v>434</v>
+      </c>
+      <c r="I21" t="s" s="0">
+        <v>535</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>536</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L21" s="0">
         <v>0</v>
@@ -3470,20 +3374,19 @@
       <c r="N21" s="7">
         <v>45627</v>
       </c>
-      <c r="O21" s="7"/>
       <c r="P21" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>28</v>
@@ -3492,19 +3395,19 @@
         <v>89</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="J22" t="s" s="0">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="K22" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L22" s="0">
         <v>25</v>
@@ -3515,20 +3418,19 @@
       <c r="N22" s="7">
         <v>45628</v>
       </c>
-      <c r="O22" s="7"/>
       <c r="P22" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>29</v>
@@ -3537,19 +3439,19 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="J23" t="s" s="0">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="K23" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L23" s="0">
         <v>0</v>
@@ -3560,20 +3462,19 @@
       <c r="N23" s="7">
         <v>45629</v>
       </c>
-      <c r="O23" s="7"/>
       <c r="P23" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>30</v>
@@ -3582,19 +3483,19 @@
         <v>91</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="K24" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L24" s="0">
         <v>0</v>
@@ -3605,20 +3506,19 @@
       <c r="N24" s="7">
         <v>45630</v>
       </c>
-      <c r="O24" s="7"/>
       <c r="P24" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>31</v>
@@ -3627,19 +3527,19 @@
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="K25" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L25" s="0">
         <v>25</v>
@@ -3650,9 +3550,8 @@
       <c r="N25" s="7">
         <v>45631</v>
       </c>
-      <c r="O25" s="7"/>
       <c r="P25" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -3663,13 +3562,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>32</v>
@@ -3681,19 +3580,19 @@
         <v>132</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>558</v>
+        <v>546</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="K27" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L27" s="0">
         <v>0</v>
@@ -3702,22 +3601,24 @@
         <v>88</v>
       </c>
       <c r="N27" s="7">
-        <v>46023</v>
-      </c>
-      <c r="O27" s="7"/>
+        <v>39525</v>
+      </c>
+      <c r="O27" s="7">
+        <v>45352</v>
+      </c>
       <c r="P27" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>33</v>
@@ -3729,19 +3630,19 @@
         <v>133</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="K28" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L28" s="0">
         <v>25</v>
@@ -3750,22 +3651,24 @@
         <v>101</v>
       </c>
       <c r="N28" s="7">
-        <v>46024</v>
-      </c>
-      <c r="O28" s="7"/>
+        <v>42667</v>
+      </c>
+      <c r="O28" s="7">
+        <v>45353</v>
+      </c>
       <c r="P28" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>34</v>
@@ -3777,13 +3680,13 @@
         <v>134</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>488</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>562</v>
+        <v>499</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L29" s="0">
         <v>0</v>
@@ -3792,22 +3695,24 @@
         <v>10</v>
       </c>
       <c r="N29" s="7">
-        <v>46025</v>
-      </c>
-      <c r="O29" s="7"/>
+        <v>44639</v>
+      </c>
+      <c r="O29" s="7">
+        <v>45354</v>
+      </c>
       <c r="P29" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>35</v>
@@ -3819,19 +3724,19 @@
         <v>135</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="K30" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L30" s="0">
         <v>0</v>
@@ -3840,22 +3745,24 @@
         <v>78</v>
       </c>
       <c r="N30" s="7">
-        <v>46026</v>
-      </c>
-      <c r="O30" s="7"/>
+        <v>37937</v>
+      </c>
+      <c r="O30" s="7">
+        <v>45355</v>
+      </c>
       <c r="P30" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>36</v>
@@ -3867,13 +3774,19 @@
         <v>136</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>514</v>
+        <v>254</v>
+      </c>
+      <c r="I31" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>553</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L31" s="0">
         <v>0</v>
@@ -3882,22 +3795,24 @@
         <v>71</v>
       </c>
       <c r="N31" s="7">
-        <v>46027</v>
-      </c>
-      <c r="O31" s="7"/>
+        <v>43242</v>
+      </c>
+      <c r="O31" s="7">
+        <v>45356</v>
+      </c>
       <c r="P31" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" t="s" s="0">
         <v>306</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="C32" t="s" s="0">
-        <v>287</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>37</v>
@@ -3909,19 +3824,19 @@
         <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>565</v>
+        <v>181</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="J32" t="s" s="0">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="K32" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L32" s="0">
         <v>0</v>
@@ -3930,11 +3845,13 @@
         <v>113</v>
       </c>
       <c r="N32" s="7">
-        <v>46028</v>
-      </c>
-      <c r="O32" s="7"/>
+        <v>39555</v>
+      </c>
+      <c r="O32" s="7">
+        <v>45357</v>
+      </c>
       <c r="P32" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -3960,13 +3877,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>38</v>
@@ -3978,19 +3895,19 @@
         <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="J36" t="s" s="0">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="K36" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L36" s="0">
         <v>25</v>
@@ -4001,20 +3918,22 @@
       <c r="N36" s="7">
         <v>43230</v>
       </c>
-      <c r="O36" s="7"/>
+      <c r="O36" s="7">
+        <v>45361</v>
+      </c>
       <c r="P36" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>39</v>
@@ -4026,19 +3945,19 @@
         <v>140</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="J37" t="s" s="0">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="K37" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L37" s="0">
         <v>0</v>
@@ -4049,20 +3968,22 @@
       <c r="N37" s="7">
         <v>38841</v>
       </c>
-      <c r="O37" s="7"/>
+      <c r="O37" s="7">
+        <v>45362</v>
+      </c>
       <c r="P37" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>40</v>
@@ -4074,19 +3995,19 @@
         <v>109</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>573</v>
+        <v>208</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="J38" t="s" s="0">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="K38" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L38" s="0">
         <v>0</v>
@@ -4097,20 +4018,22 @@
       <c r="N38" s="7">
         <v>44389</v>
       </c>
-      <c r="O38" s="7"/>
+      <c r="O38" s="7">
+        <v>45363</v>
+      </c>
       <c r="P38" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>41</v>
@@ -4122,13 +4045,13 @@
         <v>109</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L39" s="0">
         <v>0</v>
@@ -4139,20 +4062,22 @@
       <c r="N39" s="7">
         <v>45242</v>
       </c>
-      <c r="O39" s="7"/>
+      <c r="O39" s="7">
+        <v>45364</v>
+      </c>
       <c r="P39" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>42</v>
@@ -4164,19 +4089,19 @@
         <v>144</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="J40" t="s" s="0">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="K40" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L40" s="0">
         <v>0</v>
@@ -4187,20 +4112,22 @@
       <c r="N40" s="7">
         <v>41309</v>
       </c>
-      <c r="O40" s="7"/>
+      <c r="O40" s="7">
+        <v>45365</v>
+      </c>
       <c r="P40" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>43</v>
@@ -4212,19 +4139,19 @@
         <v>141</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="J41" t="s" s="0">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="K41" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L41" s="0">
         <v>0</v>
@@ -4235,20 +4162,22 @@
       <c r="N41" s="7">
         <v>45142</v>
       </c>
-      <c r="O41" s="7"/>
+      <c r="O41" s="7">
+        <v>45366</v>
+      </c>
       <c r="P41" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="D42" t="s" s="0">
         <v>44</v>
@@ -4260,19 +4189,13 @@
         <v>141</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="I42" t="s" s="0">
-        <v>581</v>
-      </c>
-      <c r="J42" t="s" s="0">
-        <v>582</v>
+        <v>500</v>
       </c>
       <c r="K42" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L42" s="0">
         <v>0</v>
@@ -4283,20 +4206,22 @@
       <c r="N42" s="7">
         <v>45048</v>
       </c>
-      <c r="O42" s="7"/>
+      <c r="O42" s="7">
+        <v>45367</v>
+      </c>
       <c r="P42" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D43" t="s" s="0">
         <v>45</v>
@@ -4308,19 +4233,19 @@
         <v>142</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="J43" t="s" s="0">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="K43" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L43" s="0">
         <v>0</v>
@@ -4331,20 +4256,22 @@
       <c r="N43" s="7">
         <v>44479</v>
       </c>
-      <c r="O43" s="7"/>
+      <c r="O43" s="7">
+        <v>45368</v>
+      </c>
       <c r="P43" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D44" t="s" s="0">
         <v>37</v>
@@ -4356,13 +4283,19 @@
         <v>142</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>573</v>
+        <v>187</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
+      </c>
+      <c r="I44" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="J44" t="s" s="0">
+        <v>570</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L44" s="0">
         <v>0</v>
@@ -4373,20 +4306,22 @@
       <c r="N44" s="7">
         <v>42624</v>
       </c>
-      <c r="O44" s="7"/>
+      <c r="O44" s="7">
+        <v>45369</v>
+      </c>
       <c r="P44" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D45" t="s" s="0">
         <v>46</v>
@@ -4398,19 +4333,19 @@
         <v>143</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="J45" t="s" s="0">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="K45" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L45" s="0">
         <v>0</v>
@@ -4421,20 +4356,22 @@
       <c r="N45" s="7">
         <v>42708</v>
       </c>
-      <c r="O45" s="7"/>
+      <c r="O45" s="7">
+        <v>45370</v>
+      </c>
       <c r="P45" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D46" t="s" s="0">
         <v>47</v>
@@ -4446,19 +4383,19 @@
         <v>95</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="J46" t="s" s="0">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="K46" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L46" s="0">
         <v>0</v>
@@ -4469,20 +4406,22 @@
       <c r="N46" s="7">
         <v>44180</v>
       </c>
-      <c r="O46" s="7"/>
+      <c r="O46" s="7">
+        <v>45371</v>
+      </c>
       <c r="P46" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D47" t="s" s="0">
         <v>48</v>
@@ -4494,19 +4433,13 @@
         <v>85</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="I47" t="s" s="0">
-        <v>589</v>
-      </c>
-      <c r="J47" t="s" s="0">
-        <v>590</v>
+        <v>501</v>
       </c>
       <c r="K47" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L47" s="0">
         <v>0</v>
@@ -4517,20 +4450,22 @@
       <c r="N47" s="7">
         <v>45047</v>
       </c>
-      <c r="O47" s="7"/>
+      <c r="O47" s="7">
+        <v>45372</v>
+      </c>
       <c r="P47" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="D48" t="s" s="0">
         <v>49</v>
@@ -4542,19 +4477,19 @@
         <v>85</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="J48" t="s" s="0">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="K48" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L48" s="0">
         <v>25</v>
@@ -4565,20 +4500,22 @@
       <c r="N48" s="7">
         <v>42182</v>
       </c>
-      <c r="O48" s="7"/>
+      <c r="O48" s="7">
+        <v>45373</v>
+      </c>
       <c r="P48" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D49" t="s" s="0">
         <v>50</v>
@@ -4590,19 +4527,19 @@
         <v>145</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="J49" t="s" s="0">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="K49" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L49" s="0">
         <v>0</v>
@@ -4611,22 +4548,24 @@
         <v>192</v>
       </c>
       <c r="N49" s="7">
-        <v>46319</v>
-      </c>
-      <c r="O49" s="7"/>
+        <v>43032</v>
+      </c>
+      <c r="O49" s="7">
+        <v>45374</v>
+      </c>
       <c r="P49" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="D50" t="s" s="0">
         <v>51</v>
@@ -4638,13 +4577,19 @@
         <v>146</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>573</v>
+        <v>193</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
+      </c>
+      <c r="I50" t="s" s="0">
+        <v>579</v>
+      </c>
+      <c r="J50" t="s" s="0">
+        <v>580</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L50" s="0">
         <v>0</v>
@@ -4655,20 +4600,22 @@
       <c r="N50" s="7">
         <v>42490</v>
       </c>
-      <c r="O50" s="7"/>
+      <c r="O50" s="7">
+        <v>45375</v>
+      </c>
       <c r="P50" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D51" t="s" s="0">
         <v>51</v>
@@ -4680,19 +4627,19 @@
         <v>87</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="J51" t="s" s="0">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="K51" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L51" s="0">
         <v>25</v>
@@ -4703,20 +4650,22 @@
       <c r="N51" s="7">
         <v>39101</v>
       </c>
-      <c r="O51" s="7"/>
+      <c r="O51" s="7">
+        <v>45376</v>
+      </c>
       <c r="P51" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D52" t="s" s="0">
         <v>11</v>
@@ -4728,19 +4677,19 @@
         <v>87</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="J52" t="s" s="0">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="K52" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L52" s="0">
         <v>0</v>
@@ -4751,20 +4700,22 @@
       <c r="N52" s="7">
         <v>44962</v>
       </c>
-      <c r="O52" s="7"/>
+      <c r="O52" s="7">
+        <v>45377</v>
+      </c>
       <c r="P52" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D53" t="s" s="0">
         <v>12</v>
@@ -4776,19 +4727,19 @@
         <v>147</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>601</v>
+        <v>587</v>
       </c>
       <c r="J53" t="s" s="0">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="K53" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L53" s="0">
         <v>0</v>
@@ -4799,20 +4750,22 @@
       <c r="N53" s="7">
         <v>42148</v>
       </c>
-      <c r="O53" s="7"/>
+      <c r="O53" s="7">
+        <v>45378</v>
+      </c>
       <c r="P53" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="D54" t="s" s="0">
         <v>13</v>
@@ -4824,13 +4777,13 @@
         <v>148</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L54" s="0">
         <v>25</v>
@@ -4841,20 +4794,22 @@
       <c r="N54" s="7">
         <v>43805</v>
       </c>
-      <c r="O54" s="7"/>
+      <c r="O54" s="7">
+        <v>45379</v>
+      </c>
       <c r="P54" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="D55" t="s" s="0">
         <v>13</v>
@@ -4866,19 +4821,19 @@
         <v>149</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="J55" t="s" s="0">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="K55" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L55" s="0">
         <v>0</v>
@@ -4889,9 +4844,11 @@
       <c r="N55" s="7">
         <v>40575</v>
       </c>
-      <c r="O55" s="7"/>
+      <c r="O55" s="7">
+        <v>45380</v>
+      </c>
       <c r="P55" s="1" t="s">
-        <v>405</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -4920,13 +4877,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D60" t="s" s="0">
         <v>17</v>
@@ -4938,13 +4895,19 @@
         <v>150</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>491</v>
+        <v>199</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>606</v>
+        <v>592</v>
+      </c>
+      <c r="I60" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="J60" t="s" s="0">
+        <v>594</v>
       </c>
       <c r="K60" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L60" s="0">
         <v>0</v>
@@ -4953,22 +4916,24 @@
         <v>27</v>
       </c>
       <c r="N60" s="7">
-        <v>46055</v>
-      </c>
-      <c r="O60" s="7"/>
+        <v>38607</v>
+      </c>
+      <c r="O60" s="7">
+        <v>44927</v>
+      </c>
       <c r="P60" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="D61" t="s" s="0">
         <v>52</v>
@@ -4980,13 +4945,19 @@
         <v>93</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>418</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>255</v>
+        <v>267</v>
+      </c>
+      <c r="I61" t="s" s="0">
+        <v>595</v>
+      </c>
+      <c r="J61" t="s" s="0">
+        <v>596</v>
       </c>
       <c r="K61" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L61" s="0">
         <v>0</v>
@@ -4995,22 +4966,24 @@
         <v>167</v>
       </c>
       <c r="N61" s="7">
-        <v>46056</v>
-      </c>
-      <c r="O61" s="7"/>
+        <v>42083</v>
+      </c>
+      <c r="O61" s="7">
+        <v>44928</v>
+      </c>
       <c r="P61" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D62" t="s" s="0">
         <v>19</v>
@@ -5022,19 +4995,19 @@
         <v>107</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="J62" t="s" s="0">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="K62" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L62" s="0">
         <v>25</v>
@@ -5043,22 +5016,24 @@
         <v>82</v>
       </c>
       <c r="N62" s="7">
-        <v>46057</v>
-      </c>
-      <c r="O62" s="7"/>
+        <v>39105</v>
+      </c>
+      <c r="O62" s="7">
+        <v>44929</v>
+      </c>
       <c r="P62" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D63" t="s" s="0">
         <v>20</v>
@@ -5070,13 +5045,19 @@
         <v>151</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>515</v>
+        <v>268</v>
+      </c>
+      <c r="I63" t="s" s="0">
+        <v>600</v>
+      </c>
+      <c r="J63" t="s" s="0">
+        <v>601</v>
       </c>
       <c r="K63" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L63" s="0">
         <v>0</v>
@@ -5085,22 +5066,24 @@
         <v>122</v>
       </c>
       <c r="N63" s="7">
-        <v>46058</v>
-      </c>
-      <c r="O63" s="7"/>
+        <v>41938</v>
+      </c>
+      <c r="O63" s="7">
+        <v>44930</v>
+      </c>
       <c r="P63" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D64" t="s" s="0">
         <v>21</v>
@@ -5109,19 +5092,19 @@
         <v>114</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="J64" t="s" s="0">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="K64" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L64" s="0">
         <v>0</v>
@@ -5130,22 +5113,24 @@
         <v>92</v>
       </c>
       <c r="N64" s="7">
-        <v>46059</v>
-      </c>
-      <c r="O64" s="7"/>
+        <v>43691</v>
+      </c>
+      <c r="O64" s="7">
+        <v>44931</v>
+      </c>
       <c r="P64" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D65" t="s" s="0">
         <v>53</v>
@@ -5154,19 +5139,19 @@
         <v>115</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="J65" t="s" s="0">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="K65" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L65" s="0">
         <v>0</v>
@@ -5175,22 +5160,24 @@
         <v>28</v>
       </c>
       <c r="N65" s="7">
-        <v>46060</v>
-      </c>
-      <c r="O65" s="7"/>
+        <v>42810</v>
+      </c>
+      <c r="O65" s="7">
+        <v>44932</v>
+      </c>
       <c r="P65" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D66" t="s" s="0">
         <v>22</v>
@@ -5199,19 +5186,19 @@
         <v>116</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="J66" t="s" s="0">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="K66" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L66" s="0">
         <v>0</v>
@@ -5220,22 +5207,24 @@
         <v>6</v>
       </c>
       <c r="N66" s="7">
-        <v>46061</v>
-      </c>
-      <c r="O66" s="7"/>
+        <v>45570</v>
+      </c>
+      <c r="O66" s="7">
+        <v>44933</v>
+      </c>
       <c r="P66" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D67" t="s" s="0">
         <v>23</v>
@@ -5247,13 +5236,13 @@
         <v>85</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="K67" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L67" s="0">
         <v>0</v>
@@ -5262,22 +5251,24 @@
         <v>200</v>
       </c>
       <c r="N67" s="7">
-        <v>46062</v>
-      </c>
-      <c r="O67" s="7"/>
+        <v>40799</v>
+      </c>
+      <c r="O67" s="7">
+        <v>44934</v>
+      </c>
       <c r="P67" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D68" t="s" s="0">
         <v>24</v>
@@ -5289,19 +5280,19 @@
         <v>85</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="J68" t="s" s="0">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="K68" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L68" s="0">
         <v>0</v>
@@ -5310,22 +5301,24 @@
         <v>23</v>
       </c>
       <c r="N68" s="7">
-        <v>46063</v>
-      </c>
-      <c r="O68" s="7"/>
+        <v>42926</v>
+      </c>
+      <c r="O68" s="7">
+        <v>44935</v>
+      </c>
       <c r="P68" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D69" t="s" s="0">
         <v>25</v>
@@ -5337,19 +5330,19 @@
         <v>145</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="J69" t="s" s="0">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="K69" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L69" s="0">
         <v>25</v>
@@ -5358,22 +5351,24 @@
         <v>183</v>
       </c>
       <c r="N69" s="7">
-        <v>46064</v>
-      </c>
-      <c r="O69" s="7"/>
+        <v>43569</v>
+      </c>
+      <c r="O69" s="7">
+        <v>44936</v>
+      </c>
       <c r="P69" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D70" t="s" s="0">
         <v>14</v>
@@ -5385,19 +5380,13 @@
         <v>146</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="I70" t="s" s="0">
-        <v>621</v>
-      </c>
-      <c r="J70" t="s" s="0">
-        <v>622</v>
+        <v>485</v>
       </c>
       <c r="K70" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L70" s="0">
         <v>0</v>
@@ -5408,20 +5397,22 @@
       <c r="N70" s="7">
         <v>42657</v>
       </c>
-      <c r="O70" s="7"/>
+      <c r="O70" s="7">
+        <v>44937</v>
+      </c>
       <c r="P70" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D71" t="s" s="0">
         <v>15</v>
@@ -5433,19 +5424,19 @@
         <v>87</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="J71" t="s" s="0">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="K71" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L71" s="0">
         <v>0</v>
@@ -5456,20 +5447,22 @@
       <c r="N71" s="7">
         <v>38841</v>
       </c>
-      <c r="O71" s="7"/>
+      <c r="O71" s="7">
+        <v>44938</v>
+      </c>
       <c r="P71" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="D72" t="s" s="0">
         <v>16</v>
@@ -5481,13 +5474,19 @@
         <v>87</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>492</v>
+        <v>210</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
+      </c>
+      <c r="I72" t="s" s="0">
+        <v>616</v>
+      </c>
+      <c r="J72" t="s" s="0">
+        <v>617</v>
       </c>
       <c r="K72" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L72" s="0">
         <v>0</v>
@@ -5498,20 +5497,22 @@
       <c r="N72" s="7">
         <v>42522</v>
       </c>
-      <c r="O72" s="7"/>
+      <c r="O72" s="7">
+        <v>44939</v>
+      </c>
       <c r="P72" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D73" t="s" s="0">
         <v>16</v>
@@ -5523,19 +5524,19 @@
         <v>147</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="J73" t="s" s="0">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="K73" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L73" s="0">
         <v>0</v>
@@ -5546,20 +5547,22 @@
       <c r="N73" s="7">
         <v>39748</v>
       </c>
-      <c r="O73" s="7"/>
+      <c r="O73" s="7">
+        <v>44940</v>
+      </c>
       <c r="P73" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D74" t="s" s="0">
         <v>54</v>
@@ -5571,19 +5574,19 @@
         <v>148</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="J74" t="s" s="0">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="K74" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L74" s="0">
         <v>25</v>
@@ -5594,20 +5597,22 @@
       <c r="N74" s="7">
         <v>40427</v>
       </c>
-      <c r="O74" s="7"/>
+      <c r="O74" s="7">
+        <v>44941</v>
+      </c>
       <c r="P74" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D75" t="s" s="0">
         <v>55</v>
@@ -5619,19 +5624,19 @@
         <v>149</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="J75" t="s" s="0">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="K75" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L75" s="0">
         <v>0</v>
@@ -5642,20 +5647,22 @@
       <c r="N75" s="7">
         <v>42543</v>
       </c>
-      <c r="O75" s="7"/>
+      <c r="O75" s="7">
+        <v>44942</v>
+      </c>
       <c r="P75" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s" s="0">
         <v>56</v>
@@ -5667,19 +5674,13 @@
         <v>152</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>634</v>
+        <v>182</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="I76" t="s" s="0">
-        <v>635</v>
-      </c>
-      <c r="J76" t="s" s="0">
-        <v>636</v>
+        <v>276</v>
       </c>
       <c r="K76" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L76" s="0">
         <v>0</v>
@@ -5690,20 +5691,22 @@
       <c r="N76" s="7">
         <v>45341</v>
       </c>
-      <c r="O76" s="7"/>
+      <c r="O76" s="7">
+        <v>45674</v>
+      </c>
       <c r="P76" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D77" t="s" s="0">
         <v>57</v>
@@ -5715,19 +5718,13 @@
         <v>153</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>637</v>
+        <v>214</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="I77" t="s" s="0">
-        <v>639</v>
-      </c>
-      <c r="J77" t="s" s="0">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="K77" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L77" s="0">
         <v>0</v>
@@ -5738,9 +5735,11 @@
       <c r="N77" s="7">
         <v>39295</v>
       </c>
-      <c r="O77" s="7"/>
+      <c r="O77" s="7">
+        <v>44944</v>
+      </c>
       <c r="P77" s="1" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
@@ -5751,13 +5750,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D79" t="s" s="0">
         <v>58</v>
@@ -5769,19 +5768,19 @@
         <v>154</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="J79" t="s" s="0">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="K79" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L79" s="0">
         <v>0</v>
@@ -5792,20 +5791,22 @@
       <c r="N79" s="7">
         <v>45483</v>
       </c>
-      <c r="O79" s="7"/>
+      <c r="O79" s="7">
+        <v>44562</v>
+      </c>
       <c r="P79" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D80" t="s" s="0">
         <v>59</v>
@@ -5817,19 +5818,19 @@
         <v>150</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="J80" t="s" s="0">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="K80" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L80" s="0">
         <v>25</v>
@@ -5840,20 +5841,22 @@
       <c r="N80" s="7">
         <v>45484</v>
       </c>
-      <c r="O80" s="7"/>
+      <c r="O80" s="7">
+        <v>44563</v>
+      </c>
       <c r="P80" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="D81" t="s" s="0">
         <v>60</v>
@@ -5865,19 +5868,19 @@
         <v>93</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="J81" t="s" s="0">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="K81" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L81" s="0">
         <v>0</v>
@@ -5888,20 +5891,22 @@
       <c r="N81" s="7">
         <v>45485</v>
       </c>
-      <c r="O81" s="7"/>
+      <c r="O81" s="7">
+        <v>44564</v>
+      </c>
       <c r="P81" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D82" t="s" s="0">
         <v>61</v>
@@ -5913,19 +5918,19 @@
         <v>107</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="J82" t="s" s="0">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="K82" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L82" s="0">
         <v>0</v>
@@ -5936,20 +5941,22 @@
       <c r="N82" s="7">
         <v>45486</v>
       </c>
-      <c r="O82" s="7"/>
+      <c r="O82" s="7">
+        <v>44565</v>
+      </c>
       <c r="P82" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="D83" t="s" s="0">
         <v>62</v>
@@ -5961,13 +5968,13 @@
         <v>151</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="K83" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L83" s="0">
         <v>0</v>
@@ -5978,20 +5985,22 @@
       <c r="N83" s="7">
         <v>45487</v>
       </c>
-      <c r="O83" s="7"/>
+      <c r="O83" s="7">
+        <v>44566</v>
+      </c>
       <c r="P83" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D84" t="s" s="0">
         <v>63</v>
@@ -6000,19 +6009,19 @@
         <v>85</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="J84" t="s" s="0">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="K84" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L84" s="0">
         <v>0</v>
@@ -6023,27 +6032,29 @@
       <c r="N84" s="7">
         <v>45488</v>
       </c>
-      <c r="O84" s="7"/>
+      <c r="O84" s="7">
+        <v>44567</v>
+      </c>
       <c r="P84" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="6"/>
       <c r="G85" s="1"/>
       <c r="H85" s="3"/>
       <c r="O85" s="7"/>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D86" t="s" s="0">
         <v>64</v>
@@ -6055,19 +6066,19 @@
         <v>155</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="J86" t="s" s="0">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="K86" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L86" s="0">
         <v>25</v>
@@ -6078,20 +6089,22 @@
       <c r="N86" s="7">
         <v>45490</v>
       </c>
-      <c r="O86" s="7"/>
+      <c r="O86" s="7">
+        <v>44569</v>
+      </c>
       <c r="P86" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="D87" t="s" s="0">
         <v>65</v>
@@ -6103,19 +6116,19 @@
         <v>156</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="J87" t="s" s="0">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="K87" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L87" s="0">
         <v>0</v>
@@ -6126,20 +6139,22 @@
       <c r="N87" s="7">
         <v>45491</v>
       </c>
-      <c r="O87" s="7"/>
+      <c r="O87" s="7">
+        <v>44570</v>
+      </c>
       <c r="P87" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D88" t="s" s="0">
         <v>66</v>
@@ -6151,19 +6166,19 @@
         <v>157</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="J88" t="s" s="0">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="K88" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L88" s="0">
         <v>0</v>
@@ -6174,20 +6189,22 @@
       <c r="N88" s="7">
         <v>45492</v>
       </c>
-      <c r="O88" s="7"/>
+      <c r="O88" s="7">
+        <v>44571</v>
+      </c>
       <c r="P88" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D89" t="s" s="0">
         <v>67</v>
@@ -6199,19 +6216,19 @@
         <v>158</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="J89" t="s" s="0">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="K89" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L89" s="0">
         <v>0</v>
@@ -6222,20 +6239,22 @@
       <c r="N89" s="7">
         <v>45493</v>
       </c>
-      <c r="O89" s="7"/>
+      <c r="O89" s="7">
+        <v>44572</v>
+      </c>
       <c r="P89" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="D90" t="s" s="0">
         <v>50</v>
@@ -6244,13 +6263,13 @@
         <v>130</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="K90" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L90" s="0">
         <v>0</v>
@@ -6261,20 +6280,22 @@
       <c r="N90" s="7">
         <v>45494</v>
       </c>
-      <c r="O90" s="7"/>
+      <c r="O90" s="7">
+        <v>44573</v>
+      </c>
       <c r="P90" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="D91" t="s" s="0">
         <v>68</v>
@@ -6286,19 +6307,19 @@
         <v>159</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="J91" t="s" s="0">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="K91" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L91" s="0">
         <v>0</v>
@@ -6309,20 +6330,22 @@
       <c r="N91" s="7">
         <v>45495</v>
       </c>
-      <c r="O91" s="7"/>
+      <c r="O91" s="7">
+        <v>44574</v>
+      </c>
       <c r="P91" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D92" t="s" s="0">
         <v>69</v>
@@ -6334,19 +6357,19 @@
         <v>160</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="J92" t="s" s="0">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="K92" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L92" s="0">
         <v>0</v>
@@ -6355,23 +6378,24 @@
         <v>56</v>
       </c>
       <c r="N92" s="7">
-        <v>46226</v>
-      </c>
-      <c r="O92" s="7"/>
+        <v>45496</v>
+      </c>
+      <c r="O92" s="7">
+        <v>44575</v>
+      </c>
       <c r="P92" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="R92" s="1"/>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D93" t="s" s="0">
         <v>70</v>
@@ -6383,19 +6407,19 @@
         <v>161</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="J93" t="s" s="0">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="K93" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L93" s="0">
         <v>25</v>
@@ -6406,20 +6430,22 @@
       <c r="N93" s="7">
         <v>45497</v>
       </c>
-      <c r="O93" s="7"/>
+      <c r="O93" s="7">
+        <v>44576</v>
+      </c>
       <c r="P93" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="D94" t="s" s="0">
         <v>71</v>
@@ -6432,10 +6458,10 @@
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="3" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="K94" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L94" s="0">
         <v>0</v>
@@ -6446,20 +6472,22 @@
       <c r="N94" s="7">
         <v>45498</v>
       </c>
-      <c r="O94" s="7"/>
+      <c r="O94" s="7">
+        <v>44577</v>
+      </c>
       <c r="P94" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D95" t="s" s="0">
         <v>72</v>
@@ -6471,19 +6499,19 @@
         <v>83</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="J95" t="s" s="0">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="K95" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L95" s="0">
         <v>0</v>
@@ -6492,14 +6520,16 @@
         <v>31</v>
       </c>
       <c r="N95" s="7">
-        <v>46229</v>
-      </c>
-      <c r="O95" s="7"/>
+        <v>45499</v>
+      </c>
+      <c r="O95" s="7">
+        <v>44578</v>
+      </c>
       <c r="P95" s="1" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="6"/>
       <c r="G96" s="1"/>
@@ -6543,13 +6573,13 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="D102" t="s" s="0">
         <v>54</v>
@@ -6561,19 +6591,19 @@
         <v>162</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="J102" t="s" s="0">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="K102" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L102" s="0">
         <v>0</v>
@@ -6584,20 +6614,22 @@
       <c r="N102" s="7">
         <v>45506</v>
       </c>
-      <c r="O102" s="7"/>
+      <c r="O102" s="7">
+        <v>44585</v>
+      </c>
       <c r="P102" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="D103" t="s" s="0">
         <v>55</v>
@@ -6609,19 +6641,19 @@
         <v>163</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="J103" t="s" s="0">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="K103" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L103" s="0">
         <v>25</v>
@@ -6632,20 +6664,22 @@
       <c r="N103" s="7">
         <v>45507</v>
       </c>
-      <c r="O103" s="7"/>
+      <c r="O103" s="7">
+        <v>44586</v>
+      </c>
       <c r="P103" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="D104" t="s" s="0">
         <v>56</v>
@@ -6657,19 +6691,19 @@
         <v>164</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="J104" t="s" s="0">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="K104" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L104" s="0">
         <v>0</v>
@@ -6680,20 +6714,22 @@
       <c r="N104" s="7">
         <v>45508</v>
       </c>
-      <c r="O104" s="7"/>
+      <c r="O104" s="7">
+        <v>44587</v>
+      </c>
       <c r="P104" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D105" t="s" s="0">
         <v>57</v>
@@ -6705,13 +6741,13 @@
         <v>79</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="K105" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L105" s="0">
         <v>0</v>
@@ -6720,22 +6756,24 @@
         <v>6</v>
       </c>
       <c r="N105" s="7">
-        <v>46239</v>
-      </c>
-      <c r="O105" s="7"/>
+        <v>45509</v>
+      </c>
+      <c r="O105" s="7">
+        <v>44588</v>
+      </c>
       <c r="P105" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="D106" t="s" s="0">
         <v>11</v>
@@ -6747,19 +6785,19 @@
         <v>93</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="J106" t="s" s="0">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="K106" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L106" s="0">
         <v>25</v>
@@ -6770,9 +6808,11 @@
       <c r="N106" s="7">
         <v>45510</v>
       </c>
-      <c r="O106" s="7"/>
+      <c r="O106" s="7">
+        <v>44589</v>
+      </c>
       <c r="P106" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
@@ -6917,13 +6957,13 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="D127" t="s" s="0">
         <v>73</v>
@@ -6935,13 +6975,13 @@
         <v>165</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>686</v>
+        <v>286</v>
       </c>
       <c r="K127" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L127" s="0">
         <v>0</v>
@@ -6952,20 +6992,22 @@
       <c r="N127" s="7">
         <v>45531</v>
       </c>
-      <c r="O127" s="7"/>
+      <c r="O127" s="7">
+        <v>45706</v>
+      </c>
       <c r="P127" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="D128" t="s" s="0">
         <v>74</v>
@@ -6977,19 +7019,19 @@
         <v>166</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>687</v>
+        <v>472</v>
       </c>
       <c r="I128" t="s" s="0">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="J128" t="s" s="0">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="K128" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L128" s="0">
         <v>0</v>
@@ -7000,20 +7042,22 @@
       <c r="N128" s="7">
         <v>45532</v>
       </c>
-      <c r="O128" s="7"/>
+      <c r="O128" s="7">
+        <v>44611</v>
+      </c>
       <c r="P128" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D129" t="s" s="0">
         <v>75</v>
@@ -7025,19 +7069,19 @@
         <v>167</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="I129" t="s" s="0">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="J129" t="s" s="0">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="K129" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L129" s="0">
         <v>0</v>
@@ -7048,20 +7092,22 @@
       <c r="N129" s="7">
         <v>45533</v>
       </c>
-      <c r="O129" s="7"/>
+      <c r="O129" s="7">
+        <v>44612</v>
+      </c>
       <c r="P129" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D130" t="s" s="0">
         <v>66</v>
@@ -7073,13 +7119,13 @@
         <v>168</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>693</v>
+        <v>287</v>
       </c>
       <c r="K130" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L130" s="0">
         <v>25</v>
@@ -7090,20 +7136,22 @@
       <c r="N130" s="7">
         <v>45534</v>
       </c>
-      <c r="O130" s="7"/>
+      <c r="O130" s="7">
+        <v>44613</v>
+      </c>
       <c r="P130" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D131" t="s" s="0">
         <v>67</v>
@@ -7115,19 +7163,19 @@
         <v>169</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>694</v>
+        <v>288</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="J131" t="s" s="0">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="K131" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L131" s="0">
         <v>0</v>
@@ -7138,20 +7186,22 @@
       <c r="N131" s="7">
         <v>45535</v>
       </c>
-      <c r="O131" s="7"/>
+      <c r="O131" s="7">
+        <v>44614</v>
+      </c>
       <c r="P131" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D132" t="s" s="0">
         <v>50</v>
@@ -7163,19 +7213,19 @@
         <v>170</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>697</v>
+        <v>289</v>
       </c>
       <c r="I132" t="s" s="0">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="J132" t="s" s="0">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="K132" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="L132" s="0">
         <v>0</v>
@@ -7186,20 +7236,22 @@
       <c r="N132" s="7">
         <v>45536</v>
       </c>
-      <c r="O132" s="7"/>
+      <c r="O132" s="7">
+        <v>44615</v>
+      </c>
       <c r="P132" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D133" t="s" s="0">
         <v>68</v>
@@ -7211,19 +7263,19 @@
         <v>162</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>700</v>
+        <v>290</v>
       </c>
       <c r="I133" t="s" s="0">
-        <v>701</v>
+        <v>681</v>
       </c>
       <c r="J133" t="s" s="0">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="K133" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L133" s="0">
         <v>0</v>
@@ -7234,20 +7286,22 @@
       <c r="N133" s="7">
         <v>45537</v>
       </c>
-      <c r="O133" s="7"/>
+      <c r="O133" s="7">
+        <v>44616</v>
+      </c>
       <c r="P133" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="D134" t="s" s="0">
         <v>69</v>
@@ -7259,19 +7313,19 @@
         <v>163</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>703</v>
+        <v>291</v>
       </c>
       <c r="I134" t="s" s="0">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="J134" t="s" s="0">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="K134" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L134" s="0">
         <v>25</v>
@@ -7282,20 +7336,22 @@
       <c r="N134" s="7">
         <v>45538</v>
       </c>
-      <c r="O134" s="7"/>
+      <c r="O134" s="7">
+        <v>44617</v>
+      </c>
       <c r="P134" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="D135" t="s" s="0">
         <v>70</v>
@@ -7308,10 +7364,10 @@
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="3" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="K135" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L135" s="0">
         <v>0</v>
@@ -7322,20 +7378,22 @@
       <c r="N135" s="7">
         <v>45539</v>
       </c>
-      <c r="O135" s="7"/>
+      <c r="O135" s="7">
+        <v>44618</v>
+      </c>
       <c r="P135" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="D136" t="s" s="0">
         <v>71</v>
@@ -7347,19 +7405,19 @@
         <v>79</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="I136" t="s" s="0">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="J136" t="s" s="0">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="K136" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L136" s="0">
         <v>0</v>
@@ -7370,9 +7428,11 @@
       <c r="N136" s="7">
         <v>45540</v>
       </c>
-      <c r="O136" s="7"/>
+      <c r="O136" s="7">
+        <v>44619</v>
+      </c>
       <c r="P136" s="1" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
@@ -7457,66 +7517,72 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>379</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="0">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>402</v>
-      </c>
-      <c r="H2" s="0">
-        <v>20</v>
+        <v>401</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="K2" s="0">
+        <v>10</v>
+      </c>
+      <c r="L2" s="0">
+        <v>2</v>
       </c>
       <c r="M2" s="0">
         <v>0</v>
@@ -7527,19 +7593,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>452</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>459</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>435</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>409</v>
-      </c>
       <c r="F3" t="s" s="0">
-        <v>382</v>
+        <v>401</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>241</v>
       </c>
       <c r="K3" s="0">
         <v>10</v>
@@ -7553,31 +7622,34 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="0">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>382</v>
-      </c>
-      <c r="K4" s="0">
-        <v>10</v>
-      </c>
-      <c r="L4" s="0">
-        <v>2</v>
+        <v>401</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="H4" s="0">
+        <v>20</v>
+      </c>
+      <c r="I4" s="0">
+        <v>0</v>
       </c>
       <c r="M4" s="0">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7585,28 +7657,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="H5" s="0">
+        <v>241</v>
+      </c>
+      <c r="I5" s="0">
         <v>20</v>
       </c>
-      <c r="I5" s="0">
-        <v>0</v>
+      <c r="J5" s="0">
+        <v>0.2</v>
       </c>
       <c r="M5" s="0">
         <v>21</v>
@@ -7617,28 +7689,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>422</v>
+        <v>447</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I6" s="0">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J6" s="0">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="M6" s="0">
         <v>21</v>
@@ -7649,28 +7721,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I7" s="0">
         <v>50</v>
       </c>
       <c r="J7" s="0">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="M7" s="0">
         <v>21</v>
@@ -7681,28 +7753,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>409</v>
+        <v>428</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I8" s="0">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J8" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="0">
         <v>21</v>
@@ -7713,28 +7785,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C9" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="F9" t="s" s="0">
         <v>401</v>
       </c>
-      <c r="D9" t="s" s="0">
-        <v>425</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>409</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>382</v>
-      </c>
       <c r="G9" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="I9" s="0">
-        <v>100</v>
+        <v>999</v>
       </c>
       <c r="J9" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M9" s="0">
         <v>21</v>
@@ -7742,92 +7814,92 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s" s="0">
+        <v>456</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>412</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F10" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C10" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>409</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>382</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="I10" s="0">
-        <v>999</v>
-      </c>
-      <c r="J10" s="0">
-        <v>5</v>
+      <c r="K10" s="0">
+        <v>10</v>
+      </c>
+      <c r="L10" s="0">
+        <v>14</v>
       </c>
       <c r="M10" s="0">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>388</v>
+        <v>452</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="K11" s="0">
         <v>10</v>
       </c>
       <c r="L11" s="0">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M11" s="0">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>402</v>
-      </c>
-      <c r="K12" s="0">
+        <v>421</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="H12" s="0">
+        <v>50</v>
+      </c>
+      <c r="I12" s="0">
         <v>10</v>
       </c>
-      <c r="L12" s="0">
-        <v>25</v>
-      </c>
       <c r="M12" s="0">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -7835,28 +7907,28 @@
         <v>14</v>
       </c>
       <c r="B13" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>409</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>446</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F13" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C13" t="s" s="0">
-        <v>388</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>389</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>402</v>
-      </c>
       <c r="G13" t="s" s="0">
-        <v>400</v>
-      </c>
-      <c r="H13" s="0">
-        <v>50</v>
+        <v>419</v>
       </c>
       <c r="I13" s="0">
-        <v>10</v>
+        <v>30</v>
+      </c>
+      <c r="J13" s="0">
+        <v>1</v>
       </c>
       <c r="M13" s="0">
         <v>21</v>
@@ -7867,28 +7939,28 @@
         <v>14</v>
       </c>
       <c r="B14" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>410</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>447</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F14" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C14" t="s" s="0">
-        <v>390</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>422</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>402</v>
-      </c>
       <c r="G14" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="I14" s="0">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J14" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="0">
         <v>21</v>
@@ -7899,28 +7971,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>411</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>448</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F15" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C15" t="s" s="0">
-        <v>391</v>
-      </c>
-      <c r="D15" t="s" s="0">
-        <v>423</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>402</v>
-      </c>
       <c r="G15" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="I15" s="0">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J15" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M15" s="0">
         <v>21</v>
@@ -7931,28 +8003,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>420</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>449</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F16" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C16" t="s" s="0">
-        <v>392</v>
-      </c>
-      <c r="D16" t="s" s="0">
-        <v>424</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>402</v>
-      </c>
       <c r="G16" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="I16" s="0">
         <v>50</v>
       </c>
       <c r="J16" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M16" s="0">
         <v>21</v>
@@ -7963,28 +8035,28 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F17" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C17" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="D17" t="s" s="0">
-        <v>425</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>402</v>
-      </c>
       <c r="G17" t="s" s="0">
-        <v>400</v>
+        <v>419</v>
       </c>
       <c r="I17" s="0">
-        <v>50</v>
+        <v>9999</v>
       </c>
       <c r="J17" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M17" s="0">
         <v>21</v>
@@ -7992,34 +8064,28 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="0">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s" s="0">
+        <v>425</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>407</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>457</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>427</v>
+      </c>
+      <c r="F18" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C18" t="s" s="0">
-        <v>404</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>426</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>408</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>402</v>
-      </c>
-      <c r="G18" t="s" s="0">
-        <v>400</v>
-      </c>
-      <c r="I18" s="0">
-        <v>9999</v>
-      </c>
-      <c r="J18" s="0">
+      <c r="H18" s="0">
         <v>20</v>
       </c>
       <c r="M18" s="0">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8027,19 +8093,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="K19" s="0">
         <v>10</v>
@@ -8056,22 +8122,22 @@
         <v>16</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="H20" s="0">
         <v>15</v>
@@ -8091,19 +8157,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="H21" s="0">
         <v>30</v>
@@ -8117,19 +8183,19 @@
         <v>18</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="H22" s="0">
         <v>15</v>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -1,43 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\Practica 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\practica 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F36DD1-3C4E-4A38-B51C-8EE7D69021F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E94603B-99B4-46E3-8C2B-96DA00A00A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF8BD292-BC82-4648-93FB-5EF5760864FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FF8BD292-BC82-4648-93FB-5EF5760864FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Contribuyente" sheetId="1" r:id="rId1"/>
     <sheet name="Ordenanza" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="667">
   <si>
     <t>Nombre</t>
   </si>
@@ -552,9 +541,6 @@
     <t>Chen</t>
   </si>
   <si>
-    <t>71393354C</t>
-  </si>
-  <si>
     <t>09611066X</t>
   </si>
   <si>
@@ -573,18 +559,12 @@
     <t>09689676Y</t>
   </si>
   <si>
-    <t>09570285P</t>
-  </si>
-  <si>
     <t>09570262P</t>
   </si>
   <si>
     <t>09548827D</t>
   </si>
   <si>
-    <t>09548486J</t>
-  </si>
-  <si>
     <t>24304263W</t>
   </si>
   <si>
@@ -600,9 +580,6 @@
     <t>71393396Q</t>
   </si>
   <si>
-    <t>71406027C</t>
-  </si>
-  <si>
     <t>09548451R</t>
   </si>
   <si>
@@ -618,9 +595,6 @@
     <t>09548317M</t>
   </si>
   <si>
-    <t>12649208J</t>
-  </si>
-  <si>
     <t>09758365V</t>
   </si>
   <si>
@@ -636,12 +610,6 @@
     <t>09548501M</t>
   </si>
   <si>
-    <t>09548290R</t>
-  </si>
-  <si>
-    <t>09626048L</t>
-  </si>
-  <si>
     <t>24571671N</t>
   </si>
   <si>
@@ -669,9 +637,6 @@
     <t>09545570H</t>
   </si>
   <si>
-    <t>71393411P</t>
-  </si>
-  <si>
     <t>71393352H</t>
   </si>
   <si>
@@ -681,9 +646,6 @@
     <t>71878948S</t>
   </si>
   <si>
-    <t>X3387K</t>
-  </si>
-  <si>
     <t>09634700T</t>
   </si>
   <si>
@@ -771,9 +733,6 @@
     <t>FechaBaja</t>
   </si>
   <si>
-    <t>24561937521546497521</t>
-  </si>
-  <si>
     <t>36520125638451012515</t>
   </si>
   <si>
@@ -786,9 +745,6 @@
     <t>20960043043554600000</t>
   </si>
   <si>
-    <t>23215465315456411515</t>
-  </si>
-  <si>
     <t>20910936583000000000</t>
   </si>
   <si>
@@ -801,9 +757,6 @@
     <t>34698752714600549403</t>
   </si>
   <si>
-    <t>66649444162310000255</t>
-  </si>
-  <si>
     <t>21508149175421346497</t>
   </si>
   <si>
@@ -843,9 +796,6 @@
     <t>36585214290025478551</t>
   </si>
   <si>
-    <t>31624561042546920007</t>
-  </si>
-  <si>
     <t>36154231712500312566</t>
   </si>
   <si>
@@ -897,24 +847,6 @@
     <t>52198484752100515144</t>
   </si>
   <si>
-    <t>32541112811220000588</t>
-  </si>
-  <si>
-    <t>26221011628048788896</t>
-  </si>
-  <si>
-    <t>12548521518742146695</t>
-  </si>
-  <si>
-    <t>01826530120201560000</t>
-  </si>
-  <si>
-    <t>21651651812511133551</t>
-  </si>
-  <si>
-    <t>51651487910005118185</t>
-  </si>
-  <si>
     <t>DK</t>
   </si>
   <si>
@@ -1350,24 +1282,9 @@
     <t>20960043052159000011</t>
   </si>
   <si>
-    <t>25415</t>
-  </si>
-  <si>
-    <t>x71563258p</t>
-  </si>
-  <si>
     <t>1234567890</t>
   </si>
   <si>
-    <t>10150</t>
-  </si>
-  <si>
-    <t>a56783</t>
-  </si>
-  <si>
-    <t>07815963256</t>
-  </si>
-  <si>
     <t>kg incluidos</t>
   </si>
   <si>
@@ -1422,306 +1339,384 @@
     <t>kg generados</t>
   </si>
   <si>
+    <t>71425232C</t>
+  </si>
+  <si>
+    <t>09632539R</t>
+  </si>
+  <si>
+    <t>15823658A</t>
+  </si>
+  <si>
+    <t>82145896Q</t>
+  </si>
+  <si>
+    <t>15963254N</t>
+  </si>
+  <si>
+    <t>09785530L</t>
+  </si>
+  <si>
+    <t>26551681807651415636</t>
+  </si>
+  <si>
+    <t>31645124443461205100</t>
+  </si>
+  <si>
+    <t>65614874165615445600</t>
+  </si>
+  <si>
+    <t>32569523016220165100</t>
+  </si>
+  <si>
+    <t>21564975243245467900</t>
+  </si>
+  <si>
+    <t>25030000104574745400</t>
+  </si>
+  <si>
+    <t>20910936513000000000</t>
+  </si>
+  <si>
+    <t>12669681145112121200</t>
+  </si>
+  <si>
+    <t>23185484465641685908</t>
+  </si>
+  <si>
+    <t>23164897642213030600</t>
+  </si>
+  <si>
+    <t>51651681961210656544</t>
+  </si>
+  <si>
+    <t>25635478321002541233</t>
+  </si>
+  <si>
+    <t>20008521528775113327</t>
+  </si>
+  <si>
+    <t>25165151118666365191</t>
+  </si>
+  <si>
+    <t>21416325811510005527</t>
+  </si>
+  <si>
+    <t>63516541828944000993</t>
+  </si>
+  <si>
+    <t>20012541150023365296</t>
+  </si>
+  <si>
+    <t>65645150865168448846</t>
+  </si>
+  <si>
+    <t>51556584221251000242</t>
+  </si>
+  <si>
+    <t>32154697195423121012</t>
+  </si>
+  <si>
+    <t>20960043033000100018</t>
+  </si>
+  <si>
+    <t>12548523465214585218</t>
+  </si>
+  <si>
+    <t>20960031442124800018</t>
+  </si>
+  <si>
+    <t>20960043033000100021</t>
+  </si>
+  <si>
+    <t>65168874641561561522</t>
+  </si>
+  <si>
+    <t>20960056133231500032</t>
+  </si>
+  <si>
+    <t>23658965274585223213</t>
+  </si>
+  <si>
+    <t>23652365142254222021</t>
+  </si>
+  <si>
+    <t>36245978133245679018</t>
+  </si>
+  <si>
+    <t>20960043013468900021</t>
+  </si>
+  <si>
+    <t>85550564726165145618</t>
+  </si>
+  <si>
+    <t>12 13 14 25</t>
+  </si>
+  <si>
+    <t>16 17 18 19</t>
+  </si>
+  <si>
+    <t>23432</t>
+  </si>
+  <si>
+    <t>345344</t>
+  </si>
+  <si>
+    <t>43532</t>
+  </si>
+  <si>
+    <t>445454</t>
+  </si>
+  <si>
+    <t>54332</t>
+  </si>
+  <si>
+    <t>234322</t>
+  </si>
+  <si>
+    <t>74635623</t>
+  </si>
+  <si>
+    <t>x8465783</t>
+  </si>
+  <si>
+    <t>83647564</t>
+  </si>
+  <si>
+    <t>83948128</t>
+  </si>
+  <si>
+    <t>92736981</t>
+  </si>
+  <si>
+    <t>a8276465</t>
+  </si>
+  <si>
+    <t>J7364567B</t>
+  </si>
+  <si>
+    <t>25147854</t>
+  </si>
+  <si>
+    <t>12345678</t>
+  </si>
+  <si>
+    <t>25632</t>
+  </si>
+  <si>
+    <t>2563254178</t>
+  </si>
+  <si>
+    <t>12345679</t>
+  </si>
+  <si>
+    <t>12345670</t>
+  </si>
+  <si>
+    <t>87635467891625345671</t>
+  </si>
+  <si>
+    <t>84729478104857627845</t>
+  </si>
+  <si>
+    <t>87457619027384957654</t>
+  </si>
+  <si>
+    <t>87457619024384957654</t>
+  </si>
+  <si>
+    <t>87457619027384957657</t>
+  </si>
+  <si>
+    <t>87457619027384957658</t>
+  </si>
+  <si>
+    <t>87457619027384957659</t>
+  </si>
+  <si>
+    <t>87457619027384957651</t>
+  </si>
+  <si>
+    <t>87457619027384957653</t>
+  </si>
+  <si>
+    <t>87457619027384957617</t>
+  </si>
+  <si>
+    <t>87457619027384957619</t>
+  </si>
+  <si>
+    <t>87457619027384957621</t>
+  </si>
+  <si>
+    <t>21584976902154655485</t>
+  </si>
+  <si>
+    <t>20960043043096200013</t>
+  </si>
+  <si>
+    <t>00750184310702510003</t>
+  </si>
+  <si>
+    <t>64578946740051516403</t>
+  </si>
+  <si>
+    <t>75647586987564758698</t>
+  </si>
+  <si>
+    <t>245619375215464975</t>
+  </si>
+  <si>
+    <t>2321546531545641151567</t>
+  </si>
+  <si>
+    <t>E6664944416231000025</t>
+  </si>
+  <si>
+    <t>3162456104254692000A</t>
+  </si>
+  <si>
+    <t>MC6436520125638451012515</t>
+  </si>
+  <si>
+    <t>rgo00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES9621584976912154655485</t>
+  </si>
+  <si>
+    <t>sdo00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>GR9420125003305201112544</t>
+  </si>
+  <si>
+    <t>vdo00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>FI5620960043043554600000</t>
+  </si>
+  <si>
+    <t>abp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>LT2132566221532587754888</t>
+  </si>
+  <si>
+    <t>acp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>74635623W</t>
+  </si>
+  <si>
+    <t>SM1325894363415485700777</t>
+  </si>
+  <si>
+    <t>lbr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>X8465783N</t>
+  </si>
+  <si>
+    <t>ES0396431245188150005111</t>
+  </si>
+  <si>
+    <t>sbr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>83647564Z</t>
+  </si>
+  <si>
+    <t>AT7125030000194574745400</t>
+  </si>
+  <si>
+    <t>agr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>83948128Z</t>
+  </si>
+  <si>
+    <t>IT2115953684881254695211</t>
+  </si>
+  <si>
+    <t>dgr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>92736981S</t>
+  </si>
+  <si>
+    <t>ES6520960043033096200013</t>
+  </si>
+  <si>
+    <t>pgs00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7423455254983263234411</t>
+  </si>
+  <si>
+    <t>mq00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>GR4920910936583000000000</t>
+  </si>
+  <si>
+    <t>bv00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES0420960043052159000011</t>
+  </si>
+  <si>
+    <t>pp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>DE6912669681125112121200</t>
+  </si>
+  <si>
+    <t>pc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2956187775315550000651</t>
+  </si>
+  <si>
+    <t>gmm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES0425516848021156151054</t>
+  </si>
+  <si>
+    <t>cgm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES4534698752714600549403</t>
+  </si>
+  <si>
+    <t>csn00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>25147854E</t>
+  </si>
+  <si>
+    <t>FR8423185484415641685908</t>
+  </si>
+  <si>
+    <t>gmm01@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>DE5021508149175421346497</t>
+  </si>
+  <si>
+    <t>tcp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>DE6721346154503164978451</t>
+  </si>
+  <si>
+    <t>ccp00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>12345678Z</t>
   </si>
   <si>
-    <t>71393419Q</t>
-  </si>
-  <si>
-    <t>09548283V</t>
-  </si>
-  <si>
-    <t>71425232C</t>
-  </si>
-  <si>
-    <t>09632539R</t>
-  </si>
-  <si>
-    <t>15823658A</t>
-  </si>
-  <si>
-    <t>96523658H</t>
-  </si>
-  <si>
-    <t>82145896Q</t>
-  </si>
-  <si>
-    <t>15963254N</t>
-  </si>
-  <si>
-    <t>09785530L</t>
-  </si>
-  <si>
-    <t>26551681807651415636</t>
-  </si>
-  <si>
-    <t>62541122421110105611</t>
-  </si>
-  <si>
-    <t>31645124443461205100</t>
-  </si>
-  <si>
-    <t>65614874165615445600</t>
-  </si>
-  <si>
-    <t>32569523016220165100</t>
-  </si>
-  <si>
-    <t>21564975243245467900</t>
-  </si>
-  <si>
-    <t>25030000104574745400</t>
-  </si>
-  <si>
-    <t>20910936513000000000</t>
-  </si>
-  <si>
-    <t>12669681145112121200</t>
-  </si>
-  <si>
-    <t>23185484465641685908</t>
-  </si>
-  <si>
-    <t>23164897642213030600</t>
-  </si>
-  <si>
-    <t>51651681961210656544</t>
-  </si>
-  <si>
-    <t>25635478321002541233</t>
-  </si>
-  <si>
-    <t>20008521528775113327</t>
-  </si>
-  <si>
-    <t>25165151118666365191</t>
-  </si>
-  <si>
-    <t>21416325811510005527</t>
-  </si>
-  <si>
-    <t>63516541828944000993</t>
-  </si>
-  <si>
-    <t>20012541150023365296</t>
-  </si>
-  <si>
-    <t>31245164156597845172</t>
-  </si>
-  <si>
-    <t>31215643855060225039</t>
-  </si>
-  <si>
-    <t>65645150865168448846</t>
-  </si>
-  <si>
-    <t>51556584221251000242</t>
-  </si>
-  <si>
-    <t>55065688761051056112</t>
-  </si>
-  <si>
-    <t>36250012804785523317</t>
-  </si>
-  <si>
-    <t>22515651915640081019</t>
-  </si>
-  <si>
-    <t>2158497690215465548</t>
-  </si>
-  <si>
-    <t>0075018431070251000</t>
-  </si>
-  <si>
-    <t>2096004304309620001</t>
-  </si>
-  <si>
-    <t>6457894674005151640</t>
-  </si>
-  <si>
-    <t>A4587946032003165464</t>
-  </si>
-  <si>
-    <t>E6552211148855332200</t>
-  </si>
-  <si>
-    <t>32154697195423121012</t>
-  </si>
-  <si>
-    <t>20960043033000100018</t>
-  </si>
-  <si>
-    <t>12548523465214585218</t>
-  </si>
-  <si>
-    <t>20960031442124800018</t>
-  </si>
-  <si>
-    <t>20960043033000100021</t>
-  </si>
-  <si>
-    <t>65168874641561561522</t>
-  </si>
-  <si>
-    <t>20960056133231500032</t>
-  </si>
-  <si>
-    <t>23658965274585223213</t>
-  </si>
-  <si>
-    <t>23652365142254222021</t>
-  </si>
-  <si>
-    <t>36245978133245679018</t>
-  </si>
-  <si>
-    <t>20960043013468900021</t>
-  </si>
-  <si>
-    <t>85550564726165145618</t>
-  </si>
-  <si>
-    <t>31645124453461205100</t>
-  </si>
-  <si>
-    <t>DK8231645124453461205100</t>
-  </si>
-  <si>
-    <t>jmd00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>65614874115615445600</t>
-  </si>
-  <si>
-    <t>ES4865614874115615445600</t>
-  </si>
-  <si>
-    <t>rfm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>32569523086220165100</t>
-  </si>
-  <si>
-    <t>DE7424561937521546497521</t>
-  </si>
-  <si>
-    <t>aln00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>MC6436520125638451012515</t>
-  </si>
-  <si>
-    <t>rgo00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>GR9420125003305201112544</t>
-  </si>
-  <si>
-    <t>vdo00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES2821651484690980008984</t>
-  </si>
-  <si>
-    <t>vbp00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>FI5620960043043554600000</t>
-  </si>
-  <si>
-    <t>abp00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>21564975263245467900</t>
-  </si>
-  <si>
-    <t>LT2132566221532587754888</t>
-  </si>
-  <si>
-    <t>acp00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>25030000194574745400</t>
-  </si>
-  <si>
-    <t>DK2500750184330702510011</t>
-  </si>
-  <si>
-    <t>cis00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES7423455254983263234411</t>
-  </si>
-  <si>
-    <t>mq00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>GR4920910936583000000000</t>
-  </si>
-  <si>
-    <t>bv00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES0420960043052159000011</t>
-  </si>
-  <si>
-    <t>pp00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>12669681125112121200</t>
-  </si>
-  <si>
-    <t>DE6912669681125112121200</t>
-  </si>
-  <si>
-    <t>pc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES2956187775315550000651</t>
-  </si>
-  <si>
-    <t>gmm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES0425516848021156151054</t>
-  </si>
-  <si>
-    <t>cgm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES4534698752714600549403</t>
-  </si>
-  <si>
-    <t>csn00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES2766649444162310000255</t>
-  </si>
-  <si>
-    <t>alo00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>23185484415641685908</t>
-  </si>
-  <si>
-    <t>FR8423185484415641685908</t>
-  </si>
-  <si>
-    <t>gmm01@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>DE5021508149175421346497</t>
-  </si>
-  <si>
-    <t>tcp00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>DE6721346154503164978451</t>
-  </si>
-  <si>
-    <t>ccp00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>ES7225187786311225455548</t>
   </si>
   <si>
@@ -1740,18 +1735,18 @@
     <t>dlr00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>FI6775647586157564758698</t>
+  </si>
+  <si>
+    <t>har00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>ES5020960043073071400000</t>
   </si>
   <si>
     <t>spr00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES8220960043042158800000</t>
-  </si>
-  <si>
-    <t>gpr00@tasabasura2026.com</t>
-  </si>
-  <si>
     <t>ES7521654587985156484454</t>
   </si>
   <si>
@@ -1764,6 +1759,12 @@
     <t>bfs00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>ES4675647586157564758698</t>
+  </si>
+  <si>
+    <t>dfg00@tasabasura2026.com</t>
+  </si>
+  <si>
     <t>GB9720910936583000000000</t>
   </si>
   <si>
@@ -1776,331 +1777,253 @@
     <t>mlg00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>DE7822631245526916432102</t>
+    <t>ES2120960043043075700000</t>
   </si>
   <si>
     <t>iag00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES2120960043043075700000</t>
-  </si>
-  <si>
-    <t>iag01@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>25635478301002541233</t>
-  </si>
-  <si>
     <t>SM7825635478301002541233</t>
   </si>
   <si>
     <t>gpg00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>32154697155423121012</t>
-  </si>
-  <si>
     <t>ES8932154697155423121012</t>
   </si>
   <si>
     <t>rgg00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>20008521588775113327</t>
-  </si>
-  <si>
     <t>GB5720008521588775113327</t>
   </si>
   <si>
     <t>afg00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>20960043073000100018</t>
-  </si>
-  <si>
-    <t>ES2520960043073000100018</t>
-  </si>
-  <si>
-    <t>apm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>GB0836585214290025478551</t>
+    <t>ES0912548523445214585218</t>
+  </si>
+  <si>
+    <t>alm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES1436154231712500312566</t>
+  </si>
+  <si>
+    <t>ad00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES8244875664127231645789</t>
+  </si>
+  <si>
+    <t>lr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2420960031482124800018</t>
+  </si>
+  <si>
+    <t>lc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES1933218885441445121022</t>
+  </si>
+  <si>
+    <t>afg01@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES8462581542713690044508</t>
+  </si>
+  <si>
+    <t>dgg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES0725165151118666365191</t>
+  </si>
+  <si>
+    <t>rog00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES6020960043023000100021</t>
+  </si>
+  <si>
+    <t>sog00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2965168874681561561522</t>
+  </si>
+  <si>
+    <t>vmg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES3220960583831234500000</t>
+  </si>
+  <si>
+    <t>mbg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7421416325801510005527</t>
+  </si>
+  <si>
+    <t>cbg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>12345670Y</t>
+  </si>
+  <si>
+    <t>LU0932628484504115151115</t>
+  </si>
+  <si>
+    <t>msh00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>12345679S</t>
+  </si>
+  <si>
+    <t>ES6620960056143231500032</t>
+  </si>
+  <si>
+    <t>fdl00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES4063516541858944000993</t>
+  </si>
+  <si>
+    <t>sdm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2923658965294585223213</t>
+  </si>
+  <si>
+    <t>egm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>FI6132658012367712548745</t>
+  </si>
+  <si>
+    <t>gpm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES5223652365132254222021</t>
+  </si>
+  <si>
+    <t>eam00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES9232584216971684051000</t>
+  </si>
+  <si>
+    <t>mg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7395485212315484010000</t>
+  </si>
+  <si>
+    <t>jac00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>LT9321856333126985542360</t>
+  </si>
+  <si>
+    <t>bdc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES4836245978123245679018</t>
+  </si>
+  <si>
+    <t>ngc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2987635467511625345671</t>
+  </si>
+  <si>
+    <t>mlc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>SE6832574512085411002255</t>
+  </si>
+  <si>
+    <t>mlc01@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES4820960043093468900021</t>
+  </si>
+  <si>
+    <t>cfc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7884729478014857627845</t>
+  </si>
+  <si>
+    <t>cgc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES1665165654918886005001</t>
+  </si>
+  <si>
+    <t>ksc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>AT9465645150815168448846</t>
+  </si>
+  <si>
+    <t>mhc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>IT3526551681807651415636</t>
+  </si>
+  <si>
+    <t>cld00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>HU2399558741836555551120</t>
+  </si>
+  <si>
+    <t>mfd00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>IE4751556584261251000242</t>
   </si>
   <si>
     <t>gmm02@tasabasura2026.com</t>
   </si>
   <si>
-    <t>12548523445214585218</t>
-  </si>
-  <si>
-    <t>ES0912548523445214585218</t>
-  </si>
-  <si>
-    <t>alm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES6931624561042546920007</t>
-  </si>
-  <si>
-    <t>ldm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES1436154231712500312566</t>
-  </si>
-  <si>
-    <t>ad00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES8244875664127231645789</t>
-  </si>
-  <si>
-    <t>lr00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>20960031482124800018</t>
-  </si>
-  <si>
-    <t>ES2420960031482124800018</t>
-  </si>
-  <si>
-    <t>lc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES1933218885441445121022</t>
-  </si>
-  <si>
-    <t>afg01@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES8462581542713690044508</t>
-  </si>
-  <si>
-    <t>dgg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>20960043023000100021</t>
-  </si>
-  <si>
-    <t>ES6020960043023000100021</t>
-  </si>
-  <si>
-    <t>sog00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>PT3536952365020014425254</t>
-  </si>
-  <si>
-    <t>vvg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>65168874681561561522</t>
-  </si>
-  <si>
-    <t>ES2965168874681561561522</t>
-  </si>
-  <si>
-    <t>vmg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES3220960583831234500000</t>
-  </si>
-  <si>
-    <t>mbg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>21416325801510005527</t>
-  </si>
-  <si>
-    <t>ES7421416325801510005527</t>
-  </si>
-  <si>
-    <t>cbg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>20960056143231500032</t>
-  </si>
-  <si>
-    <t>63516541858944000993</t>
-  </si>
-  <si>
-    <t>ES4063516541858944000993</t>
-  </si>
-  <si>
-    <t>sdm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>23658965294585223213</t>
-  </si>
-  <si>
-    <t>ES2923658965294585223213</t>
-  </si>
-  <si>
-    <t>egm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>FI6132658012367712548745</t>
-  </si>
-  <si>
-    <t>gpm00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>23652365132254222021</t>
-  </si>
-  <si>
-    <t>ES5223652365132254222021</t>
-  </si>
-  <si>
-    <t>eam00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>20012541120023365296</t>
-  </si>
-  <si>
-    <t>ES9232584216971684051000</t>
-  </si>
-  <si>
-    <t>mg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES7395485212315484010000</t>
-  </si>
-  <si>
-    <t>jac00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>LT9321856333126985542360</t>
-  </si>
-  <si>
-    <t>bdc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>36245978123245679018</t>
-  </si>
-  <si>
-    <t>ES4836245978123245679018</t>
-  </si>
-  <si>
-    <t>ngc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>31245164126597845172</t>
-  </si>
-  <si>
-    <t>ES3331245164126597845172</t>
-  </si>
-  <si>
-    <t>mlc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>SE6832574512085411002255</t>
-  </si>
-  <si>
-    <t>mlc01@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>20960043093468900021</t>
-  </si>
-  <si>
-    <t>ES4820960043093468900021</t>
-  </si>
-  <si>
-    <t>cfc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>31215643895060225039</t>
-  </si>
-  <si>
-    <t>ES9831215643895060225039</t>
-  </si>
-  <si>
-    <t>cgc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>85550564796165145618</t>
-  </si>
-  <si>
-    <t>ES1665165654918886005001</t>
-  </si>
-  <si>
-    <t>ksc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>65645150815168448846</t>
-  </si>
-  <si>
-    <t>AT9465645150815168448846</t>
-  </si>
-  <si>
-    <t>mhc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>IT3526551681807651415636</t>
-  </si>
-  <si>
-    <t>cld00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>HU2399558741836555551120</t>
-  </si>
-  <si>
-    <t>mfd00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>51556584261251000242</t>
-  </si>
-  <si>
-    <t>IE4751556584261251000242</t>
-  </si>
-  <si>
-    <t>gmm03@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>LT9362541122421110105611</t>
+    <t>LT1687457619164384957654</t>
   </si>
   <si>
     <t>dmc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>55065688711051056112</t>
-  </si>
-  <si>
-    <t>ES9255065688711051056112</t>
+    <t>ES9587457619177384957657</t>
   </si>
   <si>
     <t>ebc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES9712548521518742146695</t>
+    <t>ES0687457619167384957659</t>
   </si>
   <si>
     <t>msc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES9001826530120201560000</t>
+    <t>ES4787457619117384957651</t>
   </si>
   <si>
     <t>mdc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES9021651651812511133551</t>
+    <t>ES7987457619197384957653</t>
   </si>
   <si>
     <t>mfc00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>ES6851651487910005118185</t>
+    <t>ES4687457619187384957617</t>
   </si>
   <si>
     <t>cdd00@tasabasura2026.com</t>
   </si>
   <si>
-    <t>36250012834785523317</t>
-  </si>
-  <si>
-    <t>22515651985640081019</t>
-  </si>
-  <si>
-    <t>AT5422515651985640081019</t>
+    <t>AT6887457619187384957621</t>
   </si>
   <si>
     <t>hpd00@tasabasura2026.com</t>
@@ -2182,9 +2105,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2222,7 +2145,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2328,7 +2251,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2470,7 +2393,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2478,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C6ACB8-7F34-425E-9257-91AD8B97F35F}">
-  <dimension ref="A1:P152"/>
+  <dimension ref="A1:R152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.140625"/>
@@ -2494,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>5</v>
@@ -2527,30 +2450,30 @@
         <v>10</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="O1" t="s" s="0">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>93</v>
@@ -2559,19 +2482,13 @@
         <v>128</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>515</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>516</v>
+        <v>444</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L2" s="0">
         <v>0</v>
@@ -2582,19 +2499,22 @@
       <c r="N2" s="7">
         <v>45294</v>
       </c>
+      <c r="O2" s="7">
+        <v>45717</v>
+      </c>
       <c r="P2" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>12</v>
@@ -2606,19 +2526,13 @@
         <v>133</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>518</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -2629,19 +2543,20 @@
       <c r="N3" s="7">
         <v>38267</v>
       </c>
+      <c r="O3" s="7"/>
       <c r="P3" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>13</v>
@@ -2653,13 +2568,13 @@
         <v>134</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>520</v>
+        <v>446</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L4" s="0">
         <v>50</v>
@@ -2670,19 +2585,22 @@
       <c r="N4" s="7">
         <v>39682</v>
       </c>
+      <c r="O4" s="7">
+        <v>45719</v>
+      </c>
       <c r="P4" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>13</v>
@@ -2694,19 +2612,13 @@
         <v>135</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="I5" t="s" s="0">
-        <v>521</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="L5" s="0">
         <v>0</v>
@@ -2717,19 +2629,22 @@
       <c r="N5" s="7">
         <v>38765</v>
       </c>
+      <c r="O5" s="7">
+        <v>45720</v>
+      </c>
       <c r="P5" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>14</v>
@@ -2741,42 +2656,45 @@
         <v>136</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>464</v>
+        <v>437</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>523</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>524</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L6" s="0">
+        <v>516</v>
+      </c>
+      <c r="J6" t="s">
+        <v>517</v>
+      </c>
+      <c r="K6" t="s">
+        <v>232</v>
+      </c>
+      <c r="L6">
         <v>25</v>
       </c>
-      <c r="M6" s="0">
+      <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" s="7">
         <v>38646</v>
       </c>
+      <c r="O6" s="7">
+        <v>45721</v>
+      </c>
       <c r="P6" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D7" t="s" s="0">
         <v>15</v>
@@ -2788,36 +2706,45 @@
         <v>137</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L7" s="0">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0">
+        <v>507</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>518</v>
+      </c>
+      <c r="J7" t="s">
+        <v>519</v>
+      </c>
+      <c r="K7" t="s">
+        <v>232</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>298</v>
       </c>
       <c r="N7" s="7">
         <v>41039</v>
       </c>
+      <c r="O7" s="7">
+        <v>45722</v>
+      </c>
       <c r="P7" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>16</v>
@@ -2829,42 +2756,45 @@
         <v>118</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>525</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>526</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L8" s="0">
+        <v>520</v>
+      </c>
+      <c r="J8" t="s">
+        <v>521</v>
+      </c>
+      <c r="K8" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8">
         <v>25</v>
       </c>
-      <c r="M8" s="0">
+      <c r="M8">
         <v>51</v>
       </c>
       <c r="N8" s="7">
         <v>45738</v>
       </c>
+      <c r="O8" s="7">
+        <v>45723</v>
+      </c>
       <c r="P8" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>16</v>
@@ -2876,19 +2806,13 @@
         <v>138</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I9" t="s" s="0">
-        <v>527</v>
-      </c>
-      <c r="J9" t="s" s="0">
-        <v>528</v>
+        <v>237</v>
       </c>
       <c r="K9" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L9" s="0">
         <v>0</v>
@@ -2899,19 +2823,22 @@
       <c r="N9" s="7">
         <v>45739</v>
       </c>
+      <c r="O9" s="7">
+        <v>45724</v>
+      </c>
       <c r="P9" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>17</v>
@@ -2923,42 +2850,45 @@
         <v>139</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>529</v>
-      </c>
-      <c r="J10" t="s" s="0">
-        <v>530</v>
-      </c>
-      <c r="K10" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L10" s="0">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0">
+        <v>522</v>
+      </c>
+      <c r="J10" t="s">
+        <v>523</v>
+      </c>
+      <c r="K10" t="s">
+        <v>232</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>43</v>
       </c>
       <c r="N10" s="7">
         <v>45740</v>
       </c>
+      <c r="O10" s="7">
+        <v>45725</v>
+      </c>
       <c r="P10" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>18</v>
@@ -2970,13 +2900,13 @@
         <v>125</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>531</v>
+        <v>447</v>
       </c>
       <c r="K11" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L11" s="0">
         <v>25</v>
@@ -2987,19 +2917,22 @@
       <c r="N11" s="7">
         <v>45709</v>
       </c>
+      <c r="O11" s="7">
+        <v>45726</v>
+      </c>
       <c r="P11" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="D12" t="s" s="0">
         <v>19</v>
@@ -3011,42 +2944,43 @@
         <v>140</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>469</v>
+        <v>441</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>532</v>
-      </c>
-      <c r="J12" t="s" s="0">
-        <v>533</v>
-      </c>
-      <c r="K12" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L12" s="0">
-        <v>0</v>
-      </c>
-      <c r="M12" s="0">
+        <v>524</v>
+      </c>
+      <c r="J12" t="s">
+        <v>525</v>
+      </c>
+      <c r="K12" t="s">
+        <v>232</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
       <c r="N12" s="7">
         <v>45710</v>
       </c>
+      <c r="O12" s="7"/>
       <c r="P12" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>20</v>
@@ -3058,13 +2992,13 @@
         <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>249</v>
+        <v>513</v>
       </c>
       <c r="K13" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L13" s="0">
         <v>0</v>
@@ -3075,19 +3009,22 @@
       <c r="N13" s="7">
         <v>45873</v>
       </c>
+      <c r="O13" s="7">
+        <v>45728</v>
+      </c>
       <c r="P13" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>21</v>
@@ -3099,13 +3036,13 @@
         <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="K14" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L14" s="0">
         <v>25</v>
@@ -3116,8 +3053,9 @@
       <c r="N14" s="7">
         <v>45976</v>
       </c>
+      <c r="O14" s="7"/>
       <c r="P14" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -3128,13 +3066,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D16" t="s" s="0">
         <v>22</v>
@@ -3146,36 +3084,43 @@
         <v>141</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>437</v>
+        <v>526</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="K16" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L16" s="0">
-        <v>0</v>
-      </c>
-      <c r="M16" s="0">
+        <v>412</v>
+      </c>
+      <c r="I16" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="J16" t="s">
+        <v>528</v>
+      </c>
+      <c r="K16" t="s">
+        <v>232</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>140</v>
       </c>
       <c r="N16" s="7">
         <v>40637</v>
       </c>
+      <c r="O16" s="7"/>
       <c r="P16" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D17" t="s" s="0">
         <v>23</v>
@@ -3187,36 +3132,43 @@
         <v>141</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>438</v>
+        <v>529</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="K17" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L17" s="0">
-        <v>0</v>
-      </c>
-      <c r="M17" s="0">
+        <v>413</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>530</v>
+      </c>
+      <c r="J17" t="s">
+        <v>531</v>
+      </c>
+      <c r="K17" t="s">
+        <v>232</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>83</v>
       </c>
       <c r="N17" s="7">
         <v>45810</v>
       </c>
+      <c r="O17" s="7"/>
       <c r="P17" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="D18" t="s" s="0">
         <v>24</v>
@@ -3228,36 +3180,43 @@
         <v>142</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>533</v>
+      </c>
+      <c r="J18" t="s">
         <v>534</v>
       </c>
-      <c r="K18" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L18" s="0">
-        <v>0</v>
-      </c>
-      <c r="M18" s="0">
+      <c r="K18" t="s">
+        <v>232</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>122</v>
       </c>
       <c r="N18" s="7">
         <v>45939</v>
       </c>
+      <c r="O18" s="7"/>
       <c r="P18" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D19" t="s" s="0">
         <v>25</v>
@@ -3269,36 +3228,43 @@
         <v>142</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>440</v>
+        <v>535</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="K19" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L19" s="0">
+        <v>414</v>
+      </c>
+      <c r="I19" t="s" s="0">
+        <v>536</v>
+      </c>
+      <c r="J19" t="s">
+        <v>537</v>
+      </c>
+      <c r="K19" t="s">
+        <v>232</v>
+      </c>
+      <c r="L19">
         <v>25</v>
       </c>
-      <c r="M19" s="0">
+      <c r="M19">
         <v>153</v>
       </c>
       <c r="N19" s="7">
         <v>45946</v>
       </c>
+      <c r="O19" s="7"/>
       <c r="P19" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D20" t="s" s="0">
         <v>26</v>
@@ -3310,36 +3276,43 @@
         <v>143</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>441</v>
+        <v>538</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="K20" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L20" s="0">
-        <v>0</v>
-      </c>
-      <c r="M20" s="0">
+        <v>508</v>
+      </c>
+      <c r="I20" t="s" s="0">
+        <v>539</v>
+      </c>
+      <c r="J20" t="s">
+        <v>540</v>
+      </c>
+      <c r="K20" t="s">
+        <v>232</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>100</v>
       </c>
       <c r="N20" s="7">
         <v>45778</v>
       </c>
+      <c r="O20" s="7"/>
       <c r="P20" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="D21" t="s" s="0">
         <v>27</v>
@@ -3351,19 +3324,13 @@
         <v>95</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>171</v>
+        <v>487</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="I21" t="s" s="0">
-        <v>535</v>
-      </c>
-      <c r="J21" t="s" s="0">
-        <v>536</v>
+        <v>415</v>
       </c>
       <c r="K21" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L21" s="0">
         <v>0</v>
@@ -3374,19 +3341,20 @@
       <c r="N21" s="7">
         <v>45627</v>
       </c>
+      <c r="O21" s="7"/>
       <c r="P21" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D22" t="s" s="0">
         <v>28</v>
@@ -3395,42 +3363,43 @@
         <v>89</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>537</v>
-      </c>
-      <c r="J22" t="s" s="0">
-        <v>538</v>
-      </c>
-      <c r="K22" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L22" s="0">
+        <v>541</v>
+      </c>
+      <c r="J22" t="s">
+        <v>542</v>
+      </c>
+      <c r="K22" t="s">
+        <v>232</v>
+      </c>
+      <c r="L22">
         <v>25</v>
       </c>
-      <c r="M22" s="0">
+      <c r="M22">
         <v>74</v>
       </c>
       <c r="N22" s="7">
         <v>45628</v>
       </c>
+      <c r="O22" s="7"/>
       <c r="P22" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="D23" t="s" s="0">
         <v>29</v>
@@ -3439,42 +3408,43 @@
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>250</v>
+        <v>449</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>539</v>
-      </c>
-      <c r="J23" t="s" s="0">
-        <v>540</v>
-      </c>
-      <c r="K23" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L23" s="0">
-        <v>0</v>
-      </c>
-      <c r="M23" s="0">
+        <v>543</v>
+      </c>
+      <c r="J23" t="s">
+        <v>544</v>
+      </c>
+      <c r="K23" t="s">
+        <v>232</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>200</v>
       </c>
       <c r="N23" s="7">
         <v>45629</v>
       </c>
+      <c r="O23" s="7"/>
       <c r="P23" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="0">
         <v>30</v>
@@ -3483,42 +3453,43 @@
         <v>91</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>541</v>
-      </c>
-      <c r="J24" t="s" s="0">
-        <v>542</v>
-      </c>
-      <c r="K24" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L24" s="0">
-        <v>0</v>
-      </c>
-      <c r="M24" s="0">
+        <v>545</v>
+      </c>
+      <c r="J24" t="s">
+        <v>546</v>
+      </c>
+      <c r="K24" t="s">
+        <v>232</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>177</v>
       </c>
       <c r="N24" s="7">
         <v>45630</v>
       </c>
+      <c r="O24" s="7"/>
       <c r="P24" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>31</v>
@@ -3527,31 +3498,32 @@
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>543</v>
+        <v>450</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>544</v>
-      </c>
-      <c r="J25" t="s" s="0">
-        <v>545</v>
-      </c>
-      <c r="K25" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L25" s="0">
+        <v>547</v>
+      </c>
+      <c r="J25" t="s">
+        <v>548</v>
+      </c>
+      <c r="K25" t="s">
+        <v>232</v>
+      </c>
+      <c r="L25">
         <v>25</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M25">
         <v>42</v>
       </c>
       <c r="N25" s="7">
         <v>45631</v>
       </c>
+      <c r="O25" s="7"/>
       <c r="P25" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -3562,13 +3534,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D27" t="s" s="0">
         <v>32</v>
@@ -3580,45 +3552,43 @@
         <v>132</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>546</v>
-      </c>
-      <c r="J27" t="s" s="0">
-        <v>547</v>
-      </c>
-      <c r="K27" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L27" s="0">
-        <v>0</v>
-      </c>
-      <c r="M27" s="0">
+        <v>549</v>
+      </c>
+      <c r="J27" t="s">
+        <v>550</v>
+      </c>
+      <c r="K27" t="s">
+        <v>232</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>88</v>
       </c>
       <c r="N27" s="7">
-        <v>39525</v>
-      </c>
-      <c r="O27" s="7">
-        <v>45352</v>
-      </c>
+        <v>46023</v>
+      </c>
+      <c r="O27" s="7"/>
       <c r="P27" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D28" t="s" s="0">
         <v>33</v>
@@ -3630,45 +3600,43 @@
         <v>133</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>548</v>
-      </c>
-      <c r="J28" t="s" s="0">
-        <v>549</v>
-      </c>
-      <c r="K28" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L28" s="0">
+        <v>551</v>
+      </c>
+      <c r="J28" t="s">
+        <v>552</v>
+      </c>
+      <c r="K28" t="s">
+        <v>232</v>
+      </c>
+      <c r="L28">
         <v>25</v>
       </c>
-      <c r="M28" s="0">
+      <c r="M28">
         <v>101</v>
       </c>
       <c r="N28" s="7">
-        <v>42667</v>
-      </c>
-      <c r="O28" s="7">
-        <v>45353</v>
-      </c>
+        <v>46024</v>
+      </c>
+      <c r="O28" s="7"/>
       <c r="P28" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s" s="0">
         <v>34</v>
@@ -3680,13 +3648,13 @@
         <v>134</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>178</v>
+        <v>488</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="K29" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L29" s="0">
         <v>0</v>
@@ -3695,24 +3663,22 @@
         <v>10</v>
       </c>
       <c r="N29" s="7">
-        <v>44639</v>
-      </c>
-      <c r="O29" s="7">
-        <v>45354</v>
-      </c>
+        <v>46025</v>
+      </c>
+      <c r="O29" s="7"/>
       <c r="P29" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C30" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D30" t="s" s="0">
         <v>35</v>
@@ -3724,45 +3690,43 @@
         <v>135</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>550</v>
-      </c>
-      <c r="J30" t="s" s="0">
-        <v>551</v>
-      </c>
-      <c r="K30" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L30" s="0">
-        <v>0</v>
-      </c>
-      <c r="M30" s="0">
+        <v>553</v>
+      </c>
+      <c r="J30" t="s">
+        <v>554</v>
+      </c>
+      <c r="K30" t="s">
+        <v>232</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>78</v>
       </c>
       <c r="N30" s="7">
-        <v>37937</v>
-      </c>
-      <c r="O30" s="7">
-        <v>45355</v>
-      </c>
+        <v>46026</v>
+      </c>
+      <c r="O30" s="7"/>
       <c r="P30" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C31" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D31" t="s" s="0">
         <v>36</v>
@@ -3774,19 +3738,13 @@
         <v>136</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="I31" t="s" s="0">
-        <v>552</v>
-      </c>
-      <c r="J31" t="s" s="0">
-        <v>553</v>
+        <v>514</v>
       </c>
       <c r="K31" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L31" s="0">
         <v>0</v>
@@ -3795,24 +3753,22 @@
         <v>71</v>
       </c>
       <c r="N31" s="7">
-        <v>43242</v>
-      </c>
-      <c r="O31" s="7">
-        <v>45356</v>
-      </c>
+        <v>46027</v>
+      </c>
+      <c r="O31" s="7"/>
       <c r="P31" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D32" t="s" s="0">
         <v>37</v>
@@ -3824,34 +3780,32 @@
         <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>181</v>
+        <v>555</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>554</v>
+        <v>451</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>555</v>
-      </c>
-      <c r="J32" t="s" s="0">
         <v>556</v>
       </c>
-      <c r="K32" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L32" s="0">
-        <v>0</v>
-      </c>
-      <c r="M32" s="0">
+      <c r="J32" t="s">
+        <v>557</v>
+      </c>
+      <c r="K32" t="s">
+        <v>232</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>113</v>
       </c>
       <c r="N32" s="7">
-        <v>39555</v>
-      </c>
-      <c r="O32" s="7">
-        <v>45357</v>
-      </c>
+        <v>46028</v>
+      </c>
+      <c r="O32" s="7"/>
       <c r="P32" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -3877,13 +3831,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="C36" t="s" s="0">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D36" t="s" s="0">
         <v>38</v>
@@ -3895,45 +3849,43 @@
         <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>557</v>
-      </c>
-      <c r="J36" t="s" s="0">
         <v>558</v>
       </c>
-      <c r="K36" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L36" s="0">
+      <c r="J36" t="s">
+        <v>559</v>
+      </c>
+      <c r="K36" t="s">
+        <v>232</v>
+      </c>
+      <c r="L36">
         <v>25</v>
       </c>
-      <c r="M36" s="0">
+      <c r="M36">
         <v>13</v>
       </c>
       <c r="N36" s="7">
         <v>43230</v>
       </c>
-      <c r="O36" s="7">
-        <v>45361</v>
-      </c>
+      <c r="O36" s="7"/>
       <c r="P36" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C37" t="s" s="0">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D37" t="s" s="0">
         <v>39</v>
@@ -3945,45 +3897,43 @@
         <v>140</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>559</v>
-      </c>
-      <c r="J37" t="s" s="0">
         <v>560</v>
       </c>
-      <c r="K37" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L37" s="0">
-        <v>0</v>
-      </c>
-      <c r="M37" s="0">
+      <c r="J37" t="s">
+        <v>561</v>
+      </c>
+      <c r="K37" t="s">
+        <v>232</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
         <v>9</v>
       </c>
       <c r="N37" s="7">
         <v>38841</v>
       </c>
-      <c r="O37" s="7">
-        <v>45362</v>
-      </c>
+      <c r="O37" s="7"/>
       <c r="P37" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C38" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D38" t="s" s="0">
         <v>40</v>
@@ -3995,45 +3945,43 @@
         <v>109</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>208</v>
+        <v>562</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>561</v>
-      </c>
-      <c r="J38" t="s" s="0">
-        <v>562</v>
-      </c>
-      <c r="K38" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L38" s="0">
-        <v>0</v>
-      </c>
-      <c r="M38" s="0">
+        <v>563</v>
+      </c>
+      <c r="J38" t="s">
+        <v>564</v>
+      </c>
+      <c r="K38" t="s">
+        <v>232</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>120</v>
       </c>
       <c r="N38" s="7">
         <v>44389</v>
       </c>
-      <c r="O38" s="7">
-        <v>45363</v>
-      </c>
+      <c r="O38" s="7"/>
       <c r="P38" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="C39" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D39" t="s" s="0">
         <v>41</v>
@@ -4045,13 +3993,13 @@
         <v>109</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="K39" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L39" s="0">
         <v>0</v>
@@ -4062,22 +4010,20 @@
       <c r="N39" s="7">
         <v>45242</v>
       </c>
-      <c r="O39" s="7">
-        <v>45364</v>
-      </c>
+      <c r="O39" s="7"/>
       <c r="P39" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="C40" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D40" t="s" s="0">
         <v>42</v>
@@ -4089,45 +4035,43 @@
         <v>144</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>563</v>
-      </c>
-      <c r="J40" t="s" s="0">
-        <v>564</v>
-      </c>
-      <c r="K40" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L40" s="0">
-        <v>0</v>
-      </c>
-      <c r="M40" s="0">
+        <v>565</v>
+      </c>
+      <c r="J40" t="s">
+        <v>566</v>
+      </c>
+      <c r="K40" t="s">
+        <v>232</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>172</v>
       </c>
       <c r="N40" s="7">
         <v>41309</v>
       </c>
-      <c r="O40" s="7">
-        <v>45365</v>
-      </c>
+      <c r="O40" s="7"/>
       <c r="P40" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="C41" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s" s="0">
         <v>43</v>
@@ -4139,45 +4083,43 @@
         <v>141</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>565</v>
-      </c>
-      <c r="J41" t="s" s="0">
-        <v>566</v>
-      </c>
-      <c r="K41" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L41" s="0">
-        <v>0</v>
-      </c>
-      <c r="M41" s="0">
+        <v>567</v>
+      </c>
+      <c r="J41" t="s">
+        <v>568</v>
+      </c>
+      <c r="K41" t="s">
+        <v>232</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>79</v>
       </c>
       <c r="N41" s="7">
         <v>45142</v>
       </c>
-      <c r="O41" s="7">
-        <v>45366</v>
-      </c>
+      <c r="O41" s="7"/>
       <c r="P41" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="C42" t="s" s="0">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="D42" t="s" s="0">
         <v>44</v>
@@ -4189,39 +4131,43 @@
         <v>141</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>470</v>
+        <v>442</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="K42" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L42" s="0">
-        <v>0</v>
-      </c>
-      <c r="M42" s="0">
+        <v>511</v>
+      </c>
+      <c r="I42" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="J42" t="s">
+        <v>570</v>
+      </c>
+      <c r="K42" t="s">
+        <v>232</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>118</v>
       </c>
       <c r="N42" s="7">
         <v>45048</v>
       </c>
-      <c r="O42" s="7">
-        <v>45367</v>
-      </c>
+      <c r="O42" s="7"/>
       <c r="P42" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="C43" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D43" t="s" s="0">
         <v>45</v>
@@ -4233,45 +4179,43 @@
         <v>142</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>567</v>
-      </c>
-      <c r="J43" t="s" s="0">
-        <v>568</v>
-      </c>
-      <c r="K43" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L43" s="0">
-        <v>0</v>
-      </c>
-      <c r="M43" s="0">
+        <v>571</v>
+      </c>
+      <c r="J43" t="s">
+        <v>572</v>
+      </c>
+      <c r="K43" t="s">
+        <v>232</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>154</v>
       </c>
       <c r="N43" s="7">
         <v>44479</v>
       </c>
-      <c r="O43" s="7">
-        <v>45368</v>
-      </c>
+      <c r="O43" s="7"/>
       <c r="P43" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="C44" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D44" t="s" s="0">
         <v>37</v>
@@ -4283,19 +4227,13 @@
         <v>142</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>187</v>
+        <v>562</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I44" t="s" s="0">
-        <v>569</v>
-      </c>
-      <c r="J44" t="s" s="0">
-        <v>570</v>
+        <v>249</v>
       </c>
       <c r="K44" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L44" s="0">
         <v>0</v>
@@ -4306,22 +4244,20 @@
       <c r="N44" s="7">
         <v>42624</v>
       </c>
-      <c r="O44" s="7">
-        <v>45369</v>
-      </c>
+      <c r="O44" s="7"/>
       <c r="P44" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C45" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D45" t="s" s="0">
         <v>46</v>
@@ -4333,45 +4269,43 @@
         <v>143</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>571</v>
-      </c>
-      <c r="J45" t="s" s="0">
-        <v>572</v>
-      </c>
-      <c r="K45" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L45" s="0">
-        <v>0</v>
-      </c>
-      <c r="M45" s="0">
+        <v>573</v>
+      </c>
+      <c r="J45" t="s">
+        <v>574</v>
+      </c>
+      <c r="K45" t="s">
+        <v>232</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
         <v>99</v>
       </c>
       <c r="N45" s="7">
         <v>42708</v>
       </c>
-      <c r="O45" s="7">
-        <v>45370</v>
-      </c>
+      <c r="O45" s="7"/>
       <c r="P45" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="C46" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D46" t="s" s="0">
         <v>47</v>
@@ -4383,45 +4317,43 @@
         <v>95</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>573</v>
-      </c>
-      <c r="J46" t="s" s="0">
-        <v>574</v>
-      </c>
-      <c r="K46" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L46" s="0">
-        <v>0</v>
-      </c>
-      <c r="M46" s="0">
+        <v>575</v>
+      </c>
+      <c r="J46" t="s">
+        <v>576</v>
+      </c>
+      <c r="K46" t="s">
+        <v>232</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>65</v>
       </c>
       <c r="N46" s="7">
         <v>44180</v>
       </c>
-      <c r="O46" s="7">
-        <v>45371</v>
-      </c>
+      <c r="O46" s="7"/>
       <c r="P46" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="C47" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D47" t="s" s="0">
         <v>48</v>
@@ -4433,39 +4365,43 @@
         <v>85</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="K47" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L47" s="0">
-        <v>0</v>
-      </c>
-      <c r="M47" s="0">
+        <v>511</v>
+      </c>
+      <c r="I47" t="s" s="0">
+        <v>577</v>
+      </c>
+      <c r="J47" t="s">
+        <v>578</v>
+      </c>
+      <c r="K47" t="s">
+        <v>232</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>94</v>
       </c>
       <c r="N47" s="7">
         <v>45047</v>
       </c>
-      <c r="O47" s="7">
-        <v>45372</v>
-      </c>
+      <c r="O47" s="7"/>
       <c r="P47" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C48" t="s" s="0">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D48" t="s" s="0">
         <v>49</v>
@@ -4477,45 +4413,43 @@
         <v>85</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>575</v>
-      </c>
-      <c r="J48" t="s" s="0">
-        <v>576</v>
-      </c>
-      <c r="K48" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L48" s="0">
+        <v>579</v>
+      </c>
+      <c r="J48" t="s">
+        <v>580</v>
+      </c>
+      <c r="K48" t="s">
+        <v>232</v>
+      </c>
+      <c r="L48">
         <v>25</v>
       </c>
-      <c r="M48" s="0">
+      <c r="M48">
         <v>41</v>
       </c>
       <c r="N48" s="7">
         <v>42182</v>
       </c>
-      <c r="O48" s="7">
-        <v>45373</v>
-      </c>
+      <c r="O48" s="7"/>
       <c r="P48" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="C49" t="s" s="0">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D49" t="s" s="0">
         <v>50</v>
@@ -4527,45 +4461,43 @@
         <v>145</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I49" t="s" s="0">
+        <v>581</v>
+      </c>
+      <c r="J49" t="s">
+        <v>582</v>
+      </c>
+      <c r="K49" t="s">
+        <v>232</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>192</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="I49" t="s" s="0">
-        <v>577</v>
-      </c>
-      <c r="J49" t="s" s="0">
-        <v>578</v>
-      </c>
-      <c r="K49" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L49" s="0">
-        <v>0</v>
-      </c>
-      <c r="M49" s="0">
-        <v>192</v>
-      </c>
       <c r="N49" s="7">
-        <v>43032</v>
-      </c>
-      <c r="O49" s="7">
-        <v>45374</v>
-      </c>
+        <v>46319</v>
+      </c>
+      <c r="O49" s="7"/>
       <c r="P49" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C50" t="s" s="0">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D50" t="s" s="0">
         <v>51</v>
@@ -4577,19 +4509,13 @@
         <v>146</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>193</v>
+        <v>562</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="I50" t="s" s="0">
-        <v>579</v>
-      </c>
-      <c r="J50" t="s" s="0">
-        <v>580</v>
+        <v>252</v>
       </c>
       <c r="K50" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L50" s="0">
         <v>0</v>
@@ -4600,22 +4526,20 @@
       <c r="N50" s="7">
         <v>42490</v>
       </c>
-      <c r="O50" s="7">
-        <v>45375</v>
-      </c>
+      <c r="O50" s="7"/>
       <c r="P50" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C51" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D51" t="s" s="0">
         <v>51</v>
@@ -4627,45 +4551,43 @@
         <v>87</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>581</v>
-      </c>
-      <c r="J51" t="s" s="0">
-        <v>582</v>
-      </c>
-      <c r="K51" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L51" s="0">
+        <v>583</v>
+      </c>
+      <c r="J51" t="s">
+        <v>584</v>
+      </c>
+      <c r="K51" t="s">
+        <v>232</v>
+      </c>
+      <c r="L51">
         <v>25</v>
       </c>
-      <c r="M51" s="0">
+      <c r="M51">
         <v>157</v>
       </c>
       <c r="N51" s="7">
         <v>39101</v>
       </c>
-      <c r="O51" s="7">
-        <v>45376</v>
-      </c>
+      <c r="O51" s="7"/>
       <c r="P51" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C52" t="s" s="0">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D52" t="s" s="0">
         <v>11</v>
@@ -4677,45 +4599,43 @@
         <v>87</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>583</v>
+        <v>454</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>584</v>
-      </c>
-      <c r="J52" t="s" s="0">
         <v>585</v>
       </c>
-      <c r="K52" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L52" s="0">
-        <v>0</v>
-      </c>
-      <c r="M52" s="0">
+      <c r="J52" t="s">
+        <v>586</v>
+      </c>
+      <c r="K52" t="s">
+        <v>232</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>126</v>
       </c>
       <c r="N52" s="7">
         <v>44962</v>
       </c>
-      <c r="O52" s="7">
-        <v>45377</v>
-      </c>
+      <c r="O52" s="7"/>
       <c r="P52" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C53" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D53" t="s" s="0">
         <v>12</v>
@@ -4727,45 +4647,43 @@
         <v>147</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>586</v>
+        <v>462</v>
       </c>
       <c r="I53" t="s" s="0">
         <v>587</v>
       </c>
-      <c r="J53" t="s" s="0">
+      <c r="J53" t="s">
         <v>588</v>
       </c>
-      <c r="K53" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L53" s="0">
-        <v>0</v>
-      </c>
-      <c r="M53" s="0">
+      <c r="K53" t="s">
+        <v>232</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
         <v>184</v>
       </c>
       <c r="N53" s="7">
         <v>42148</v>
       </c>
-      <c r="O53" s="7">
-        <v>45378</v>
-      </c>
+      <c r="O53" s="7"/>
       <c r="P53" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C54" t="s" s="0">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="D54" t="s" s="0">
         <v>13</v>
@@ -4777,13 +4695,13 @@
         <v>148</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="K54" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L54" s="0">
         <v>25</v>
@@ -4794,22 +4712,20 @@
       <c r="N54" s="7">
         <v>43805</v>
       </c>
-      <c r="O54" s="7">
-        <v>45379</v>
-      </c>
+      <c r="O54" s="7"/>
       <c r="P54" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C55" t="s" s="0">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D55" t="s" s="0">
         <v>13</v>
@@ -4821,34 +4737,32 @@
         <v>149</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H55" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="I55" t="s" s="0">
         <v>589</v>
       </c>
-      <c r="I55" t="s" s="0">
+      <c r="J55" t="s">
         <v>590</v>
       </c>
-      <c r="J55" t="s" s="0">
-        <v>591</v>
-      </c>
-      <c r="K55" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L55" s="0">
-        <v>0</v>
-      </c>
-      <c r="M55" s="0">
+      <c r="K55" t="s">
+        <v>232</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
         <v>44</v>
       </c>
       <c r="N55" s="7">
         <v>40575</v>
       </c>
-      <c r="O55" s="7">
-        <v>45380</v>
-      </c>
+      <c r="O55" s="7"/>
       <c r="P55" s="1" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -4877,13 +4791,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C60" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D60" t="s" s="0">
         <v>17</v>
@@ -4895,19 +4809,13 @@
         <v>150</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>199</v>
+        <v>491</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="I60" t="s" s="0">
-        <v>593</v>
-      </c>
-      <c r="J60" t="s" s="0">
-        <v>594</v>
+        <v>463</v>
       </c>
       <c r="K60" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L60" s="0">
         <v>0</v>
@@ -4916,24 +4824,22 @@
         <v>27</v>
       </c>
       <c r="N60" s="7">
-        <v>38607</v>
-      </c>
-      <c r="O60" s="7">
-        <v>44927</v>
-      </c>
+        <v>46055</v>
+      </c>
+      <c r="O60" s="7"/>
       <c r="P60" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="C61" t="s" s="0">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="D61" t="s" s="0">
         <v>52</v>
@@ -4945,19 +4851,13 @@
         <v>93</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>200</v>
+        <v>418</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="I61" t="s" s="0">
-        <v>595</v>
-      </c>
-      <c r="J61" t="s" s="0">
-        <v>596</v>
+        <v>255</v>
       </c>
       <c r="K61" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L61" s="0">
         <v>0</v>
@@ -4966,24 +4866,22 @@
         <v>167</v>
       </c>
       <c r="N61" s="7">
-        <v>42083</v>
-      </c>
-      <c r="O61" s="7">
-        <v>44928</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="O61" s="7"/>
       <c r="P61" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C62" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D62" t="s" s="0">
         <v>19</v>
@@ -4995,45 +4893,43 @@
         <v>107</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>597</v>
+        <v>464</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>598</v>
-      </c>
-      <c r="J62" t="s" s="0">
-        <v>599</v>
-      </c>
-      <c r="K62" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L62" s="0">
+        <v>591</v>
+      </c>
+      <c r="J62" t="s">
+        <v>592</v>
+      </c>
+      <c r="K62" t="s">
+        <v>232</v>
+      </c>
+      <c r="L62">
         <v>25</v>
       </c>
-      <c r="M62" s="0">
+      <c r="M62">
         <v>82</v>
       </c>
       <c r="N62" s="7">
-        <v>39105</v>
-      </c>
-      <c r="O62" s="7">
-        <v>44929</v>
-      </c>
+        <v>46057</v>
+      </c>
+      <c r="O62" s="7"/>
       <c r="P62" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C63" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D63" t="s" s="0">
         <v>20</v>
@@ -5045,19 +4941,13 @@
         <v>151</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="I63" t="s" s="0">
-        <v>600</v>
-      </c>
-      <c r="J63" t="s" s="0">
-        <v>601</v>
+        <v>515</v>
       </c>
       <c r="K63" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L63" s="0">
         <v>0</v>
@@ -5066,24 +4956,22 @@
         <v>122</v>
       </c>
       <c r="N63" s="7">
-        <v>41938</v>
-      </c>
-      <c r="O63" s="7">
-        <v>44930</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="O63" s="7"/>
       <c r="P63" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C64" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D64" t="s" s="0">
         <v>21</v>
@@ -5092,45 +4980,43 @@
         <v>114</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>602</v>
-      </c>
-      <c r="J64" t="s" s="0">
-        <v>603</v>
-      </c>
-      <c r="K64" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L64" s="0">
-        <v>0</v>
-      </c>
-      <c r="M64" s="0">
+        <v>593</v>
+      </c>
+      <c r="J64" t="s">
+        <v>594</v>
+      </c>
+      <c r="K64" t="s">
+        <v>232</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
         <v>92</v>
       </c>
       <c r="N64" s="7">
-        <v>43691</v>
-      </c>
-      <c r="O64" s="7">
-        <v>44931</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="O64" s="7"/>
       <c r="P64" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C65" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D65" t="s" s="0">
         <v>53</v>
@@ -5139,45 +5025,43 @@
         <v>115</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>604</v>
-      </c>
-      <c r="J65" t="s" s="0">
-        <v>605</v>
-      </c>
-      <c r="K65" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L65" s="0">
-        <v>0</v>
-      </c>
-      <c r="M65" s="0">
+        <v>595</v>
+      </c>
+      <c r="J65" t="s">
+        <v>596</v>
+      </c>
+      <c r="K65" t="s">
+        <v>232</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
         <v>28</v>
       </c>
       <c r="N65" s="7">
-        <v>42810</v>
-      </c>
-      <c r="O65" s="7">
-        <v>44932</v>
-      </c>
+        <v>46060</v>
+      </c>
+      <c r="O65" s="7"/>
       <c r="P65" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C66" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D66" t="s" s="0">
         <v>22</v>
@@ -5186,45 +5070,43 @@
         <v>116</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>606</v>
+        <v>465</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>607</v>
-      </c>
-      <c r="J66" t="s" s="0">
-        <v>608</v>
-      </c>
-      <c r="K66" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L66" s="0">
-        <v>0</v>
-      </c>
-      <c r="M66" s="0">
+        <v>597</v>
+      </c>
+      <c r="J66" t="s">
+        <v>598</v>
+      </c>
+      <c r="K66" t="s">
+        <v>232</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
         <v>6</v>
       </c>
       <c r="N66" s="7">
-        <v>45570</v>
-      </c>
-      <c r="O66" s="7">
-        <v>44933</v>
-      </c>
+        <v>46061</v>
+      </c>
+      <c r="O66" s="7"/>
       <c r="P66" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C67" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D67" t="s" s="0">
         <v>23</v>
@@ -5236,13 +5118,13 @@
         <v>85</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K67" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L67" s="0">
         <v>0</v>
@@ -5251,24 +5133,22 @@
         <v>200</v>
       </c>
       <c r="N67" s="7">
-        <v>40799</v>
-      </c>
-      <c r="O67" s="7">
-        <v>44934</v>
-      </c>
+        <v>46062</v>
+      </c>
+      <c r="O67" s="7"/>
       <c r="P67" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C68" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D68" t="s" s="0">
         <v>24</v>
@@ -5280,45 +5160,43 @@
         <v>85</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>609</v>
-      </c>
-      <c r="J68" t="s" s="0">
-        <v>610</v>
-      </c>
-      <c r="K68" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L68" s="0">
-        <v>0</v>
-      </c>
-      <c r="M68" s="0">
+        <v>599</v>
+      </c>
+      <c r="J68" t="s">
+        <v>600</v>
+      </c>
+      <c r="K68" t="s">
+        <v>232</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
         <v>23</v>
       </c>
       <c r="N68" s="7">
-        <v>42926</v>
-      </c>
-      <c r="O68" s="7">
-        <v>44935</v>
-      </c>
+        <v>46063</v>
+      </c>
+      <c r="O68" s="7"/>
       <c r="P68" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="C69" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D69" t="s" s="0">
         <v>25</v>
@@ -5330,45 +5208,43 @@
         <v>145</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>611</v>
-      </c>
-      <c r="J69" t="s" s="0">
-        <v>612</v>
-      </c>
-      <c r="K69" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L69" s="0">
+        <v>601</v>
+      </c>
+      <c r="J69" t="s">
+        <v>602</v>
+      </c>
+      <c r="K69" t="s">
+        <v>232</v>
+      </c>
+      <c r="L69">
         <v>25</v>
       </c>
-      <c r="M69" s="0">
+      <c r="M69">
         <v>183</v>
       </c>
       <c r="N69" s="7">
-        <v>43569</v>
-      </c>
-      <c r="O69" s="7">
-        <v>44936</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="O69" s="7"/>
       <c r="P69" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C70" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D70" t="s" s="0">
         <v>14</v>
@@ -5380,39 +5256,43 @@
         <v>146</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="K70" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L70" s="0">
-        <v>0</v>
-      </c>
-      <c r="M70" s="0">
+        <v>456</v>
+      </c>
+      <c r="I70" t="s" s="0">
+        <v>603</v>
+      </c>
+      <c r="J70" t="s">
+        <v>604</v>
+      </c>
+      <c r="K70" t="s">
+        <v>232</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
         <v>73</v>
       </c>
       <c r="N70" s="7">
         <v>42657</v>
       </c>
-      <c r="O70" s="7">
-        <v>44937</v>
-      </c>
+      <c r="O70" s="7"/>
       <c r="P70" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C71" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D71" t="s" s="0">
         <v>15</v>
@@ -5424,45 +5304,43 @@
         <v>87</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>613</v>
+        <v>466</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>614</v>
-      </c>
-      <c r="J71" t="s" s="0">
-        <v>615</v>
-      </c>
-      <c r="K71" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L71" s="0">
-        <v>0</v>
-      </c>
-      <c r="M71" s="0">
+        <v>605</v>
+      </c>
+      <c r="J71" t="s">
+        <v>606</v>
+      </c>
+      <c r="K71" t="s">
+        <v>232</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
         <v>180</v>
       </c>
       <c r="N71" s="7">
         <v>38841</v>
       </c>
-      <c r="O71" s="7">
-        <v>44938</v>
-      </c>
+      <c r="O71" s="7"/>
       <c r="P71" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C72" t="s" s="0">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="D72" t="s" s="0">
         <v>16</v>
@@ -5474,19 +5352,13 @@
         <v>87</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I72" t="s" s="0">
-        <v>616</v>
-      </c>
-      <c r="J72" t="s" s="0">
-        <v>617</v>
+        <v>261</v>
       </c>
       <c r="K72" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L72" s="0">
         <v>0</v>
@@ -5497,22 +5369,20 @@
       <c r="N72" s="7">
         <v>42522</v>
       </c>
-      <c r="O72" s="7">
-        <v>44939</v>
-      </c>
+      <c r="O72" s="7"/>
       <c r="P72" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C73" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D73" t="s" s="0">
         <v>16</v>
@@ -5524,45 +5394,43 @@
         <v>147</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>618</v>
+        <v>467</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>619</v>
-      </c>
-      <c r="J73" t="s" s="0">
-        <v>620</v>
-      </c>
-      <c r="K73" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L73" s="0">
-        <v>0</v>
-      </c>
-      <c r="M73" s="0">
+        <v>607</v>
+      </c>
+      <c r="J73" t="s">
+        <v>608</v>
+      </c>
+      <c r="K73" t="s">
+        <v>232</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
         <v>18</v>
       </c>
       <c r="N73" s="7">
         <v>39748</v>
       </c>
-      <c r="O73" s="7">
-        <v>44940</v>
-      </c>
+      <c r="O73" s="7"/>
       <c r="P73" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="C74" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D74" t="s" s="0">
         <v>54</v>
@@ -5574,45 +5442,43 @@
         <v>148</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>621</v>
-      </c>
-      <c r="J74" t="s" s="0">
-        <v>622</v>
-      </c>
-      <c r="K74" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L74" s="0">
+        <v>609</v>
+      </c>
+      <c r="J74" t="s">
+        <v>610</v>
+      </c>
+      <c r="K74" t="s">
+        <v>232</v>
+      </c>
+      <c r="L74">
         <v>25</v>
       </c>
-      <c r="M74" s="0">
+      <c r="M74">
         <v>109</v>
       </c>
       <c r="N74" s="7">
         <v>40427</v>
       </c>
-      <c r="O74" s="7">
-        <v>44941</v>
-      </c>
+      <c r="O74" s="7"/>
       <c r="P74" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="C75" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D75" t="s" s="0">
         <v>55</v>
@@ -5624,45 +5490,43 @@
         <v>149</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>623</v>
+        <v>457</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>624</v>
-      </c>
-      <c r="J75" t="s" s="0">
-        <v>625</v>
-      </c>
-      <c r="K75" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L75" s="0">
-        <v>0</v>
-      </c>
-      <c r="M75" s="0">
+        <v>611</v>
+      </c>
+      <c r="J75" t="s">
+        <v>612</v>
+      </c>
+      <c r="K75" t="s">
+        <v>232</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
         <v>12</v>
       </c>
       <c r="N75" s="7">
         <v>42543</v>
       </c>
-      <c r="O75" s="7">
-        <v>44942</v>
-      </c>
+      <c r="O75" s="7"/>
       <c r="P75" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C76" t="s" s="0">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D76" t="s" s="0">
         <v>56</v>
@@ -5674,39 +5538,43 @@
         <v>152</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>182</v>
+        <v>613</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="K76" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L76" s="0">
-        <v>0</v>
-      </c>
-      <c r="M76" s="0">
+        <v>263</v>
+      </c>
+      <c r="I76" t="s" s="0">
+        <v>614</v>
+      </c>
+      <c r="J76" t="s">
+        <v>615</v>
+      </c>
+      <c r="K76" t="s">
+        <v>232</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
         <v>174</v>
       </c>
       <c r="N76" s="7">
         <v>45341</v>
       </c>
-      <c r="O76" s="7">
-        <v>45674</v>
-      </c>
+      <c r="O76" s="7"/>
       <c r="P76" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C77" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D77" t="s" s="0">
         <v>57</v>
@@ -5718,28 +5586,32 @@
         <v>153</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>214</v>
+        <v>616</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="K77" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L77" s="0">
-        <v>0</v>
-      </c>
-      <c r="M77" s="0">
+        <v>468</v>
+      </c>
+      <c r="I77" t="s" s="0">
+        <v>617</v>
+      </c>
+      <c r="J77" t="s">
+        <v>618</v>
+      </c>
+      <c r="K77" t="s">
+        <v>232</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
         <v>112</v>
       </c>
       <c r="N77" s="7">
         <v>39295</v>
       </c>
-      <c r="O77" s="7">
-        <v>44944</v>
-      </c>
+      <c r="O77" s="7"/>
       <c r="P77" s="1" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
@@ -5750,13 +5622,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D79" t="s" s="0">
         <v>58</v>
@@ -5768,45 +5640,43 @@
         <v>154</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>627</v>
+        <v>458</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>628</v>
-      </c>
-      <c r="J79" t="s" s="0">
-        <v>629</v>
-      </c>
-      <c r="K79" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L79" s="0">
-        <v>0</v>
-      </c>
-      <c r="M79" s="0">
+        <v>619</v>
+      </c>
+      <c r="J79" t="s">
+        <v>620</v>
+      </c>
+      <c r="K79" t="s">
+        <v>232</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
         <v>121</v>
       </c>
       <c r="N79" s="7">
         <v>45483</v>
       </c>
-      <c r="O79" s="7">
-        <v>44562</v>
-      </c>
+      <c r="O79" s="7"/>
       <c r="P79" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D80" t="s" s="0">
         <v>59</v>
@@ -5818,45 +5688,43 @@
         <v>150</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>630</v>
+        <v>469</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>631</v>
-      </c>
-      <c r="J80" t="s" s="0">
-        <v>632</v>
-      </c>
-      <c r="K80" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L80" s="0">
+        <v>621</v>
+      </c>
+      <c r="J80" t="s">
+        <v>622</v>
+      </c>
+      <c r="K80" t="s">
+        <v>232</v>
+      </c>
+      <c r="L80">
         <v>25</v>
       </c>
-      <c r="M80" s="0">
+      <c r="M80">
         <v>146</v>
       </c>
       <c r="N80" s="7">
         <v>45484</v>
       </c>
-      <c r="O80" s="7">
-        <v>44563</v>
-      </c>
+      <c r="O80" s="7"/>
       <c r="P80" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="D81" t="s" s="0">
         <v>60</v>
@@ -5868,45 +5736,43 @@
         <v>93</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>633</v>
-      </c>
-      <c r="J81" t="s" s="0">
-        <v>634</v>
-      </c>
-      <c r="K81" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L81" s="0">
-        <v>0</v>
-      </c>
-      <c r="M81" s="0">
+        <v>623</v>
+      </c>
+      <c r="J81" t="s">
+        <v>624</v>
+      </c>
+      <c r="K81" t="s">
+        <v>232</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
         <v>139</v>
       </c>
       <c r="N81" s="7">
         <v>45485</v>
       </c>
-      <c r="O81" s="7">
-        <v>44564</v>
-      </c>
+      <c r="O81" s="7"/>
       <c r="P81" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="C82" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D82" t="s" s="0">
         <v>61</v>
@@ -5918,45 +5784,43 @@
         <v>107</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>635</v>
+        <v>470</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>636</v>
-      </c>
-      <c r="J82" t="s" s="0">
-        <v>637</v>
-      </c>
-      <c r="K82" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L82" s="0">
-        <v>0</v>
-      </c>
-      <c r="M82" s="0">
+        <v>625</v>
+      </c>
+      <c r="J82" t="s">
+        <v>626</v>
+      </c>
+      <c r="K82" t="s">
+        <v>232</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
         <v>6</v>
       </c>
       <c r="N82" s="7">
         <v>45486</v>
       </c>
-      <c r="O82" s="7">
-        <v>44565</v>
-      </c>
+      <c r="O82" s="7"/>
       <c r="P82" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C83" t="s" s="0">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="D83" t="s" s="0">
         <v>62</v>
@@ -5968,13 +5832,13 @@
         <v>151</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>638</v>
+        <v>459</v>
       </c>
       <c r="K83" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L83" s="0">
         <v>0</v>
@@ -5985,22 +5849,20 @@
       <c r="N83" s="7">
         <v>45487</v>
       </c>
-      <c r="O83" s="7">
-        <v>44566</v>
-      </c>
+      <c r="O83" s="7"/>
       <c r="P83" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="C84" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D84" t="s" s="0">
         <v>63</v>
@@ -6009,52 +5871,50 @@
         <v>85</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>639</v>
-      </c>
-      <c r="J84" t="s" s="0">
-        <v>640</v>
-      </c>
-      <c r="K84" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L84" s="0">
-        <v>0</v>
-      </c>
-      <c r="M84" s="0">
+        <v>627</v>
+      </c>
+      <c r="J84" t="s">
+        <v>628</v>
+      </c>
+      <c r="K84" t="s">
+        <v>232</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
         <v>123</v>
       </c>
       <c r="N84" s="7">
         <v>45488</v>
       </c>
-      <c r="O84" s="7">
-        <v>44567</v>
-      </c>
+      <c r="O84" s="7"/>
       <c r="P84" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="4"/>
       <c r="B85" s="6"/>
       <c r="G85" s="1"/>
       <c r="H85" s="3"/>
       <c r="O85" s="7"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C86" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D86" t="s" s="0">
         <v>64</v>
@@ -6066,45 +5926,43 @@
         <v>155</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>641</v>
-      </c>
-      <c r="J86" t="s" s="0">
-        <v>642</v>
-      </c>
-      <c r="K86" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L86" s="0">
+        <v>629</v>
+      </c>
+      <c r="J86" t="s">
+        <v>630</v>
+      </c>
+      <c r="K86" t="s">
+        <v>232</v>
+      </c>
+      <c r="L86">
         <v>25</v>
       </c>
-      <c r="M86" s="0">
+      <c r="M86">
         <v>170</v>
       </c>
       <c r="N86" s="7">
         <v>45490</v>
       </c>
-      <c r="O86" s="7">
-        <v>44569</v>
-      </c>
+      <c r="O86" s="7"/>
       <c r="P86" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C87" t="s" s="0">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="D87" t="s" s="0">
         <v>65</v>
@@ -6116,45 +5974,43 @@
         <v>156</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>643</v>
-      </c>
-      <c r="J87" t="s" s="0">
-        <v>644</v>
-      </c>
-      <c r="K87" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L87" s="0">
-        <v>0</v>
-      </c>
-      <c r="M87" s="0">
+        <v>631</v>
+      </c>
+      <c r="J87" t="s">
+        <v>632</v>
+      </c>
+      <c r="K87" t="s">
+        <v>232</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
         <v>171</v>
       </c>
       <c r="N87" s="7">
         <v>45491</v>
       </c>
-      <c r="O87" s="7">
-        <v>44570</v>
-      </c>
+      <c r="O87" s="7"/>
       <c r="P87" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C88" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D88" t="s" s="0">
         <v>66</v>
@@ -6166,45 +6022,43 @@
         <v>157</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>645</v>
+        <v>471</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>646</v>
-      </c>
-      <c r="J88" t="s" s="0">
-        <v>647</v>
-      </c>
-      <c r="K88" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L88" s="0">
-        <v>0</v>
-      </c>
-      <c r="M88" s="0">
+        <v>633</v>
+      </c>
+      <c r="J88" t="s">
+        <v>634</v>
+      </c>
+      <c r="K88" t="s">
+        <v>232</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
         <v>93</v>
       </c>
       <c r="N88" s="7">
         <v>45492</v>
       </c>
-      <c r="O88" s="7">
-        <v>44571</v>
-      </c>
+      <c r="O88" s="7"/>
       <c r="P88" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="C89" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D89" t="s" s="0">
         <v>67</v>
@@ -6216,45 +6070,43 @@
         <v>158</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>648</v>
+        <v>495</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>649</v>
-      </c>
-      <c r="J89" t="s" s="0">
-        <v>650</v>
-      </c>
-      <c r="K89" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L89" s="0">
-        <v>0</v>
-      </c>
-      <c r="M89" s="0">
+        <v>635</v>
+      </c>
+      <c r="J89" t="s">
+        <v>636</v>
+      </c>
+      <c r="K89" t="s">
+        <v>232</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
         <v>40</v>
       </c>
       <c r="N89" s="7">
         <v>45493</v>
       </c>
-      <c r="O89" s="7">
-        <v>44572</v>
-      </c>
+      <c r="O89" s="7"/>
       <c r="P89" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="C90" t="s" s="0">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D90" t="s" s="0">
         <v>50</v>
@@ -6263,13 +6115,13 @@
         <v>130</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="K90" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L90" s="0">
         <v>0</v>
@@ -6280,22 +6132,20 @@
       <c r="N90" s="7">
         <v>45494</v>
       </c>
-      <c r="O90" s="7">
-        <v>44573</v>
-      </c>
+      <c r="O90" s="7"/>
       <c r="P90" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="C91" t="s" s="0">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="D91" t="s" s="0">
         <v>68</v>
@@ -6307,45 +6157,43 @@
         <v>159</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>651</v>
-      </c>
-      <c r="J91" t="s" s="0">
-        <v>652</v>
-      </c>
-      <c r="K91" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L91" s="0">
-        <v>0</v>
-      </c>
-      <c r="M91" s="0">
+        <v>637</v>
+      </c>
+      <c r="J91" t="s">
+        <v>638</v>
+      </c>
+      <c r="K91" t="s">
+        <v>232</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
         <v>125</v>
       </c>
       <c r="N91" s="7">
         <v>45495</v>
       </c>
-      <c r="O91" s="7">
-        <v>44574</v>
-      </c>
+      <c r="O91" s="7"/>
       <c r="P91" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="C92" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D92" t="s" s="0">
         <v>69</v>
@@ -6357,45 +6205,44 @@
         <v>160</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>653</v>
+        <v>472</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>654</v>
-      </c>
-      <c r="J92" t="s" s="0">
-        <v>655</v>
-      </c>
-      <c r="K92" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L92" s="0">
-        <v>0</v>
-      </c>
-      <c r="M92" s="0">
+        <v>639</v>
+      </c>
+      <c r="J92" t="s">
+        <v>640</v>
+      </c>
+      <c r="K92" t="s">
+        <v>232</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
         <v>56</v>
       </c>
       <c r="N92" s="7">
-        <v>45496</v>
-      </c>
-      <c r="O92" s="7">
-        <v>44575</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="O92" s="7"/>
       <c r="P92" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+      <c r="R92" s="1"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="C93" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D93" t="s" s="0">
         <v>70</v>
@@ -6407,45 +6254,43 @@
         <v>161</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>656</v>
+        <v>496</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>657</v>
-      </c>
-      <c r="J93" t="s" s="0">
-        <v>658</v>
-      </c>
-      <c r="K93" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L93" s="0">
+        <v>641</v>
+      </c>
+      <c r="J93" t="s">
+        <v>642</v>
+      </c>
+      <c r="K93" t="s">
+        <v>232</v>
+      </c>
+      <c r="L93">
         <v>25</v>
       </c>
-      <c r="M93" s="0">
+      <c r="M93">
         <v>88</v>
       </c>
       <c r="N93" s="7">
         <v>45497</v>
       </c>
-      <c r="O93" s="7">
-        <v>44576</v>
-      </c>
+      <c r="O93" s="7"/>
       <c r="P93" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="C94" t="s" s="0">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="D94" t="s" s="0">
         <v>71</v>
@@ -6458,10 +6303,10 @@
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="3" t="s">
-        <v>659</v>
+        <v>473</v>
       </c>
       <c r="K94" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L94" s="0">
         <v>0</v>
@@ -6472,22 +6317,20 @@
       <c r="N94" s="7">
         <v>45498</v>
       </c>
-      <c r="O94" s="7">
-        <v>44577</v>
-      </c>
+      <c r="O94" s="7"/>
       <c r="P94" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="C95" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D95" t="s" s="0">
         <v>72</v>
@@ -6499,37 +6342,35 @@
         <v>83</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>660</v>
-      </c>
-      <c r="J95" t="s" s="0">
-        <v>661</v>
-      </c>
-      <c r="K95" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L95" s="0">
-        <v>0</v>
-      </c>
-      <c r="M95" s="0">
+        <v>643</v>
+      </c>
+      <c r="J95" t="s">
+        <v>644</v>
+      </c>
+      <c r="K95" t="s">
+        <v>232</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
         <v>31</v>
       </c>
       <c r="N95" s="7">
-        <v>45499</v>
-      </c>
-      <c r="O95" s="7">
-        <v>44578</v>
-      </c>
+        <v>46229</v>
+      </c>
+      <c r="O95" s="7"/>
       <c r="P95" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="4"/>
       <c r="B96" s="6"/>
       <c r="G96" s="1"/>
@@ -6573,13 +6414,13 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C102" t="s" s="0">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="D102" t="s" s="0">
         <v>54</v>
@@ -6591,45 +6432,43 @@
         <v>162</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>662</v>
+        <v>460</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>663</v>
-      </c>
-      <c r="J102" t="s" s="0">
-        <v>664</v>
-      </c>
-      <c r="K102" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L102" s="0">
-        <v>0</v>
-      </c>
-      <c r="M102" s="0">
+        <v>645</v>
+      </c>
+      <c r="J102" t="s">
+        <v>646</v>
+      </c>
+      <c r="K102" t="s">
+        <v>232</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
         <v>17</v>
       </c>
       <c r="N102" s="7">
         <v>45506</v>
       </c>
-      <c r="O102" s="7">
-        <v>44585</v>
-      </c>
+      <c r="O102" s="7"/>
       <c r="P102" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="C103" t="s" s="0">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D103" t="s" s="0">
         <v>55</v>
@@ -6641,45 +6480,43 @@
         <v>163</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>665</v>
-      </c>
-      <c r="J103" t="s" s="0">
-        <v>666</v>
-      </c>
-      <c r="K103" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L103" s="0">
+        <v>647</v>
+      </c>
+      <c r="J103" t="s">
+        <v>648</v>
+      </c>
+      <c r="K103" t="s">
+        <v>232</v>
+      </c>
+      <c r="L103">
         <v>25</v>
       </c>
-      <c r="M103" s="0">
+      <c r="M103">
         <v>52</v>
       </c>
       <c r="N103" s="7">
         <v>45507</v>
       </c>
-      <c r="O103" s="7">
-        <v>44586</v>
-      </c>
+      <c r="O103" s="7"/>
       <c r="P103" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C104" t="s" s="0">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="D104" t="s" s="0">
         <v>56</v>
@@ -6691,45 +6528,43 @@
         <v>164</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>667</v>
-      </c>
-      <c r="J104" t="s" s="0">
-        <v>668</v>
-      </c>
-      <c r="K104" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L104" s="0">
-        <v>0</v>
-      </c>
-      <c r="M104" s="0">
+        <v>649</v>
+      </c>
+      <c r="J104" t="s">
+        <v>650</v>
+      </c>
+      <c r="K104" t="s">
+        <v>232</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
         <v>135</v>
       </c>
       <c r="N104" s="7">
         <v>45508</v>
       </c>
-      <c r="O104" s="7">
-        <v>44587</v>
-      </c>
+      <c r="O104" s="7"/>
       <c r="P104" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C105" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D105" t="s" s="0">
         <v>57</v>
@@ -6741,13 +6576,13 @@
         <v>79</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="K105" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L105" s="0">
         <v>0</v>
@@ -6756,24 +6591,22 @@
         <v>6</v>
       </c>
       <c r="N105" s="7">
-        <v>45509</v>
-      </c>
-      <c r="O105" s="7">
-        <v>44588</v>
-      </c>
+        <v>46239</v>
+      </c>
+      <c r="O105" s="7"/>
       <c r="P105" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C106" t="s" s="0">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="D106" t="s" s="0">
         <v>11</v>
@@ -6785,34 +6618,32 @@
         <v>93</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>669</v>
+        <v>461</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>670</v>
-      </c>
-      <c r="J106" t="s" s="0">
-        <v>671</v>
-      </c>
-      <c r="K106" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L106" s="0">
+        <v>651</v>
+      </c>
+      <c r="J106" t="s">
+        <v>652</v>
+      </c>
+      <c r="K106" t="s">
+        <v>232</v>
+      </c>
+      <c r="L106">
         <v>25</v>
       </c>
-      <c r="M106" s="0">
+      <c r="M106">
         <v>127</v>
       </c>
       <c r="N106" s="7">
         <v>45510</v>
       </c>
-      <c r="O106" s="7">
-        <v>44589</v>
-      </c>
+      <c r="O106" s="7"/>
       <c r="P106" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
@@ -6957,13 +6788,13 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="C127" t="s" s="0">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="D127" t="s" s="0">
         <v>73</v>
@@ -6975,13 +6806,13 @@
         <v>165</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>286</v>
+        <v>497</v>
       </c>
       <c r="K127" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L127" s="0">
         <v>0</v>
@@ -6992,22 +6823,20 @@
       <c r="N127" s="7">
         <v>45531</v>
       </c>
-      <c r="O127" s="7">
-        <v>45706</v>
-      </c>
+      <c r="O127" s="7"/>
       <c r="P127" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="C128" t="s" s="0">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="D128" t="s" s="0">
         <v>74</v>
@@ -7019,45 +6848,43 @@
         <v>166</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="I128" t="s" s="0">
-        <v>672</v>
-      </c>
-      <c r="J128" t="s" s="0">
-        <v>673</v>
-      </c>
-      <c r="K128" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L128" s="0">
-        <v>0</v>
-      </c>
-      <c r="M128" s="0">
+        <v>653</v>
+      </c>
+      <c r="J128" t="s">
+        <v>654</v>
+      </c>
+      <c r="K128" t="s">
+        <v>232</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
         <v>195</v>
       </c>
       <c r="N128" s="7">
         <v>45532</v>
       </c>
-      <c r="O128" s="7">
-        <v>44611</v>
-      </c>
+      <c r="O128" s="7"/>
       <c r="P128" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="C129" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D129" t="s" s="0">
         <v>75</v>
@@ -7069,45 +6896,43 @@
         <v>167</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>674</v>
+        <v>499</v>
       </c>
       <c r="I129" t="s" s="0">
-        <v>675</v>
-      </c>
-      <c r="J129" t="s" s="0">
-        <v>676</v>
-      </c>
-      <c r="K129" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L129" s="0">
-        <v>0</v>
-      </c>
-      <c r="M129" s="0">
+        <v>655</v>
+      </c>
+      <c r="J129" t="s">
+        <v>656</v>
+      </c>
+      <c r="K129" t="s">
+        <v>232</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
         <v>117</v>
       </c>
       <c r="N129" s="7">
         <v>45533</v>
       </c>
-      <c r="O129" s="7">
-        <v>44612</v>
-      </c>
+      <c r="O129" s="7"/>
       <c r="P129" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C130" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D130" t="s" s="0">
         <v>66</v>
@@ -7119,13 +6944,13 @@
         <v>168</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>287</v>
+        <v>500</v>
       </c>
       <c r="K130" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L130" s="0">
         <v>25</v>
@@ -7136,22 +6961,20 @@
       <c r="N130" s="7">
         <v>45534</v>
       </c>
-      <c r="O130" s="7">
-        <v>44613</v>
-      </c>
+      <c r="O130" s="7"/>
       <c r="P130" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C131" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D131" t="s" s="0">
         <v>67</v>
@@ -7163,45 +6986,43 @@
         <v>169</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>288</v>
+        <v>501</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>677</v>
-      </c>
-      <c r="J131" t="s" s="0">
-        <v>678</v>
-      </c>
-      <c r="K131" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L131" s="0">
-        <v>0</v>
-      </c>
-      <c r="M131" s="0">
+        <v>657</v>
+      </c>
+      <c r="J131" t="s">
+        <v>658</v>
+      </c>
+      <c r="K131" t="s">
+        <v>232</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
         <v>54</v>
       </c>
       <c r="N131" s="7">
         <v>45535</v>
       </c>
-      <c r="O131" s="7">
-        <v>44614</v>
-      </c>
+      <c r="O131" s="7"/>
       <c r="P131" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="C132" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D132" t="s" s="0">
         <v>50</v>
@@ -7213,45 +7034,43 @@
         <v>170</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>289</v>
+        <v>502</v>
       </c>
       <c r="I132" t="s" s="0">
-        <v>679</v>
-      </c>
-      <c r="J132" t="s" s="0">
-        <v>680</v>
-      </c>
-      <c r="K132" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="L132" s="0">
-        <v>0</v>
-      </c>
-      <c r="M132" s="0">
+        <v>659</v>
+      </c>
+      <c r="J132" t="s">
+        <v>660</v>
+      </c>
+      <c r="K132" t="s">
+        <v>400</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
         <v>76</v>
       </c>
       <c r="N132" s="7">
         <v>45536</v>
       </c>
-      <c r="O132" s="7">
-        <v>44615</v>
-      </c>
+      <c r="O132" s="7"/>
       <c r="P132" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D133" t="s" s="0">
         <v>68</v>
@@ -7263,45 +7082,43 @@
         <v>162</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>290</v>
+        <v>503</v>
       </c>
       <c r="I133" t="s" s="0">
-        <v>681</v>
-      </c>
-      <c r="J133" t="s" s="0">
-        <v>682</v>
-      </c>
-      <c r="K133" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L133" s="0">
-        <v>0</v>
-      </c>
-      <c r="M133" s="0">
+        <v>661</v>
+      </c>
+      <c r="J133" t="s">
+        <v>662</v>
+      </c>
+      <c r="K133" t="s">
+        <v>232</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
         <v>67</v>
       </c>
       <c r="N133" s="7">
         <v>45537</v>
       </c>
-      <c r="O133" s="7">
-        <v>44616</v>
-      </c>
+      <c r="O133" s="7"/>
       <c r="P133" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="C134" t="s" s="0">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D134" t="s" s="0">
         <v>69</v>
@@ -7313,45 +7130,43 @@
         <v>163</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>291</v>
+        <v>504</v>
       </c>
       <c r="I134" t="s" s="0">
-        <v>683</v>
-      </c>
-      <c r="J134" t="s" s="0">
-        <v>684</v>
-      </c>
-      <c r="K134" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L134" s="0">
+        <v>663</v>
+      </c>
+      <c r="J134" t="s">
+        <v>664</v>
+      </c>
+      <c r="K134" t="s">
+        <v>232</v>
+      </c>
+      <c r="L134">
         <v>25</v>
       </c>
-      <c r="M134" s="0">
+      <c r="M134">
         <v>110</v>
       </c>
       <c r="N134" s="7">
         <v>45538</v>
       </c>
-      <c r="O134" s="7">
-        <v>44617</v>
-      </c>
+      <c r="O134" s="7"/>
       <c r="P134" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="C135" t="s" s="0">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="D135" t="s" s="0">
         <v>70</v>
@@ -7364,10 +7179,10 @@
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="3" t="s">
-        <v>685</v>
+        <v>505</v>
       </c>
       <c r="K135" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="L135" s="0">
         <v>0</v>
@@ -7378,22 +7193,20 @@
       <c r="N135" s="7">
         <v>45539</v>
       </c>
-      <c r="O135" s="7">
-        <v>44618</v>
-      </c>
+      <c r="O135" s="7"/>
       <c r="P135" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="C136" t="s" s="0">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="D136" t="s" s="0">
         <v>71</v>
@@ -7405,34 +7218,32 @@
         <v>79</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>686</v>
+        <v>506</v>
       </c>
       <c r="I136" t="s" s="0">
-        <v>687</v>
-      </c>
-      <c r="J136" t="s" s="0">
-        <v>688</v>
-      </c>
-      <c r="K136" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="L136" s="0">
-        <v>0</v>
-      </c>
-      <c r="M136" s="0">
+        <v>665</v>
+      </c>
+      <c r="J136" t="s">
+        <v>666</v>
+      </c>
+      <c r="K136" t="s">
+        <v>232</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
         <v>17</v>
       </c>
       <c r="N136" s="7">
         <v>45540</v>
       </c>
-      <c r="O136" s="7">
-        <v>44619</v>
-      </c>
+      <c r="O136" s="7"/>
       <c r="P136" s="1" t="s">
-        <v>424</v>
+        <v>475</v>
       </c>
     </row>
     <row r="137" spans="1:16" x14ac:dyDescent="0.25">
@@ -7517,72 +7328,66 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="H1" t="s" s="0">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="M1" t="s" s="0">
-        <v>398</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="0">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="K2" s="0">
-        <v>10</v>
-      </c>
-      <c r="L2" s="0">
-        <v>2</v>
+        <v>402</v>
+      </c>
+      <c r="H2" s="0">
+        <v>20</v>
       </c>
       <c r="M2" s="0">
         <v>0</v>
@@ -7593,22 +7398,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>241</v>
+        <v>382</v>
       </c>
       <c r="K3" s="0">
         <v>10</v>
@@ -7622,34 +7424,31 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="H4" s="0">
-        <v>20</v>
-      </c>
-      <c r="I4" s="0">
-        <v>0</v>
+        <v>382</v>
+      </c>
+      <c r="K4" s="0">
+        <v>10</v>
+      </c>
+      <c r="L4" s="0">
+        <v>2</v>
       </c>
       <c r="M4" s="0">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7657,28 +7456,28 @@
         <v>11</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C5" t="s" s="0">
+        <v>388</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>389</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>446</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>428</v>
-      </c>
       <c r="F5" t="s" s="0">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
+      </c>
+      <c r="H5" s="0">
+        <v>20</v>
       </c>
       <c r="I5" s="0">
-        <v>20</v>
-      </c>
-      <c r="J5" s="0">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="0">
         <v>21</v>
@@ -7689,28 +7488,28 @@
         <v>11</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="G6" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I6" s="0">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J6" s="0">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M6" s="0">
         <v>21</v>
@@ -7721,28 +7520,28 @@
         <v>11</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="G7" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I7" s="0">
         <v>50</v>
       </c>
       <c r="J7" s="0">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M7" s="0">
         <v>21</v>
@@ -7753,28 +7552,28 @@
         <v>11</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="G8" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I8" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J8" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="0">
         <v>21</v>
@@ -7785,28 +7584,28 @@
         <v>11</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="G9" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I9" s="0">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="J9" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M9" s="0">
         <v>21</v>
@@ -7814,92 +7613,92 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>456</v>
+        <v>421</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="K10" s="0">
-        <v>10</v>
-      </c>
-      <c r="L10" s="0">
-        <v>14</v>
+        <v>382</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I10" s="0">
+        <v>999</v>
+      </c>
+      <c r="J10" s="0">
+        <v>5</v>
       </c>
       <c r="M10" s="0">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>452</v>
+        <v>388</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>453</v>
+        <v>393</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="K11" s="0">
         <v>10</v>
       </c>
       <c r="L11" s="0">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M11" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="D12" t="s" s="0">
+        <v>429</v>
+      </c>
+      <c r="E12" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="E12" t="s" s="0">
-        <v>427</v>
-      </c>
       <c r="F12" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="G12" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="H12" s="0">
-        <v>50</v>
-      </c>
-      <c r="I12" s="0">
+        <v>402</v>
+      </c>
+      <c r="K12" s="0">
         <v>10</v>
       </c>
+      <c r="L12" s="0">
+        <v>25</v>
+      </c>
       <c r="M12" s="0">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -7907,28 +7706,28 @@
         <v>14</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>446</v>
+        <v>389</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="G13" t="s" s="0">
-        <v>419</v>
+        <v>400</v>
+      </c>
+      <c r="H13" s="0">
+        <v>50</v>
       </c>
       <c r="I13" s="0">
-        <v>30</v>
-      </c>
-      <c r="J13" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M13" s="0">
         <v>21</v>
@@ -7939,28 +7738,28 @@
         <v>14</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>447</v>
+        <v>422</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="G14" t="s" s="0">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="I14" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J14" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="0">
         <v>21</v>
@@ -7971,28 +7770,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>448</v>
+        <v>423</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="G15" t="s" s="0">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="I15" s="0">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J15" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M15" s="0">
         <v>21</v>
@@ -8003,28 +7802,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>449</v>
+        <v>424</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="G16" t="s" s="0">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="I16" s="0">
         <v>50</v>
       </c>
       <c r="J16" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M16" s="0">
         <v>21</v>
@@ -8035,28 +7834,28 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="G17" t="s" s="0">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="I17" s="0">
-        <v>9999</v>
+        <v>50</v>
       </c>
       <c r="J17" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M17" s="0">
         <v>21</v>
@@ -8064,28 +7863,34 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="0">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="F18" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="H18" s="0">
+        <v>402</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>400</v>
+      </c>
+      <c r="I18" s="0">
+        <v>9999</v>
+      </c>
+      <c r="J18" s="0">
         <v>20</v>
       </c>
       <c r="M18" s="0">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -8093,19 +7898,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="F19" t="s" s="0">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="K19" s="0">
         <v>10</v>
@@ -8122,22 +7927,22 @@
         <v>16</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="F20" t="s" s="0">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="G20" t="s" s="0">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="H20" s="0">
         <v>15</v>
@@ -8157,19 +7962,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="F21" t="s" s="0">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="H21" s="0">
         <v>30</v>
@@ -8183,19 +7988,19 @@
         <v>18</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="D22" t="s" s="0">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="E22" t="s" s="0">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="F22" t="s" s="0">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="H22" s="0">
         <v>15</v>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>
@@ -1576,12 +1576,24 @@
     <t>3162456104254692000A</t>
   </si>
   <si>
+    <t>31645124453461205100</t>
+  </si>
+  <si>
+    <t>65614874115615445600</t>
+  </si>
+  <si>
+    <t>32569523086220165100</t>
+  </si>
+  <si>
     <t>MC6436520125638451012515</t>
   </si>
   <si>
     <t>rgo00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>21584976912154655485</t>
+  </si>
+  <si>
     <t>ES9621584976912154655485</t>
   </si>
   <si>
@@ -1600,12 +1612,18 @@
     <t>abp00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>21564975263245467900</t>
+  </si>
+  <si>
     <t>LT2132566221532587754888</t>
   </si>
   <si>
     <t>acp00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>00750184350702510003</t>
+  </si>
+  <si>
     <t>74635623W</t>
   </si>
   <si>
@@ -1627,6 +1645,9 @@
     <t>83647564Z</t>
   </si>
   <si>
+    <t>25030000194574745400</t>
+  </si>
+  <si>
     <t>AT7125030000194574745400</t>
   </si>
   <si>
@@ -1645,6 +1666,9 @@
     <t>92736981S</t>
   </si>
   <si>
+    <t>20960043033096200013</t>
+  </si>
+  <si>
     <t>ES6520960043033096200013</t>
   </si>
   <si>
@@ -1669,6 +1693,9 @@
     <t>pp00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>12669681125112121200</t>
+  </si>
+  <si>
     <t>DE6912669681125112121200</t>
   </si>
   <si>
@@ -1687,6 +1714,9 @@
     <t>cgm00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>64578946720051516403</t>
+  </si>
+  <si>
     <t>ES4534698752714600549403</t>
   </si>
   <si>
@@ -1696,6 +1726,9 @@
     <t>25147854E</t>
   </si>
   <si>
+    <t>23185484415641685908</t>
+  </si>
+  <si>
     <t>FR8423185484415641685908</t>
   </si>
   <si>
@@ -1735,6 +1768,9 @@
     <t>dlr00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>75647586157564758698</t>
+  </si>
+  <si>
     <t>FI6775647586157564758698</t>
   </si>
   <si>
@@ -1783,24 +1819,39 @@
     <t>iag00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>25635478301002541233</t>
+  </si>
+  <si>
     <t>SM7825635478301002541233</t>
   </si>
   <si>
     <t>gpg00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>32154697155423121012</t>
+  </si>
+  <si>
     <t>ES8932154697155423121012</t>
   </si>
   <si>
     <t>rgg00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>20008521588775113327</t>
+  </si>
+  <si>
     <t>GB5720008521588775113327</t>
   </si>
   <si>
     <t>afg00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>20960043073000100018</t>
+  </si>
+  <si>
+    <t>12548523445214585218</t>
+  </si>
+  <si>
     <t>ES0912548523445214585218</t>
   </si>
   <si>
@@ -1819,6 +1870,9 @@
     <t>lr00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>20960031482124800018</t>
+  </si>
+  <si>
     <t>ES2420960031482124800018</t>
   </si>
   <si>
@@ -1843,12 +1897,18 @@
     <t>rog00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>20960043023000100021</t>
+  </si>
+  <si>
     <t>ES6020960043023000100021</t>
   </si>
   <si>
     <t>sog00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>65168874681561561522</t>
+  </si>
+  <si>
     <t>ES2965168874681561561522</t>
   </si>
   <si>
@@ -1861,6 +1921,9 @@
     <t>mbg00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>21416325801510005527</t>
+  </si>
+  <si>
     <t>ES7421416325801510005527</t>
   </si>
   <si>
@@ -1879,18 +1942,27 @@
     <t>12345679S</t>
   </si>
   <si>
+    <t>20960056143231500032</t>
+  </si>
+  <si>
     <t>ES6620960056143231500032</t>
   </si>
   <si>
     <t>fdl00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>63516541858944000993</t>
+  </si>
+  <si>
     <t>ES4063516541858944000993</t>
   </si>
   <si>
     <t>sdm00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>23658965294585223213</t>
+  </si>
+  <si>
     <t>ES2923658965294585223213</t>
   </si>
   <si>
@@ -1903,12 +1975,18 @@
     <t>gpm00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>23652365132254222021</t>
+  </si>
+  <si>
     <t>ES5223652365132254222021</t>
   </si>
   <si>
     <t>eam00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>20012541120023365296</t>
+  </si>
+  <si>
     <t>ES9232584216971684051000</t>
   </si>
   <si>
@@ -1927,12 +2005,18 @@
     <t>bdc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>36245978123245679018</t>
+  </si>
+  <si>
     <t>ES4836245978123245679018</t>
   </si>
   <si>
     <t>ngc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87635467511625345671</t>
+  </si>
+  <si>
     <t>ES2987635467511625345671</t>
   </si>
   <si>
@@ -1945,24 +2029,36 @@
     <t>mlc01@tasabasura2026.com</t>
   </si>
   <si>
+    <t>20960043093468900021</t>
+  </si>
+  <si>
     <t>ES4820960043093468900021</t>
   </si>
   <si>
     <t>cfc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>84729478014857627845</t>
+  </si>
+  <si>
     <t>ES7884729478014857627845</t>
   </si>
   <si>
     <t>cgc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>85550564796165145618</t>
+  </si>
+  <si>
     <t>ES1665165654918886005001</t>
   </si>
   <si>
     <t>ksc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>65645150815168448846</t>
+  </si>
+  <si>
     <t>AT9465645150815168448846</t>
   </si>
   <si>
@@ -1981,46 +2077,79 @@
     <t>mfd00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>51556584261251000242</t>
+  </si>
+  <si>
     <t>IE4751556584261251000242</t>
   </si>
   <si>
     <t>gmm02@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87457619137384957654</t>
+  </si>
+  <si>
+    <t>87457619164384957654</t>
+  </si>
+  <si>
     <t>LT1687457619164384957654</t>
   </si>
   <si>
     <t>dmc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87457619177384957657</t>
+  </si>
+  <si>
     <t>ES9587457619177384957657</t>
   </si>
   <si>
     <t>ebc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87457619117384957658</t>
+  </si>
+  <si>
+    <t>87457619167384957659</t>
+  </si>
+  <si>
     <t>ES0687457619167384957659</t>
   </si>
   <si>
     <t>msc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87457619117384957651</t>
+  </si>
+  <si>
     <t>ES4787457619117384957651</t>
   </si>
   <si>
     <t>mdc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87457619197384957653</t>
+  </si>
+  <si>
     <t>ES7987457619197384957653</t>
   </si>
   <si>
     <t>mfc00@tasabasura2026.com</t>
   </si>
   <si>
+    <t>87457619187384957617</t>
+  </si>
+  <si>
     <t>ES4687457619187384957617</t>
   </si>
   <si>
     <t>cdd00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619177384957619</t>
+  </si>
+  <si>
+    <t>87457619187384957621</t>
   </si>
   <si>
     <t>AT6887457619187384957621</t>
@@ -2485,7 +2614,7 @@
         <v>476</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>444</v>
+        <v>516</v>
       </c>
       <c r="K2" t="s" s="0">
         <v>232</v>
@@ -2529,7 +2658,7 @@
         <v>477</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>445</v>
+        <v>517</v>
       </c>
       <c r="K3" t="s" s="0">
         <v>232</v>
@@ -2571,7 +2700,7 @@
         <v>478</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>446</v>
+        <v>518</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>232</v>
@@ -2662,10 +2791,10 @@
         <v>235</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J6" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="K6" t="s">
         <v>232</v>
@@ -2709,13 +2838,13 @@
         <v>438</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="I7" t="s" s="0">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="J7" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K7" t="s">
         <v>232</v>
@@ -2762,10 +2891,10 @@
         <v>236</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="J8" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="K8" t="s">
         <v>232</v>
@@ -2856,10 +2985,10 @@
         <v>238</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="J10" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K10" t="s">
         <v>232</v>
@@ -2903,7 +3032,7 @@
         <v>481</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>447</v>
+        <v>528</v>
       </c>
       <c r="K11" t="s" s="0">
         <v>232</v>
@@ -2950,10 +3079,10 @@
         <v>411</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="J12" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="K12" t="s">
         <v>232</v>
@@ -3039,7 +3168,7 @@
         <v>410</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="K14" t="s" s="0">
         <v>232</v>
@@ -3084,16 +3213,16 @@
         <v>141</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>412</v>
       </c>
       <c r="I16" t="s" s="0">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="J16" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="K16" t="s">
         <v>232</v>
@@ -3132,16 +3261,16 @@
         <v>141</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>413</v>
       </c>
       <c r="I17" t="s" s="0">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J17" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="K17" t="s">
         <v>232</v>
@@ -3180,16 +3309,16 @@
         <v>142</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>448</v>
+        <v>539</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="J18" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="K18" t="s">
         <v>232</v>
@@ -3228,16 +3357,16 @@
         <v>142</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>414</v>
       </c>
       <c r="I19" t="s" s="0">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="J19" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="K19" t="s">
         <v>232</v>
@@ -3276,16 +3405,16 @@
         <v>143</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="I20" t="s" s="0">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="J20" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="K20" t="s">
         <v>232</v>
@@ -3369,10 +3498,10 @@
         <v>416</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="J22" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="K22" t="s">
         <v>232</v>
@@ -3411,13 +3540,13 @@
         <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>449</v>
+        <v>239</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="J23" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="K23" t="s">
         <v>232</v>
@@ -3459,10 +3588,10 @@
         <v>417</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="J24" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="K24" t="s">
         <v>232</v>
@@ -3501,13 +3630,13 @@
         <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>450</v>
+        <v>555</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="J25" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="K25" t="s">
         <v>232</v>
@@ -3558,10 +3687,10 @@
         <v>240</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="J27" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="K27" t="s">
         <v>232</v>
@@ -3606,10 +3735,10 @@
         <v>241</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="J28" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="K28" t="s">
         <v>232</v>
@@ -3651,7 +3780,7 @@
         <v>488</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>510</v>
+        <v>562</v>
       </c>
       <c r="K29" t="s" s="0">
         <v>232</v>
@@ -3696,10 +3825,10 @@
         <v>242</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="J30" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="K30" t="s">
         <v>232</v>
@@ -3780,16 +3909,16 @@
         <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>451</v>
+        <v>566</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="J32" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="K32" t="s">
         <v>232</v>
@@ -3855,10 +3984,10 @@
         <v>243</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="J36" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="K36" t="s">
         <v>232</v>
@@ -3903,10 +4032,10 @@
         <v>244</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="J37" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="K37" t="s">
         <v>232</v>
@@ -3945,16 +4074,16 @@
         <v>109</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>245</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="J38" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="K38" t="s">
         <v>232</v>
@@ -4041,10 +4170,10 @@
         <v>246</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="J40" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="K40" t="s">
         <v>232</v>
@@ -4089,10 +4218,10 @@
         <v>247</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="J41" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="K41" t="s">
         <v>232</v>
@@ -4134,13 +4263,13 @@
         <v>442</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>511</v>
+        <v>580</v>
       </c>
       <c r="I42" t="s" s="0">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="J42" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="K42" t="s">
         <v>232</v>
@@ -4185,10 +4314,10 @@
         <v>248</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="J43" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="K43" t="s">
         <v>232</v>
@@ -4227,7 +4356,7 @@
         <v>142</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>249</v>
@@ -4275,10 +4404,10 @@
         <v>250</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="J45" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="K45" t="s">
         <v>232</v>
@@ -4323,10 +4452,10 @@
         <v>453</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="J46" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="K46" t="s">
         <v>232</v>
@@ -4368,13 +4497,13 @@
         <v>186</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>511</v>
+        <v>580</v>
       </c>
       <c r="I47" t="s" s="0">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="J47" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="K47" t="s">
         <v>232</v>
@@ -4419,10 +4548,10 @@
         <v>239</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="J48" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="K48" t="s">
         <v>232</v>
@@ -4467,10 +4596,10 @@
         <v>251</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="J49" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="K49" t="s">
         <v>232</v>
@@ -4509,7 +4638,7 @@
         <v>146</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>252</v>
@@ -4557,10 +4686,10 @@
         <v>253</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="J51" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="K51" t="s">
         <v>232</v>
@@ -4602,13 +4731,13 @@
         <v>190</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>454</v>
+        <v>597</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="J52" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="K52" t="s">
         <v>232</v>
@@ -4650,13 +4779,13 @@
         <v>191</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>462</v>
+        <v>600</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="J53" t="s">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="K53" t="s">
         <v>232</v>
@@ -4740,13 +4869,13 @@
         <v>193</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>455</v>
+        <v>603</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="J55" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="K55" t="s">
         <v>232</v>
@@ -4812,7 +4941,7 @@
         <v>491</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>463</v>
+        <v>606</v>
       </c>
       <c r="K60" t="s" s="0">
         <v>232</v>
@@ -4896,13 +5025,13 @@
         <v>194</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>464</v>
+        <v>607</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="J62" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="K62" t="s">
         <v>232</v>
@@ -4986,10 +5115,10 @@
         <v>256</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>593</v>
+        <v>610</v>
       </c>
       <c r="J64" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="K64" t="s">
         <v>232</v>
@@ -5031,10 +5160,10 @@
         <v>257</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="J65" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="K65" t="s">
         <v>232</v>
@@ -5073,13 +5202,13 @@
         <v>198</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>465</v>
+        <v>614</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="J66" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="K66" t="s">
         <v>232</v>
@@ -5166,10 +5295,10 @@
         <v>259</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="J68" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="K68" t="s">
         <v>232</v>
@@ -5214,10 +5343,10 @@
         <v>260</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="J69" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="K69" t="s">
         <v>232</v>
@@ -5262,10 +5391,10 @@
         <v>456</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="J70" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="K70" t="s">
         <v>232</v>
@@ -5307,13 +5436,13 @@
         <v>202</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>466</v>
+        <v>623</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>605</v>
+        <v>624</v>
       </c>
       <c r="J71" t="s">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="K71" t="s">
         <v>232</v>
@@ -5397,13 +5526,13 @@
         <v>203</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>467</v>
+        <v>626</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="J73" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="K73" t="s">
         <v>232</v>
@@ -5448,10 +5577,10 @@
         <v>262</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="J74" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="K74" t="s">
         <v>232</v>
@@ -5493,13 +5622,13 @@
         <v>205</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>457</v>
+        <v>631</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="J75" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="K75" t="s">
         <v>232</v>
@@ -5538,16 +5667,16 @@
         <v>152</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>263</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="J76" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="K76" t="s">
         <v>232</v>
@@ -5586,16 +5715,16 @@
         <v>153</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>468</v>
+        <v>638</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>617</v>
+        <v>639</v>
       </c>
       <c r="J77" t="s">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="K77" t="s">
         <v>232</v>
@@ -5643,13 +5772,13 @@
         <v>206</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>458</v>
+        <v>641</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="J79" t="s">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="K79" t="s">
         <v>232</v>
@@ -5691,13 +5820,13 @@
         <v>207</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>469</v>
+        <v>644</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="J80" t="s">
-        <v>622</v>
+        <v>646</v>
       </c>
       <c r="K80" t="s">
         <v>232</v>
@@ -5742,10 +5871,10 @@
         <v>264</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>623</v>
+        <v>647</v>
       </c>
       <c r="J81" t="s">
-        <v>624</v>
+        <v>648</v>
       </c>
       <c r="K81" t="s">
         <v>232</v>
@@ -5787,13 +5916,13 @@
         <v>209</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>470</v>
+        <v>649</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="J82" t="s">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="K82" t="s">
         <v>232</v>
@@ -5835,7 +5964,7 @@
         <v>210</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>459</v>
+        <v>652</v>
       </c>
       <c r="K83" t="s" s="0">
         <v>232</v>
@@ -5877,10 +6006,10 @@
         <v>265</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>627</v>
+        <v>653</v>
       </c>
       <c r="J84" t="s">
-        <v>628</v>
+        <v>654</v>
       </c>
       <c r="K84" t="s">
         <v>232</v>
@@ -5932,10 +6061,10 @@
         <v>266</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="J86" t="s">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="K86" t="s">
         <v>232</v>
@@ -5980,10 +6109,10 @@
         <v>267</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="J87" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="K87" t="s">
         <v>232</v>
@@ -6025,13 +6154,13 @@
         <v>214</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>471</v>
+        <v>659</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="J88" t="s">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="K88" t="s">
         <v>232</v>
@@ -6073,13 +6202,13 @@
         <v>215</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>495</v>
+        <v>662</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="J89" t="s">
-        <v>636</v>
+        <v>664</v>
       </c>
       <c r="K89" t="s">
         <v>232</v>
@@ -6163,10 +6292,10 @@
         <v>269</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="J91" t="s">
-        <v>638</v>
+        <v>666</v>
       </c>
       <c r="K91" t="s">
         <v>232</v>
@@ -6208,13 +6337,13 @@
         <v>217</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>472</v>
+        <v>667</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>639</v>
+        <v>668</v>
       </c>
       <c r="J92" t="s">
-        <v>640</v>
+        <v>669</v>
       </c>
       <c r="K92" t="s">
         <v>232</v>
@@ -6257,13 +6386,13 @@
         <v>218</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>496</v>
+        <v>670</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="J93" t="s">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="K93" t="s">
         <v>232</v>
@@ -6303,7 +6432,7 @@
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="3" t="s">
-        <v>473</v>
+        <v>673</v>
       </c>
       <c r="K94" t="s" s="0">
         <v>232</v>
@@ -6348,10 +6477,10 @@
         <v>270</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="J95" t="s">
-        <v>644</v>
+        <v>675</v>
       </c>
       <c r="K95" t="s">
         <v>232</v>
@@ -6435,13 +6564,13 @@
         <v>220</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>460</v>
+        <v>676</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>645</v>
+        <v>677</v>
       </c>
       <c r="J102" t="s">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="K102" t="s">
         <v>232</v>
@@ -6486,10 +6615,10 @@
         <v>443</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>647</v>
+        <v>679</v>
       </c>
       <c r="J103" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="K103" t="s">
         <v>232</v>
@@ -6534,10 +6663,10 @@
         <v>271</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="J104" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="K104" t="s">
         <v>232</v>
@@ -6621,13 +6750,13 @@
         <v>224</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>461</v>
+        <v>683</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>651</v>
+        <v>684</v>
       </c>
       <c r="J106" t="s">
-        <v>652</v>
+        <v>685</v>
       </c>
       <c r="K106" t="s">
         <v>232</v>
@@ -6809,7 +6938,7 @@
         <v>218</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>497</v>
+        <v>686</v>
       </c>
       <c r="K127" t="s" s="0">
         <v>232</v>
@@ -6851,13 +6980,13 @@
         <v>225</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>498</v>
+        <v>687</v>
       </c>
       <c r="I128" t="s" s="0">
-        <v>653</v>
+        <v>688</v>
       </c>
       <c r="J128" t="s">
-        <v>654</v>
+        <v>689</v>
       </c>
       <c r="K128" t="s">
         <v>232</v>
@@ -6899,13 +7028,13 @@
         <v>226</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>499</v>
+        <v>690</v>
       </c>
       <c r="I129" t="s" s="0">
-        <v>655</v>
+        <v>691</v>
       </c>
       <c r="J129" t="s">
-        <v>656</v>
+        <v>692</v>
       </c>
       <c r="K129" t="s">
         <v>232</v>
@@ -6947,7 +7076,7 @@
         <v>226</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>500</v>
+        <v>693</v>
       </c>
       <c r="K130" t="s" s="0">
         <v>232</v>
@@ -6989,13 +7118,13 @@
         <v>227</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>501</v>
+        <v>694</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>657</v>
+        <v>695</v>
       </c>
       <c r="J131" t="s">
-        <v>658</v>
+        <v>696</v>
       </c>
       <c r="K131" t="s">
         <v>232</v>
@@ -7037,13 +7166,13 @@
         <v>228</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>502</v>
+        <v>697</v>
       </c>
       <c r="I132" t="s" s="0">
-        <v>659</v>
+        <v>698</v>
       </c>
       <c r="J132" t="s">
-        <v>660</v>
+        <v>699</v>
       </c>
       <c r="K132" t="s">
         <v>400</v>
@@ -7085,13 +7214,13 @@
         <v>229</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>503</v>
+        <v>700</v>
       </c>
       <c r="I133" t="s" s="0">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="J133" t="s">
-        <v>662</v>
+        <v>702</v>
       </c>
       <c r="K133" t="s">
         <v>232</v>
@@ -7133,13 +7262,13 @@
         <v>230</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>504</v>
+        <v>703</v>
       </c>
       <c r="I134" t="s" s="0">
-        <v>663</v>
+        <v>704</v>
       </c>
       <c r="J134" t="s">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="K134" t="s">
         <v>232</v>
@@ -7179,7 +7308,7 @@
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="3" t="s">
-        <v>505</v>
+        <v>706</v>
       </c>
       <c r="K135" t="s" s="0">
         <v>232</v>
@@ -7221,13 +7350,13 @@
         <v>231</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>506</v>
+        <v>707</v>
       </c>
       <c r="I136" t="s" s="0">
-        <v>665</v>
+        <v>708</v>
       </c>
       <c r="J136" t="s">
-        <v>666</v>
+        <v>709</v>
       </c>
       <c r="K136" t="s">
         <v>232</v>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="1439">
   <si>
     <t>Nombre</t>
   </si>
@@ -4813,16 +4813,16 @@
       <c r="I2" t="s" s="0">
         <v>773</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>774</v>
       </c>
-      <c r="K2" t="s">
-        <v>243</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+      <c r="K2" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L2" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0">
         <v>80</v>
       </c>
       <c r="N2" s="6">
@@ -4863,16 +4863,16 @@
       <c r="I3" t="s" s="0">
         <v>776</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>777</v>
       </c>
-      <c r="K3" t="s">
-        <v>243</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
+      <c r="K3" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L3" s="0">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0">
         <v>10</v>
       </c>
       <c r="N3" s="6">
@@ -4957,16 +4957,16 @@
       <c r="I5" t="s" s="0">
         <v>780</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="0">
         <v>781</v>
       </c>
-      <c r="K5" t="s">
-        <v>243</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="K5" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L5" s="0">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0">
         <v>950</v>
       </c>
       <c r="N5" s="6">
@@ -5007,16 +5007,16 @@
       <c r="I6" t="s" s="0">
         <v>783</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" t="s" s="0">
         <v>784</v>
       </c>
-      <c r="K6" t="s">
-        <v>243</v>
-      </c>
-      <c r="L6">
+      <c r="K6" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L6" s="0">
         <v>25</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="0">
         <v>150</v>
       </c>
       <c r="N6" s="6">
@@ -5057,16 +5057,16 @@
       <c r="I7" t="s" s="0">
         <v>786</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" t="s" s="0">
         <v>787</v>
       </c>
-      <c r="K7" t="s">
-        <v>243</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
+      <c r="K7" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0">
         <v>50</v>
       </c>
       <c r="N7" s="6">
@@ -5107,16 +5107,16 @@
       <c r="I8" t="s" s="0">
         <v>790</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" t="s" s="0">
         <v>791</v>
       </c>
-      <c r="K8" t="s">
-        <v>243</v>
-      </c>
-      <c r="L8">
+      <c r="K8" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L8" s="0">
         <v>25</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="0">
         <v>51</v>
       </c>
       <c r="N8" s="6">
@@ -5201,16 +5201,16 @@
       <c r="I10" t="s" s="0">
         <v>795</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" t="s" s="0">
         <v>796</v>
       </c>
-      <c r="K10" t="s">
-        <v>243</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
+      <c r="K10" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L10" s="0">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0">
         <v>43</v>
       </c>
       <c r="N10" s="6">
@@ -5295,16 +5295,16 @@
       <c r="I12" t="s" s="0">
         <v>800</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" t="s" s="0">
         <v>801</v>
       </c>
-      <c r="K12" t="s">
-        <v>243</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
+      <c r="K12" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L12" s="0">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0">
         <v>0</v>
       </c>
       <c r="N12" s="6">
@@ -5662,16 +5662,16 @@
       <c r="I21" t="s" s="0">
         <v>808</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" t="s" s="0">
         <v>809</v>
       </c>
-      <c r="K21" t="s">
-        <v>243</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
+      <c r="K21" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L21" s="0">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0">
         <v>122</v>
       </c>
       <c r="N21" s="6">
@@ -5709,16 +5709,16 @@
       <c r="I22" t="s" s="0">
         <v>811</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" t="s" s="0">
         <v>812</v>
       </c>
-      <c r="K22" t="s">
-        <v>243</v>
-      </c>
-      <c r="L22">
+      <c r="K22" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L22" s="0">
         <v>25</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="0">
         <v>74</v>
       </c>
       <c r="N22" s="6">
@@ -5797,16 +5797,16 @@
       <c r="I24" t="s" s="0">
         <v>814</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" t="s" s="0">
         <v>815</v>
       </c>
-      <c r="K24" t="s">
-        <v>243</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
+      <c r="K24" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L24" s="0">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0">
         <v>177</v>
       </c>
       <c r="N24" s="6">
@@ -5844,16 +5844,16 @@
       <c r="I25" t="s" s="0">
         <v>817</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" t="s" s="0">
         <v>818</v>
       </c>
-      <c r="K25" t="s">
-        <v>243</v>
-      </c>
-      <c r="L25">
+      <c r="K25" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L25" s="0">
         <v>25</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="0">
         <v>42</v>
       </c>
       <c r="N25" s="6">
@@ -5903,16 +5903,16 @@
       <c r="I27" t="s" s="0">
         <v>820</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" t="s" s="0">
         <v>821</v>
       </c>
-      <c r="K27" t="s">
-        <v>243</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
+      <c r="K27" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0</v>
+      </c>
+      <c r="M27" s="0">
         <v>88</v>
       </c>
       <c r="N27" s="6">
@@ -5953,16 +5953,16 @@
       <c r="I28" t="s" s="0">
         <v>823</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" t="s" s="0">
         <v>824</v>
       </c>
-      <c r="K28" t="s">
-        <v>243</v>
-      </c>
-      <c r="L28">
+      <c r="K28" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L28" s="0">
         <v>25</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="0">
         <v>101</v>
       </c>
       <c r="N28" s="6">
@@ -6003,16 +6003,16 @@
       <c r="I29" t="s" s="0">
         <v>826</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" t="s" s="0">
         <v>827</v>
       </c>
-      <c r="K29" t="s">
-        <v>243</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
+      <c r="K29" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L29" s="0">
+        <v>0</v>
+      </c>
+      <c r="M29" s="0">
         <v>10</v>
       </c>
       <c r="N29" s="6">
@@ -6053,16 +6053,16 @@
       <c r="I30" t="s" s="0">
         <v>828</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" t="s" s="0">
         <v>829</v>
       </c>
-      <c r="K30" t="s">
-        <v>243</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
+      <c r="K30" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L30" s="0">
+        <v>0</v>
+      </c>
+      <c r="M30" s="0">
         <v>78</v>
       </c>
       <c r="N30" s="6">
@@ -6103,16 +6103,16 @@
       <c r="I31" t="s" s="0">
         <v>831</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" t="s" s="0">
         <v>832</v>
       </c>
-      <c r="K31" t="s">
-        <v>243</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
+      <c r="K31" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L31" s="0">
+        <v>0</v>
+      </c>
+      <c r="M31" s="0">
         <v>71</v>
       </c>
       <c r="N31" s="6">
@@ -6153,16 +6153,16 @@
       <c r="I32" t="s" s="0">
         <v>834</v>
       </c>
-      <c r="J32" t="s">
+      <c r="J32" t="s" s="0">
         <v>835</v>
       </c>
-      <c r="K32" t="s">
-        <v>243</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
+      <c r="K32" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L32" s="0">
+        <v>0</v>
+      </c>
+      <c r="M32" s="0">
         <v>113</v>
       </c>
       <c r="N32" s="6">
@@ -6230,16 +6230,16 @@
       <c r="I36" t="s" s="0">
         <v>838</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" t="s" s="0">
         <v>839</v>
       </c>
-      <c r="K36" t="s">
-        <v>243</v>
-      </c>
-      <c r="L36">
+      <c r="K36" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L36" s="0">
         <v>25</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="0">
         <v>10</v>
       </c>
       <c r="N36" s="6">
@@ -6278,16 +6278,16 @@
       <c r="I37" t="s" s="0">
         <v>842</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" t="s" s="0">
         <v>843</v>
       </c>
-      <c r="K37" t="s">
-        <v>243</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
+      <c r="K37" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0</v>
+      </c>
+      <c r="M37" s="0">
         <v>50</v>
       </c>
       <c r="N37" s="6">
@@ -6368,16 +6368,16 @@
       <c r="I39" t="s" s="0">
         <v>847</v>
       </c>
-      <c r="J39" t="s">
+      <c r="J39" t="s" s="0">
         <v>848</v>
       </c>
-      <c r="K39" t="s">
-        <v>243</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
+      <c r="K39" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0</v>
+      </c>
+      <c r="M39" s="0">
         <v>500</v>
       </c>
       <c r="N39" s="6">
@@ -6416,16 +6416,16 @@
       <c r="I40" t="s" s="0">
         <v>851</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" t="s" s="0">
         <v>852</v>
       </c>
-      <c r="K40" t="s">
-        <v>243</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
+      <c r="K40" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0</v>
+      </c>
+      <c r="M40" s="0">
         <v>120</v>
       </c>
       <c r="N40" s="6">
@@ -6464,16 +6464,16 @@
       <c r="I41" t="s" s="0">
         <v>855</v>
       </c>
-      <c r="J41" t="s">
+      <c r="J41" t="s" s="0">
         <v>856</v>
       </c>
-      <c r="K41" t="s">
-        <v>243</v>
-      </c>
-      <c r="L41">
+      <c r="K41" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L41" s="0">
         <v>50</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="0">
         <v>30</v>
       </c>
       <c r="N41" s="6">
@@ -6512,16 +6512,16 @@
       <c r="I42" t="s" s="0">
         <v>859</v>
       </c>
-      <c r="J42" t="s">
+      <c r="J42" t="s" s="0">
         <v>860</v>
       </c>
-      <c r="K42" t="s">
-        <v>243</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
+      <c r="K42" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L42" s="0">
+        <v>0</v>
+      </c>
+      <c r="M42" s="0">
         <v>118</v>
       </c>
       <c r="N42" s="6">
@@ -6560,16 +6560,16 @@
       <c r="I43" t="s" s="0">
         <v>862</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" t="s" s="0">
         <v>863</v>
       </c>
-      <c r="K43" t="s">
-        <v>243</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
+      <c r="K43" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L43" s="0">
+        <v>0</v>
+      </c>
+      <c r="M43" s="0">
         <v>154</v>
       </c>
       <c r="N43" s="6">
@@ -6608,16 +6608,16 @@
       <c r="I44" t="s" s="0">
         <v>865</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J44" t="s" s="0">
         <v>866</v>
       </c>
-      <c r="K44" t="s">
-        <v>243</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
+      <c r="K44" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L44" s="0">
+        <v>0</v>
+      </c>
+      <c r="M44" s="0">
         <v>57</v>
       </c>
       <c r="N44" s="6">
@@ -6656,16 +6656,16 @@
       <c r="I45" t="s" s="0">
         <v>868</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" t="s" s="0">
         <v>869</v>
       </c>
-      <c r="K45" t="s">
-        <v>243</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
+      <c r="K45" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L45" s="0">
+        <v>0</v>
+      </c>
+      <c r="M45" s="0">
         <v>99</v>
       </c>
       <c r="N45" s="6">
@@ -6704,16 +6704,16 @@
       <c r="I46" t="s" s="0">
         <v>871</v>
       </c>
-      <c r="J46" t="s">
+      <c r="J46" t="s" s="0">
         <v>872</v>
       </c>
-      <c r="K46" t="s">
-        <v>243</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
+      <c r="K46" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L46" s="0">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0">
         <v>65</v>
       </c>
       <c r="N46" s="6">
@@ -6752,16 +6752,16 @@
       <c r="I47" t="s" s="0">
         <v>874</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" t="s" s="0">
         <v>875</v>
       </c>
-      <c r="K47" t="s">
-        <v>243</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
+      <c r="K47" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L47" s="0">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0">
         <v>94</v>
       </c>
       <c r="N47" s="6">
@@ -6800,16 +6800,16 @@
       <c r="I48" t="s" s="0">
         <v>877</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" t="s" s="0">
         <v>878</v>
       </c>
-      <c r="K48" t="s">
-        <v>243</v>
-      </c>
-      <c r="L48">
+      <c r="K48" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L48" s="0">
         <v>25</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="0">
         <v>41</v>
       </c>
       <c r="N48" s="6">
@@ -6848,16 +6848,16 @@
       <c r="I49" t="s" s="0">
         <v>880</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J49" t="s" s="0">
         <v>881</v>
       </c>
-      <c r="K49" t="s">
-        <v>243</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
+      <c r="K49" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L49" s="0">
+        <v>0</v>
+      </c>
+      <c r="M49" s="0">
         <v>192</v>
       </c>
       <c r="N49" s="6">
@@ -6938,16 +6938,16 @@
       <c r="I51" t="s" s="0">
         <v>883</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" t="s" s="0">
         <v>884</v>
       </c>
-      <c r="K51" t="s">
-        <v>243</v>
-      </c>
-      <c r="L51">
+      <c r="K51" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L51" s="0">
         <v>25</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="0">
         <v>157</v>
       </c>
       <c r="N51" s="6">
@@ -6986,16 +6986,16 @@
       <c r="I52" t="s" s="0">
         <v>886</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" t="s" s="0">
         <v>887</v>
       </c>
-      <c r="K52" t="s">
-        <v>243</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
+      <c r="K52" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L52" s="0">
+        <v>0</v>
+      </c>
+      <c r="M52" s="0">
         <v>126</v>
       </c>
       <c r="N52" s="6">
@@ -7034,16 +7034,16 @@
       <c r="I53" t="s" s="0">
         <v>889</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" t="s" s="0">
         <v>890</v>
       </c>
-      <c r="K53" t="s">
-        <v>243</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
+      <c r="K53" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L53" s="0">
+        <v>0</v>
+      </c>
+      <c r="M53" s="0">
         <v>184</v>
       </c>
       <c r="N53" s="6">
@@ -7124,16 +7124,16 @@
       <c r="I55" t="s" s="0">
         <v>892</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" t="s" s="0">
         <v>893</v>
       </c>
-      <c r="K55" t="s">
-        <v>243</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
+      <c r="K55" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L55" s="0">
+        <v>0</v>
+      </c>
+      <c r="M55" s="0">
         <v>44</v>
       </c>
       <c r="N55" s="6">
@@ -7208,16 +7208,16 @@
       <c r="I60" t="s" s="0">
         <v>895</v>
       </c>
-      <c r="J60" t="s">
+      <c r="J60" t="s" s="0">
         <v>896</v>
       </c>
-      <c r="K60" t="s">
-        <v>243</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
+      <c r="K60" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L60" s="0">
+        <v>0</v>
+      </c>
+      <c r="M60" s="0">
         <v>27</v>
       </c>
       <c r="N60" s="6">
@@ -7258,16 +7258,16 @@
       <c r="I61" t="s" s="0">
         <v>898</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" t="s" s="0">
         <v>899</v>
       </c>
-      <c r="K61" t="s">
-        <v>243</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
+      <c r="K61" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L61" s="0">
+        <v>0</v>
+      </c>
+      <c r="M61" s="0">
         <v>167</v>
       </c>
       <c r="N61" s="6">
@@ -7308,16 +7308,16 @@
       <c r="I62" t="s" s="0">
         <v>901</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" t="s" s="0">
         <v>902</v>
       </c>
-      <c r="K62" t="s">
-        <v>243</v>
-      </c>
-      <c r="L62">
+      <c r="K62" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L62" s="0">
         <v>25</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="0">
         <v>82</v>
       </c>
       <c r="N62" s="6">
@@ -7358,16 +7358,16 @@
       <c r="I63" t="s" s="0">
         <v>904</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" t="s" s="0">
         <v>905</v>
       </c>
-      <c r="K63" t="s">
-        <v>243</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
+      <c r="K63" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L63" s="0">
+        <v>0</v>
+      </c>
+      <c r="M63" s="0">
         <v>122</v>
       </c>
       <c r="N63" s="6">
@@ -7405,16 +7405,16 @@
       <c r="I64" t="s" s="0">
         <v>907</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J64" t="s" s="0">
         <v>908</v>
       </c>
-      <c r="K64" t="s">
-        <v>243</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
+      <c r="K64" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L64" s="0">
+        <v>0</v>
+      </c>
+      <c r="M64" s="0">
         <v>92</v>
       </c>
       <c r="N64" s="6">
@@ -7452,16 +7452,16 @@
       <c r="I65" t="s" s="0">
         <v>910</v>
       </c>
-      <c r="J65" t="s">
+      <c r="J65" t="s" s="0">
         <v>911</v>
       </c>
-      <c r="K65" t="s">
-        <v>243</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
+      <c r="K65" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L65" s="0">
+        <v>0</v>
+      </c>
+      <c r="M65" s="0">
         <v>28</v>
       </c>
       <c r="N65" s="6">
@@ -7499,16 +7499,16 @@
       <c r="I66" t="s" s="0">
         <v>913</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" t="s" s="0">
         <v>914</v>
       </c>
-      <c r="K66" t="s">
-        <v>243</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
+      <c r="K66" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L66" s="0">
+        <v>0</v>
+      </c>
+      <c r="M66" s="0">
         <v>6</v>
       </c>
       <c r="N66" s="6">
@@ -7637,16 +7637,16 @@
       <c r="I69" t="s" s="0">
         <v>917</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" t="s" s="0">
         <v>918</v>
       </c>
-      <c r="K69" t="s">
-        <v>243</v>
-      </c>
-      <c r="L69">
+      <c r="K69" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L69" s="0">
         <v>25</v>
       </c>
-      <c r="M69">
+      <c r="M69" s="0">
         <v>183</v>
       </c>
       <c r="N69" s="6">
@@ -7687,16 +7687,16 @@
       <c r="I70" t="s" s="0">
         <v>919</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" t="s" s="0">
         <v>920</v>
       </c>
-      <c r="K70" t="s">
-        <v>243</v>
-      </c>
-      <c r="L70">
+      <c r="K70" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L70" s="0">
         <v>1</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="0">
         <v>73</v>
       </c>
       <c r="N70" s="6">
@@ -7737,16 +7737,16 @@
       <c r="I71" t="s" s="0">
         <v>895</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" t="s" s="0">
         <v>921</v>
       </c>
-      <c r="K71" t="s">
-        <v>243</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
+      <c r="K71" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L71" s="0">
+        <v>0</v>
+      </c>
+      <c r="M71" s="0">
         <v>180</v>
       </c>
       <c r="N71" s="6">
@@ -7787,16 +7787,16 @@
       <c r="I72" t="s" s="0">
         <v>923</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J72" t="s" s="0">
         <v>924</v>
       </c>
-      <c r="K72" t="s">
-        <v>243</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
+      <c r="K72" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L72" s="0">
+        <v>0</v>
+      </c>
+      <c r="M72" s="0">
         <v>187</v>
       </c>
       <c r="N72" s="6">
@@ -7837,16 +7837,16 @@
       <c r="I73" t="s" s="0">
         <v>926</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J73" t="s" s="0">
         <v>927</v>
       </c>
-      <c r="K73" t="s">
-        <v>243</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
+      <c r="K73" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L73" s="0">
+        <v>0</v>
+      </c>
+      <c r="M73" s="0">
         <v>18</v>
       </c>
       <c r="N73" s="6">
@@ -7887,16 +7887,16 @@
       <c r="I74" t="s" s="0">
         <v>929</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" t="s" s="0">
         <v>930</v>
       </c>
-      <c r="K74" t="s">
-        <v>243</v>
-      </c>
-      <c r="L74">
+      <c r="K74" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L74" s="0">
         <v>25</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="0">
         <v>109</v>
       </c>
       <c r="N74" s="6">
@@ -7937,16 +7937,16 @@
       <c r="I75" t="s" s="0">
         <v>932</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" t="s" s="0">
         <v>933</v>
       </c>
-      <c r="K75" t="s">
-        <v>243</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
+      <c r="K75" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L75" s="0">
+        <v>0</v>
+      </c>
+      <c r="M75" s="0">
         <v>12</v>
       </c>
       <c r="N75" s="6">
@@ -7987,16 +7987,16 @@
       <c r="I76" t="s" s="0">
         <v>935</v>
       </c>
-      <c r="J76" t="s">
+      <c r="J76" t="s" s="0">
         <v>936</v>
       </c>
-      <c r="K76" t="s">
-        <v>243</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
+      <c r="K76" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L76" s="0">
+        <v>0</v>
+      </c>
+      <c r="M76" s="0">
         <v>174</v>
       </c>
       <c r="N76" s="6">
@@ -8090,16 +8090,16 @@
       <c r="I79" t="s" s="0">
         <v>938</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" t="s" s="0">
         <v>939</v>
       </c>
-      <c r="K79" t="s">
-        <v>243</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
+      <c r="K79" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L79" s="0">
+        <v>0</v>
+      </c>
+      <c r="M79" s="0">
         <v>121</v>
       </c>
       <c r="N79" s="6">
@@ -8140,16 +8140,16 @@
       <c r="I80" t="s" s="0">
         <v>940</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" t="s" s="0">
         <v>941</v>
       </c>
-      <c r="K80" t="s">
-        <v>243</v>
-      </c>
-      <c r="L80">
+      <c r="K80" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L80" s="0">
         <v>25</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="0">
         <v>146</v>
       </c>
       <c r="N80" s="6">
@@ -8190,16 +8190,16 @@
       <c r="I81" t="s" s="0">
         <v>943</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" t="s" s="0">
         <v>944</v>
       </c>
-      <c r="K81" t="s">
-        <v>243</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
+      <c r="K81" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L81" s="0">
+        <v>0</v>
+      </c>
+      <c r="M81" s="0">
         <v>139</v>
       </c>
       <c r="N81" s="6">
@@ -8240,16 +8240,16 @@
       <c r="I82" t="s" s="0">
         <v>946</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J82" t="s" s="0">
         <v>947</v>
       </c>
-      <c r="K82" t="s">
-        <v>243</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
+      <c r="K82" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L82" s="0">
+        <v>0</v>
+      </c>
+      <c r="M82" s="0">
         <v>6</v>
       </c>
       <c r="N82" s="6">
@@ -8331,16 +8331,16 @@
       <c r="I84" t="s" s="0">
         <v>950</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" t="s" s="0">
         <v>951</v>
       </c>
-      <c r="K84" t="s">
-        <v>243</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
+      <c r="K84" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L84" s="0">
+        <v>0</v>
+      </c>
+      <c r="M84" s="0">
         <v>123</v>
       </c>
       <c r="N84" s="6">
@@ -8390,16 +8390,16 @@
       <c r="I86" t="s" s="0">
         <v>953</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" t="s" s="0">
         <v>954</v>
       </c>
-      <c r="K86" t="s">
-        <v>243</v>
-      </c>
-      <c r="L86">
+      <c r="K86" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L86" s="0">
         <v>25</v>
       </c>
-      <c r="M86">
+      <c r="M86" s="0">
         <v>170</v>
       </c>
       <c r="N86" s="6">
@@ -8440,16 +8440,16 @@
       <c r="I87" t="s" s="0">
         <v>956</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" t="s" s="0">
         <v>957</v>
       </c>
-      <c r="K87" t="s">
-        <v>243</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
+      <c r="K87" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L87" s="0">
+        <v>0</v>
+      </c>
+      <c r="M87" s="0">
         <v>171</v>
       </c>
       <c r="N87" s="6">
@@ -8490,16 +8490,16 @@
       <c r="I88" t="s" s="0">
         <v>959</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" t="s" s="0">
         <v>960</v>
       </c>
-      <c r="K88" t="s">
-        <v>243</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
+      <c r="K88" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L88" s="0">
+        <v>0</v>
+      </c>
+      <c r="M88" s="0">
         <v>93</v>
       </c>
       <c r="N88" s="6">
@@ -8540,16 +8540,16 @@
       <c r="I89" t="s" s="0">
         <v>962</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" t="s" s="0">
         <v>963</v>
       </c>
-      <c r="K89" t="s">
-        <v>243</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
+      <c r="K89" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L89" s="0">
+        <v>0</v>
+      </c>
+      <c r="M89" s="0">
         <v>40</v>
       </c>
       <c r="N89" s="6">
@@ -8631,16 +8631,16 @@
       <c r="I91" t="s" s="0">
         <v>966</v>
       </c>
-      <c r="J91" t="s">
+      <c r="J91" t="s" s="0">
         <v>967</v>
       </c>
-      <c r="K91" t="s">
-        <v>243</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
+      <c r="K91" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L91" s="0">
+        <v>0</v>
+      </c>
+      <c r="M91" s="0">
         <v>125</v>
       </c>
       <c r="N91" s="6">
@@ -8681,16 +8681,16 @@
       <c r="I92" t="s" s="0">
         <v>968</v>
       </c>
-      <c r="J92" t="s">
+      <c r="J92" t="s" s="0">
         <v>969</v>
       </c>
-      <c r="K92" t="s">
-        <v>243</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
+      <c r="K92" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L92" s="0">
+        <v>0</v>
+      </c>
+      <c r="M92" s="0">
         <v>56</v>
       </c>
       <c r="N92" s="6">
@@ -8731,16 +8731,16 @@
       <c r="I93" t="s" s="0">
         <v>971</v>
       </c>
-      <c r="J93" t="s">
+      <c r="J93" t="s" s="0">
         <v>972</v>
       </c>
-      <c r="K93" t="s">
-        <v>243</v>
-      </c>
-      <c r="L93">
+      <c r="K93" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L93" s="0">
         <v>25</v>
       </c>
-      <c r="M93">
+      <c r="M93" s="0">
         <v>88</v>
       </c>
       <c r="N93" s="6">
@@ -8823,16 +8823,16 @@
       <c r="I95" t="s" s="0">
         <v>975</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J95" t="s" s="0">
         <v>976</v>
       </c>
-      <c r="K95" t="s">
-        <v>243</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
+      <c r="K95" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L95" s="0">
+        <v>0</v>
+      </c>
+      <c r="M95" s="0">
         <v>31</v>
       </c>
       <c r="N95" s="6">
@@ -8927,16 +8927,16 @@
       <c r="I102" t="s" s="0">
         <v>978</v>
       </c>
-      <c r="J102" t="s">
+      <c r="J102" t="s" s="0">
         <v>979</v>
       </c>
-      <c r="K102" t="s">
-        <v>243</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
+      <c r="K102" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L102" s="0">
+        <v>0</v>
+      </c>
+      <c r="M102" s="0">
         <v>17</v>
       </c>
       <c r="N102" s="6">
@@ -8977,16 +8977,16 @@
       <c r="I103" t="s" s="0">
         <v>981</v>
       </c>
-      <c r="J103" t="s">
+      <c r="J103" t="s" s="0">
         <v>982</v>
       </c>
-      <c r="K103" t="s">
-        <v>243</v>
-      </c>
-      <c r="L103">
+      <c r="K103" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L103" s="0">
         <v>25</v>
       </c>
-      <c r="M103">
+      <c r="M103" s="0">
         <v>52</v>
       </c>
       <c r="N103" s="6">
@@ -9027,16 +9027,16 @@
       <c r="I104" t="s" s="0">
         <v>984</v>
       </c>
-      <c r="J104" t="s">
+      <c r="J104" t="s" s="0">
         <v>985</v>
       </c>
-      <c r="K104" t="s">
-        <v>243</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
+      <c r="K104" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L104" s="0">
+        <v>0</v>
+      </c>
+      <c r="M104" s="0">
         <v>135</v>
       </c>
       <c r="N104" s="6">
@@ -9121,16 +9121,16 @@
       <c r="I106" t="s" s="0">
         <v>988</v>
       </c>
-      <c r="J106" t="s">
+      <c r="J106" t="s" s="0">
         <v>989</v>
       </c>
-      <c r="K106" t="s">
-        <v>243</v>
-      </c>
-      <c r="L106">
+      <c r="K106" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L106" s="0">
         <v>25</v>
       </c>
-      <c r="M106">
+      <c r="M106" s="0">
         <v>127</v>
       </c>
       <c r="N106" s="6">
@@ -9439,16 +9439,16 @@
       <c r="I129" t="s" s="0">
         <v>992</v>
       </c>
-      <c r="J129" t="s">
+      <c r="J129" t="s" s="0">
         <v>993</v>
       </c>
-      <c r="K129" t="s">
-        <v>243</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
+      <c r="K129" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L129" s="0">
+        <v>0</v>
+      </c>
+      <c r="M129" s="0">
         <v>117</v>
       </c>
       <c r="N129" s="6">
@@ -9533,16 +9533,16 @@
       <c r="I131" t="s" s="0">
         <v>996</v>
       </c>
-      <c r="J131" t="s">
+      <c r="J131" t="s" s="0">
         <v>997</v>
       </c>
-      <c r="K131" t="s">
-        <v>243</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
+      <c r="K131" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L131" s="0">
+        <v>0</v>
+      </c>
+      <c r="M131" s="0">
         <v>54</v>
       </c>
       <c r="N131" s="6">
@@ -9583,16 +9583,16 @@
       <c r="I132" t="s" s="0">
         <v>999</v>
       </c>
-      <c r="J132" t="s">
+      <c r="J132" t="s" s="0">
         <v>1000</v>
       </c>
-      <c r="K132" t="s">
+      <c r="K132" t="s" s="0">
         <v>373</v>
       </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
+      <c r="L132" s="0">
+        <v>0</v>
+      </c>
+      <c r="M132" s="0">
         <v>76</v>
       </c>
       <c r="N132" s="6">
@@ -9677,16 +9677,16 @@
       <c r="I134" t="s" s="0">
         <v>1002</v>
       </c>
-      <c r="J134" t="s">
+      <c r="J134" t="s" s="0">
         <v>1003</v>
       </c>
-      <c r="K134" t="s">
-        <v>243</v>
-      </c>
-      <c r="L134">
+      <c r="K134" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L134" s="0">
         <v>25</v>
       </c>
-      <c r="M134">
+      <c r="M134" s="0">
         <v>110</v>
       </c>
       <c r="N134" s="6">
@@ -9853,16 +9853,16 @@
       <c r="I142" t="s" s="0">
         <v>1006</v>
       </c>
-      <c r="J142" t="s">
+      <c r="J142" t="s" s="0">
         <v>1007</v>
       </c>
-      <c r="K142" t="s">
-        <v>243</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
+      <c r="K142" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L142" s="0">
+        <v>0</v>
+      </c>
+      <c r="M142" s="0">
         <v>80</v>
       </c>
       <c r="N142" s="6">
@@ -9903,16 +9903,16 @@
       <c r="I143" t="s" s="0">
         <v>776</v>
       </c>
-      <c r="J143" t="s">
+      <c r="J143" t="s" s="0">
         <v>1009</v>
       </c>
-      <c r="K143" t="s">
-        <v>243</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
+      <c r="K143" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L143" s="0">
+        <v>0</v>
+      </c>
+      <c r="M143" s="0">
         <v>10</v>
       </c>
       <c r="N143" s="6">
@@ -9953,16 +9953,16 @@
       <c r="I144" t="s" s="0">
         <v>1011</v>
       </c>
-      <c r="J144" t="s">
+      <c r="J144" t="s" s="0">
         <v>1012</v>
       </c>
-      <c r="K144" t="s">
-        <v>243</v>
-      </c>
-      <c r="L144">
+      <c r="K144" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L144" s="0">
         <v>50</v>
       </c>
-      <c r="M144">
+      <c r="M144" s="0">
         <v>650</v>
       </c>
       <c r="N144" s="6">
@@ -10003,16 +10003,16 @@
       <c r="I145" t="s" s="0">
         <v>1013</v>
       </c>
-      <c r="J145" t="s">
+      <c r="J145" t="s" s="0">
         <v>1014</v>
       </c>
-      <c r="K145" t="s">
-        <v>243</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
+      <c r="K145" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L145" s="0">
+        <v>0</v>
+      </c>
+      <c r="M145" s="0">
         <v>950</v>
       </c>
       <c r="N145" s="6">
@@ -10053,16 +10053,16 @@
       <c r="I146" t="s" s="0">
         <v>1017</v>
       </c>
-      <c r="J146" t="s">
+      <c r="J146" t="s" s="0">
         <v>1018</v>
       </c>
-      <c r="K146" t="s">
-        <v>243</v>
-      </c>
-      <c r="L146">
+      <c r="K146" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L146" s="0">
         <v>25</v>
       </c>
-      <c r="M146">
+      <c r="M146" s="0">
         <v>150</v>
       </c>
       <c r="N146" s="6">
@@ -10103,16 +10103,16 @@
       <c r="I147" t="s" s="0">
         <v>786</v>
       </c>
-      <c r="J147" t="s">
+      <c r="J147" t="s" s="0">
         <v>1020</v>
       </c>
-      <c r="K147" t="s">
-        <v>243</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
+      <c r="K147" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L147" s="0">
+        <v>0</v>
+      </c>
+      <c r="M147" s="0">
         <v>50</v>
       </c>
       <c r="N147" s="6">
@@ -10153,16 +10153,16 @@
       <c r="I148" t="s" s="0">
         <v>790</v>
       </c>
-      <c r="J148" t="s">
+      <c r="J148" t="s" s="0">
         <v>1022</v>
       </c>
-      <c r="K148" t="s">
-        <v>243</v>
-      </c>
-      <c r="L148">
+      <c r="K148" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L148" s="0">
         <v>25</v>
       </c>
-      <c r="M148">
+      <c r="M148" s="0">
         <v>51</v>
       </c>
       <c r="N148" s="6">
@@ -10203,16 +10203,16 @@
       <c r="I149" t="s" s="0">
         <v>1025</v>
       </c>
-      <c r="J149" t="s">
+      <c r="J149" t="s" s="0">
         <v>1026</v>
       </c>
-      <c r="K149" t="s">
-        <v>243</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
+      <c r="K149" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L149" s="0">
+        <v>0</v>
+      </c>
+      <c r="M149" s="0">
         <v>137</v>
       </c>
       <c r="N149" s="6">
@@ -10253,16 +10253,16 @@
       <c r="I150" t="s" s="0">
         <v>795</v>
       </c>
-      <c r="J150" t="s">
+      <c r="J150" t="s" s="0">
         <v>1028</v>
       </c>
-      <c r="K150" t="s">
-        <v>243</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150">
+      <c r="K150" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L150" s="0">
+        <v>0</v>
+      </c>
+      <c r="M150" s="0">
         <v>43</v>
       </c>
       <c r="N150" s="6">
@@ -10303,16 +10303,16 @@
       <c r="I151" t="s" s="0">
         <v>1031</v>
       </c>
-      <c r="J151" t="s">
+      <c r="J151" t="s" s="0">
         <v>1032</v>
       </c>
-      <c r="K151" t="s">
-        <v>243</v>
-      </c>
-      <c r="L151">
+      <c r="K151" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L151" s="0">
         <v>25</v>
       </c>
-      <c r="M151">
+      <c r="M151" s="0">
         <v>187</v>
       </c>
       <c r="N151" s="6">
@@ -10397,16 +10397,16 @@
       <c r="I153" t="s" s="0">
         <v>1036</v>
       </c>
-      <c r="J153" t="s">
+      <c r="J153" t="s" s="0">
         <v>1037</v>
       </c>
-      <c r="K153" t="s">
-        <v>243</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
+      <c r="K153" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L153" s="0">
+        <v>0</v>
+      </c>
+      <c r="M153" s="0">
         <v>179</v>
       </c>
       <c r="N153" s="6">
@@ -10502,16 +10502,16 @@
       <c r="I156" t="s" s="0">
         <v>1040</v>
       </c>
-      <c r="J156" t="s">
+      <c r="J156" t="s" s="0">
         <v>1041</v>
       </c>
-      <c r="K156" t="s">
-        <v>243</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
+      <c r="K156" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L156" s="0">
+        <v>0</v>
+      </c>
+      <c r="M156" s="0">
         <v>140</v>
       </c>
       <c r="N156" s="6">
@@ -10596,16 +10596,16 @@
       <c r="I158" t="s" s="0">
         <v>1045</v>
       </c>
-      <c r="J158" t="s">
+      <c r="J158" t="s" s="0">
         <v>1046</v>
       </c>
-      <c r="K158" t="s">
-        <v>243</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
+      <c r="K158" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L158" s="0">
+        <v>0</v>
+      </c>
+      <c r="M158" s="0">
         <v>122</v>
       </c>
       <c r="N158" s="6">
@@ -10646,16 +10646,16 @@
       <c r="I159" t="s" s="0">
         <v>1048</v>
       </c>
-      <c r="J159" t="s">
+      <c r="J159" t="s" s="0">
         <v>1049</v>
       </c>
-      <c r="K159" t="s">
-        <v>243</v>
-      </c>
-      <c r="L159">
+      <c r="K159" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L159" s="0">
         <v>25</v>
       </c>
-      <c r="M159">
+      <c r="M159" s="0">
         <v>153</v>
       </c>
       <c r="N159" s="6">
@@ -10696,16 +10696,16 @@
       <c r="I160" t="s" s="0">
         <v>1052</v>
       </c>
-      <c r="J160" t="s">
+      <c r="J160" t="s" s="0">
         <v>1053</v>
       </c>
-      <c r="K160" t="s">
-        <v>243</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160">
+      <c r="K160" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L160" s="0">
+        <v>0</v>
+      </c>
+      <c r="M160" s="0">
         <v>100</v>
       </c>
       <c r="N160" s="6">
@@ -10746,16 +10746,16 @@
       <c r="I161" t="s" s="0">
         <v>808</v>
       </c>
-      <c r="J161" t="s">
+      <c r="J161" t="s" s="0">
         <v>1055</v>
       </c>
-      <c r="K161" t="s">
-        <v>243</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161">
+      <c r="K161" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L161" s="0">
+        <v>0</v>
+      </c>
+      <c r="M161" s="0">
         <v>122</v>
       </c>
       <c r="N161" s="6">
@@ -10796,16 +10796,16 @@
       <c r="I162" t="s" s="0">
         <v>811</v>
       </c>
-      <c r="J162" t="s">
+      <c r="J162" t="s" s="0">
         <v>1056</v>
       </c>
-      <c r="K162" t="s">
-        <v>243</v>
-      </c>
-      <c r="L162">
+      <c r="K162" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L162" s="0">
         <v>25</v>
       </c>
-      <c r="M162">
+      <c r="M162" s="0">
         <v>74</v>
       </c>
       <c r="N162" s="6">
@@ -10890,16 +10890,16 @@
       <c r="I164" t="s" s="0">
         <v>814</v>
       </c>
-      <c r="J164" t="s">
+      <c r="J164" t="s" s="0">
         <v>1059</v>
       </c>
-      <c r="K164" t="s">
-        <v>243</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164">
+      <c r="K164" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L164" s="0">
+        <v>0</v>
+      </c>
+      <c r="M164" s="0">
         <v>177</v>
       </c>
       <c r="N164" s="6">
@@ -10940,16 +10940,16 @@
       <c r="I165" t="s" s="0">
         <v>1062</v>
       </c>
-      <c r="J165" t="s">
+      <c r="J165" t="s" s="0">
         <v>1063</v>
       </c>
-      <c r="K165" t="s">
-        <v>243</v>
-      </c>
-      <c r="L165">
+      <c r="K165" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L165" s="0">
         <v>25</v>
       </c>
-      <c r="M165">
+      <c r="M165" s="0">
         <v>42</v>
       </c>
       <c r="N165" s="6">
@@ -11001,16 +11001,16 @@
       <c r="I167" t="s" s="0">
         <v>820</v>
       </c>
-      <c r="J167" t="s">
+      <c r="J167" t="s" s="0">
         <v>1065</v>
       </c>
-      <c r="K167" t="s">
-        <v>243</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167">
+      <c r="K167" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L167" s="0">
+        <v>0</v>
+      </c>
+      <c r="M167" s="0">
         <v>88</v>
       </c>
       <c r="N167" s="6">
@@ -11051,16 +11051,16 @@
       <c r="I168" t="s" s="0">
         <v>1068</v>
       </c>
-      <c r="J168" t="s">
+      <c r="J168" t="s" s="0">
         <v>1069</v>
       </c>
-      <c r="K168" t="s">
-        <v>243</v>
-      </c>
-      <c r="L168">
+      <c r="K168" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L168" s="0">
         <v>25</v>
       </c>
-      <c r="M168">
+      <c r="M168" s="0">
         <v>101</v>
       </c>
       <c r="N168" s="6">
@@ -11101,16 +11101,16 @@
       <c r="I169" t="s" s="0">
         <v>826</v>
       </c>
-      <c r="J169" t="s">
+      <c r="J169" t="s" s="0">
         <v>1071</v>
       </c>
-      <c r="K169" t="s">
-        <v>243</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="M169">
+      <c r="K169" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L169" s="0">
+        <v>0</v>
+      </c>
+      <c r="M169" s="0">
         <v>10</v>
       </c>
       <c r="N169" s="6">
@@ -11151,16 +11151,16 @@
       <c r="I170" t="s" s="0">
         <v>828</v>
       </c>
-      <c r="J170" t="s">
+      <c r="J170" t="s" s="0">
         <v>1073</v>
       </c>
-      <c r="K170" t="s">
-        <v>243</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="M170">
+      <c r="K170" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L170" s="0">
+        <v>0</v>
+      </c>
+      <c r="M170" s="0">
         <v>78</v>
       </c>
       <c r="N170" s="6">
@@ -11201,16 +11201,16 @@
       <c r="I171" t="s" s="0">
         <v>1076</v>
       </c>
-      <c r="J171" t="s">
+      <c r="J171" t="s" s="0">
         <v>1077</v>
       </c>
-      <c r="K171" t="s">
-        <v>243</v>
-      </c>
-      <c r="L171">
-        <v>0</v>
-      </c>
-      <c r="M171">
+      <c r="K171" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L171" s="0">
+        <v>0</v>
+      </c>
+      <c r="M171" s="0">
         <v>71</v>
       </c>
       <c r="N171" s="6">
@@ -11251,16 +11251,16 @@
       <c r="I172" t="s" s="0">
         <v>834</v>
       </c>
-      <c r="J172" t="s">
+      <c r="J172" t="s" s="0">
         <v>1079</v>
       </c>
-      <c r="K172" t="s">
-        <v>243</v>
-      </c>
-      <c r="L172">
-        <v>0</v>
-      </c>
-      <c r="M172">
+      <c r="K172" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L172" s="0">
+        <v>0</v>
+      </c>
+      <c r="M172" s="0">
         <v>113</v>
       </c>
       <c r="N172" s="6">
@@ -11334,16 +11334,16 @@
       <c r="I176" t="s" s="0">
         <v>838</v>
       </c>
-      <c r="J176" t="s">
+      <c r="J176" t="s" s="0">
         <v>1081</v>
       </c>
-      <c r="K176" t="s">
-        <v>243</v>
-      </c>
-      <c r="L176">
+      <c r="K176" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L176" s="0">
         <v>25</v>
       </c>
-      <c r="M176">
+      <c r="M176" s="0">
         <v>10</v>
       </c>
       <c r="N176" s="6">
@@ -11382,16 +11382,16 @@
       <c r="I177" t="s" s="0">
         <v>1084</v>
       </c>
-      <c r="J177" t="s">
+      <c r="J177" t="s" s="0">
         <v>1085</v>
       </c>
-      <c r="K177" t="s">
-        <v>243</v>
-      </c>
-      <c r="L177">
-        <v>0</v>
-      </c>
-      <c r="M177">
+      <c r="K177" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L177" s="0">
+        <v>0</v>
+      </c>
+      <c r="M177" s="0">
         <v>50</v>
       </c>
       <c r="N177" s="6">
@@ -11430,16 +11430,16 @@
       <c r="I178" t="s" s="0">
         <v>1088</v>
       </c>
-      <c r="J178" t="s">
+      <c r="J178" t="s" s="0">
         <v>1089</v>
       </c>
-      <c r="K178" t="s">
-        <v>243</v>
-      </c>
-      <c r="L178">
-        <v>0</v>
-      </c>
-      <c r="M178">
+      <c r="K178" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L178" s="0">
+        <v>0</v>
+      </c>
+      <c r="M178" s="0">
         <v>141</v>
       </c>
       <c r="N178" s="6">
@@ -11478,16 +11478,16 @@
       <c r="I179" t="s" s="0">
         <v>847</v>
       </c>
-      <c r="J179" t="s">
+      <c r="J179" t="s" s="0">
         <v>1091</v>
       </c>
-      <c r="K179" t="s">
-        <v>243</v>
-      </c>
-      <c r="L179">
-        <v>0</v>
-      </c>
-      <c r="M179">
+      <c r="K179" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L179" s="0">
+        <v>0</v>
+      </c>
+      <c r="M179" s="0">
         <v>500</v>
       </c>
       <c r="N179" s="6">
@@ -11526,16 +11526,16 @@
       <c r="I180" t="s" s="0">
         <v>851</v>
       </c>
-      <c r="J180" t="s">
+      <c r="J180" t="s" s="0">
         <v>1093</v>
       </c>
-      <c r="K180" t="s">
-        <v>243</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
-      <c r="M180">
+      <c r="K180" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L180" s="0">
+        <v>0</v>
+      </c>
+      <c r="M180" s="0">
         <v>120</v>
       </c>
       <c r="N180" s="6">
@@ -11574,16 +11574,16 @@
       <c r="I181" t="s" s="0">
         <v>855</v>
       </c>
-      <c r="J181" t="s">
+      <c r="J181" t="s" s="0">
         <v>1095</v>
       </c>
-      <c r="K181" t="s">
-        <v>243</v>
-      </c>
-      <c r="L181">
+      <c r="K181" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L181" s="0">
         <v>50</v>
       </c>
-      <c r="M181">
+      <c r="M181" s="0">
         <v>30</v>
       </c>
       <c r="N181" s="6">
@@ -11622,16 +11622,16 @@
       <c r="I182" t="s" s="0">
         <v>1098</v>
       </c>
-      <c r="J182" t="s">
+      <c r="J182" t="s" s="0">
         <v>1099</v>
       </c>
-      <c r="K182" t="s">
-        <v>243</v>
-      </c>
-      <c r="L182">
-        <v>0</v>
-      </c>
-      <c r="M182">
+      <c r="K182" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L182" s="0">
+        <v>0</v>
+      </c>
+      <c r="M182" s="0">
         <v>118</v>
       </c>
       <c r="N182" s="6">
@@ -11670,16 +11670,16 @@
       <c r="I183" t="s" s="0">
         <v>862</v>
       </c>
-      <c r="J183" t="s">
+      <c r="J183" t="s" s="0">
         <v>1101</v>
       </c>
-      <c r="K183" t="s">
-        <v>243</v>
-      </c>
-      <c r="L183">
-        <v>0</v>
-      </c>
-      <c r="M183">
+      <c r="K183" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L183" s="0">
+        <v>0</v>
+      </c>
+      <c r="M183" s="0">
         <v>154</v>
       </c>
       <c r="N183" s="6">
@@ -11718,16 +11718,16 @@
       <c r="I184" t="s" s="0">
         <v>865</v>
       </c>
-      <c r="J184" t="s">
+      <c r="J184" t="s" s="0">
         <v>1103</v>
       </c>
-      <c r="K184" t="s">
-        <v>243</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
-      <c r="M184">
+      <c r="K184" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L184" s="0">
+        <v>0</v>
+      </c>
+      <c r="M184" s="0">
         <v>57</v>
       </c>
       <c r="N184" s="6">
@@ -11766,16 +11766,16 @@
       <c r="I185" t="s" s="0">
         <v>868</v>
       </c>
-      <c r="J185" t="s">
+      <c r="J185" t="s" s="0">
         <v>1105</v>
       </c>
-      <c r="K185" t="s">
-        <v>243</v>
-      </c>
-      <c r="L185">
-        <v>0</v>
-      </c>
-      <c r="M185">
+      <c r="K185" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L185" s="0">
+        <v>0</v>
+      </c>
+      <c r="M185" s="0">
         <v>99</v>
       </c>
       <c r="N185" s="6">
@@ -11856,16 +11856,16 @@
       <c r="I187" t="s" s="0">
         <v>874</v>
       </c>
-      <c r="J187" t="s">
+      <c r="J187" t="s" s="0">
         <v>1108</v>
       </c>
-      <c r="K187" t="s">
-        <v>243</v>
-      </c>
-      <c r="L187">
-        <v>0</v>
-      </c>
-      <c r="M187">
+      <c r="K187" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L187" s="0">
+        <v>0</v>
+      </c>
+      <c r="M187" s="0">
         <v>94</v>
       </c>
       <c r="N187" s="6">
@@ -11904,16 +11904,16 @@
       <c r="I188" t="s" s="0">
         <v>877</v>
       </c>
-      <c r="J188" t="s">
+      <c r="J188" t="s" s="0">
         <v>1110</v>
       </c>
-      <c r="K188" t="s">
-        <v>243</v>
-      </c>
-      <c r="L188">
+      <c r="K188" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L188" s="0">
         <v>25</v>
       </c>
-      <c r="M188">
+      <c r="M188" s="0">
         <v>41</v>
       </c>
       <c r="N188" s="6">
@@ -11952,16 +11952,16 @@
       <c r="I189" t="s" s="0">
         <v>880</v>
       </c>
-      <c r="J189" t="s">
+      <c r="J189" t="s" s="0">
         <v>1112</v>
       </c>
-      <c r="K189" t="s">
-        <v>243</v>
-      </c>
-      <c r="L189">
-        <v>0</v>
-      </c>
-      <c r="M189">
+      <c r="K189" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L189" s="0">
+        <v>0</v>
+      </c>
+      <c r="M189" s="0">
         <v>192</v>
       </c>
       <c r="N189" s="6">
@@ -12000,16 +12000,16 @@
       <c r="I190" t="s" s="0">
         <v>1115</v>
       </c>
-      <c r="J190" t="s">
+      <c r="J190" t="s" s="0">
         <v>1116</v>
       </c>
-      <c r="K190" t="s">
-        <v>243</v>
-      </c>
-      <c r="L190">
-        <v>0</v>
-      </c>
-      <c r="M190">
+      <c r="K190" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L190" s="0">
+        <v>0</v>
+      </c>
+      <c r="M190" s="0">
         <v>88</v>
       </c>
       <c r="N190" s="6">
@@ -12048,16 +12048,16 @@
       <c r="I191" t="s" s="0">
         <v>1118</v>
       </c>
-      <c r="J191" t="s">
+      <c r="J191" t="s" s="0">
         <v>1119</v>
       </c>
-      <c r="K191" t="s">
-        <v>243</v>
-      </c>
-      <c r="L191">
+      <c r="K191" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L191" s="0">
         <v>25</v>
       </c>
-      <c r="M191">
+      <c r="M191" s="0">
         <v>157</v>
       </c>
       <c r="N191" s="6">
@@ -12096,16 +12096,16 @@
       <c r="I192" t="s" s="0">
         <v>886</v>
       </c>
-      <c r="J192" t="s">
+      <c r="J192" t="s" s="0">
         <v>1121</v>
       </c>
-      <c r="K192" t="s">
-        <v>243</v>
-      </c>
-      <c r="L192">
-        <v>0</v>
-      </c>
-      <c r="M192">
+      <c r="K192" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L192" s="0">
+        <v>0</v>
+      </c>
+      <c r="M192" s="0">
         <v>126</v>
       </c>
       <c r="N192" s="6">
@@ -12228,16 +12228,16 @@
       <c r="I195" t="s" s="0">
         <v>892</v>
       </c>
-      <c r="J195" t="s">
+      <c r="J195" t="s" s="0">
         <v>1125</v>
       </c>
-      <c r="K195" t="s">
-        <v>243</v>
-      </c>
-      <c r="L195">
-        <v>0</v>
-      </c>
-      <c r="M195">
+      <c r="K195" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L195" s="0">
+        <v>0</v>
+      </c>
+      <c r="M195" s="0">
         <v>44</v>
       </c>
       <c r="N195" s="6">
@@ -12320,16 +12320,16 @@
       <c r="I200" t="s" s="0">
         <v>895</v>
       </c>
-      <c r="J200" t="s">
+      <c r="J200" t="s" s="0">
         <v>1127</v>
       </c>
-      <c r="K200" t="s">
-        <v>243</v>
-      </c>
-      <c r="L200">
-        <v>0</v>
-      </c>
-      <c r="M200">
+      <c r="K200" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L200" s="0">
+        <v>0</v>
+      </c>
+      <c r="M200" s="0">
         <v>27</v>
       </c>
       <c r="N200" s="6">
@@ -12370,16 +12370,16 @@
       <c r="I201" t="s" s="0">
         <v>898</v>
       </c>
-      <c r="J201" t="s">
+      <c r="J201" t="s" s="0">
         <v>1129</v>
       </c>
-      <c r="K201" t="s">
-        <v>243</v>
-      </c>
-      <c r="L201">
-        <v>0</v>
-      </c>
-      <c r="M201">
+      <c r="K201" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L201" s="0">
+        <v>0</v>
+      </c>
+      <c r="M201" s="0">
         <v>167</v>
       </c>
       <c r="N201" s="6">
@@ -12420,16 +12420,16 @@
       <c r="I202" t="s" s="0">
         <v>1132</v>
       </c>
-      <c r="J202" t="s">
+      <c r="J202" t="s" s="0">
         <v>1133</v>
       </c>
-      <c r="K202" t="s">
-        <v>243</v>
-      </c>
-      <c r="L202">
+      <c r="K202" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L202" s="0">
         <v>25</v>
       </c>
-      <c r="M202">
+      <c r="M202" s="0">
         <v>82</v>
       </c>
       <c r="N202" s="6">
@@ -12470,16 +12470,16 @@
       <c r="I203" t="s" s="0">
         <v>904</v>
       </c>
-      <c r="J203" t="s">
+      <c r="J203" t="s" s="0">
         <v>1135</v>
       </c>
-      <c r="K203" t="s">
-        <v>243</v>
-      </c>
-      <c r="L203">
-        <v>0</v>
-      </c>
-      <c r="M203">
+      <c r="K203" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L203" s="0">
+        <v>0</v>
+      </c>
+      <c r="M203" s="0">
         <v>122</v>
       </c>
       <c r="N203" s="6">
@@ -12520,16 +12520,16 @@
       <c r="I204" t="s" s="0">
         <v>907</v>
       </c>
-      <c r="J204" t="s">
+      <c r="J204" t="s" s="0">
         <v>1137</v>
       </c>
-      <c r="K204" t="s">
-        <v>243</v>
-      </c>
-      <c r="L204">
-        <v>0</v>
-      </c>
-      <c r="M204">
+      <c r="K204" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L204" s="0">
+        <v>0</v>
+      </c>
+      <c r="M204" s="0">
         <v>92</v>
       </c>
       <c r="N204" s="6">
@@ -12570,16 +12570,16 @@
       <c r="I205" t="s" s="0">
         <v>910</v>
       </c>
-      <c r="J205" t="s">
+      <c r="J205" t="s" s="0">
         <v>1139</v>
       </c>
-      <c r="K205" t="s">
-        <v>243</v>
-      </c>
-      <c r="L205">
-        <v>0</v>
-      </c>
-      <c r="M205">
+      <c r="K205" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L205" s="0">
+        <v>0</v>
+      </c>
+      <c r="M205" s="0">
         <v>28</v>
       </c>
       <c r="N205" s="6">
@@ -12620,16 +12620,16 @@
       <c r="I206" t="s" s="0">
         <v>913</v>
       </c>
-      <c r="J206" t="s">
+      <c r="J206" t="s" s="0">
         <v>1141</v>
       </c>
-      <c r="K206" t="s">
-        <v>243</v>
-      </c>
-      <c r="L206">
-        <v>0</v>
-      </c>
-      <c r="M206">
+      <c r="K206" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L206" s="0">
+        <v>0</v>
+      </c>
+      <c r="M206" s="0">
         <v>6</v>
       </c>
       <c r="N206" s="6">
@@ -12670,16 +12670,16 @@
       <c r="I207" t="s" s="0">
         <v>1143</v>
       </c>
-      <c r="J207" t="s">
+      <c r="J207" t="s" s="0">
         <v>1144</v>
       </c>
-      <c r="K207" t="s">
-        <v>243</v>
-      </c>
-      <c r="L207">
-        <v>0</v>
-      </c>
-      <c r="M207">
+      <c r="K207" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L207" s="0">
+        <v>0</v>
+      </c>
+      <c r="M207" s="0">
         <v>200</v>
       </c>
       <c r="N207" s="6">
@@ -12720,16 +12720,16 @@
       <c r="I208" t="s" s="0">
         <v>1147</v>
       </c>
-      <c r="J208" t="s">
+      <c r="J208" t="s" s="0">
         <v>1148</v>
       </c>
-      <c r="K208" t="s">
-        <v>243</v>
-      </c>
-      <c r="L208">
-        <v>0</v>
-      </c>
-      <c r="M208">
+      <c r="K208" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L208" s="0">
+        <v>0</v>
+      </c>
+      <c r="M208" s="0">
         <v>23</v>
       </c>
       <c r="N208" s="6">
@@ -12770,16 +12770,16 @@
       <c r="I209" t="s" s="0">
         <v>917</v>
       </c>
-      <c r="J209" t="s">
+      <c r="J209" t="s" s="0">
         <v>1150</v>
       </c>
-      <c r="K209" t="s">
-        <v>243</v>
-      </c>
-      <c r="L209">
+      <c r="K209" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L209" s="0">
         <v>25</v>
       </c>
-      <c r="M209">
+      <c r="M209" s="0">
         <v>183</v>
       </c>
       <c r="N209" s="6">
@@ -12820,16 +12820,16 @@
       <c r="I210" t="s" s="0">
         <v>919</v>
       </c>
-      <c r="J210" t="s">
+      <c r="J210" t="s" s="0">
         <v>1152</v>
       </c>
-      <c r="K210" t="s">
-        <v>243</v>
-      </c>
-      <c r="L210">
-        <v>0</v>
-      </c>
-      <c r="M210">
+      <c r="K210" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L210" s="0">
+        <v>0</v>
+      </c>
+      <c r="M210" s="0">
         <v>73</v>
       </c>
       <c r="N210" s="6">
@@ -12870,16 +12870,16 @@
       <c r="I211" t="s" s="0">
         <v>1155</v>
       </c>
-      <c r="J211" t="s">
+      <c r="J211" t="s" s="0">
         <v>1156</v>
       </c>
-      <c r="K211" t="s">
-        <v>243</v>
-      </c>
-      <c r="L211">
-        <v>0</v>
-      </c>
-      <c r="M211">
+      <c r="K211" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L211" s="0">
+        <v>0</v>
+      </c>
+      <c r="M211" s="0">
         <v>180</v>
       </c>
       <c r="N211" s="6">
@@ -12920,16 +12920,16 @@
       <c r="I212" t="s" s="0">
         <v>923</v>
       </c>
-      <c r="J212" t="s">
+      <c r="J212" t="s" s="0">
         <v>1158</v>
       </c>
-      <c r="K212" t="s">
-        <v>243</v>
-      </c>
-      <c r="L212">
-        <v>0</v>
-      </c>
-      <c r="M212">
+      <c r="K212" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L212" s="0">
+        <v>0</v>
+      </c>
+      <c r="M212" s="0">
         <v>187</v>
       </c>
       <c r="N212" s="6">
@@ -12970,16 +12970,16 @@
       <c r="I213" t="s" s="0">
         <v>926</v>
       </c>
-      <c r="J213" t="s">
+      <c r="J213" t="s" s="0">
         <v>1160</v>
       </c>
-      <c r="K213" t="s">
-        <v>243</v>
-      </c>
-      <c r="L213">
-        <v>0</v>
-      </c>
-      <c r="M213">
+      <c r="K213" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L213" s="0">
+        <v>0</v>
+      </c>
+      <c r="M213" s="0">
         <v>18</v>
       </c>
       <c r="N213" s="6">
@@ -13020,16 +13020,16 @@
       <c r="I214" t="s" s="0">
         <v>929</v>
       </c>
-      <c r="J214" t="s">
+      <c r="J214" t="s" s="0">
         <v>1162</v>
       </c>
-      <c r="K214" t="s">
-        <v>243</v>
-      </c>
-      <c r="L214">
+      <c r="K214" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L214" s="0">
         <v>25</v>
       </c>
-      <c r="M214">
+      <c r="M214" s="0">
         <v>109</v>
       </c>
       <c r="N214" s="6">
@@ -13070,16 +13070,16 @@
       <c r="I215" t="s" s="0">
         <v>1165</v>
       </c>
-      <c r="J215" t="s">
+      <c r="J215" t="s" s="0">
         <v>1166</v>
       </c>
-      <c r="K215" t="s">
-        <v>243</v>
-      </c>
-      <c r="L215">
-        <v>0</v>
-      </c>
-      <c r="M215">
+      <c r="K215" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L215" s="0">
+        <v>0</v>
+      </c>
+      <c r="M215" s="0">
         <v>12</v>
       </c>
       <c r="N215" s="6">
@@ -13120,16 +13120,16 @@
       <c r="I216" t="s" s="0">
         <v>935</v>
       </c>
-      <c r="J216" t="s">
+      <c r="J216" t="s" s="0">
         <v>1168</v>
       </c>
-      <c r="K216" t="s">
-        <v>243</v>
-      </c>
-      <c r="L216">
-        <v>0</v>
-      </c>
-      <c r="M216">
+      <c r="K216" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L216" s="0">
+        <v>0</v>
+      </c>
+      <c r="M216" s="0">
         <v>174</v>
       </c>
       <c r="N216" s="6">
@@ -13170,16 +13170,16 @@
       <c r="I217" t="s" s="0">
         <v>1171</v>
       </c>
-      <c r="J217" t="s">
+      <c r="J217" t="s" s="0">
         <v>1172</v>
       </c>
-      <c r="K217" t="s">
-        <v>243</v>
-      </c>
-      <c r="L217">
-        <v>0</v>
-      </c>
-      <c r="M217">
+      <c r="K217" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L217" s="0">
+        <v>0</v>
+      </c>
+      <c r="M217" s="0">
         <v>112</v>
       </c>
       <c r="N217" s="6">
@@ -13231,16 +13231,16 @@
       <c r="I219" t="s" s="0">
         <v>938</v>
       </c>
-      <c r="J219" t="s">
+      <c r="J219" t="s" s="0">
         <v>1174</v>
       </c>
-      <c r="K219" t="s">
-        <v>243</v>
-      </c>
-      <c r="L219">
-        <v>0</v>
-      </c>
-      <c r="M219">
+      <c r="K219" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L219" s="0">
+        <v>0</v>
+      </c>
+      <c r="M219" s="0">
         <v>121</v>
       </c>
       <c r="N219" s="6">
@@ -13325,16 +13325,16 @@
       <c r="I221" t="s" s="0">
         <v>943</v>
       </c>
-      <c r="J221" t="s">
+      <c r="J221" t="s" s="0">
         <v>1177</v>
       </c>
-      <c r="K221" t="s">
-        <v>243</v>
-      </c>
-      <c r="L221">
-        <v>0</v>
-      </c>
-      <c r="M221">
+      <c r="K221" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L221" s="0">
+        <v>0</v>
+      </c>
+      <c r="M221" s="0">
         <v>139</v>
       </c>
       <c r="N221" s="6">
@@ -13419,16 +13419,16 @@
       <c r="I223" t="s" s="0">
         <v>1180</v>
       </c>
-      <c r="J223" t="s">
+      <c r="J223" t="s" s="0">
         <v>1181</v>
       </c>
-      <c r="K223" t="s">
-        <v>243</v>
-      </c>
-      <c r="L223">
-        <v>0</v>
-      </c>
-      <c r="M223">
+      <c r="K223" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L223" s="0">
+        <v>0</v>
+      </c>
+      <c r="M223" s="0">
         <v>63</v>
       </c>
       <c r="N223" s="6">
@@ -13469,16 +13469,16 @@
       <c r="I224" t="s" s="0">
         <v>950</v>
       </c>
-      <c r="J224" t="s">
+      <c r="J224" t="s" s="0">
         <v>1183</v>
       </c>
-      <c r="K224" t="s">
-        <v>243</v>
-      </c>
-      <c r="L224">
-        <v>0</v>
-      </c>
-      <c r="M224">
+      <c r="K224" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L224" s="0">
+        <v>0</v>
+      </c>
+      <c r="M224" s="0">
         <v>123</v>
       </c>
       <c r="N224" s="6">
@@ -13530,16 +13530,16 @@
       <c r="I226" t="s" s="0">
         <v>953</v>
       </c>
-      <c r="J226" t="s">
+      <c r="J226" t="s" s="0">
         <v>1185</v>
       </c>
-      <c r="K226" t="s">
-        <v>243</v>
-      </c>
-      <c r="L226">
+      <c r="K226" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L226" s="0">
         <v>25</v>
       </c>
-      <c r="M226">
+      <c r="M226" s="0">
         <v>170</v>
       </c>
       <c r="N226" s="6">
@@ -13580,16 +13580,16 @@
       <c r="I227" t="s" s="0">
         <v>956</v>
       </c>
-      <c r="J227" t="s">
+      <c r="J227" t="s" s="0">
         <v>1187</v>
       </c>
-      <c r="K227" t="s">
-        <v>243</v>
-      </c>
-      <c r="L227">
-        <v>0</v>
-      </c>
-      <c r="M227">
+      <c r="K227" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L227" s="0">
+        <v>0</v>
+      </c>
+      <c r="M227" s="0">
         <v>171</v>
       </c>
       <c r="N227" s="6">
@@ -13630,16 +13630,16 @@
       <c r="I228" t="s" s="0">
         <v>959</v>
       </c>
-      <c r="J228" t="s">
+      <c r="J228" t="s" s="0">
         <v>1188</v>
       </c>
-      <c r="K228" t="s">
-        <v>243</v>
-      </c>
-      <c r="L228">
-        <v>0</v>
-      </c>
-      <c r="M228">
+      <c r="K228" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L228" s="0">
+        <v>0</v>
+      </c>
+      <c r="M228" s="0">
         <v>93</v>
       </c>
       <c r="N228" s="6">
@@ -13680,16 +13680,16 @@
       <c r="I229" t="s" s="0">
         <v>1190</v>
       </c>
-      <c r="J229" t="s">
+      <c r="J229" t="s" s="0">
         <v>1191</v>
       </c>
-      <c r="K229" t="s">
-        <v>243</v>
-      </c>
-      <c r="L229">
-        <v>0</v>
-      </c>
-      <c r="M229">
+      <c r="K229" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L229" s="0">
+        <v>0</v>
+      </c>
+      <c r="M229" s="0">
         <v>40</v>
       </c>
       <c r="N229" s="6">
@@ -13730,16 +13730,16 @@
       <c r="I230" t="s" s="0">
         <v>1194</v>
       </c>
-      <c r="J230" t="s">
+      <c r="J230" t="s" s="0">
         <v>1195</v>
       </c>
-      <c r="K230" t="s">
-        <v>243</v>
-      </c>
-      <c r="L230">
-        <v>0</v>
-      </c>
-      <c r="M230">
+      <c r="K230" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L230" s="0">
+        <v>0</v>
+      </c>
+      <c r="M230" s="0">
         <v>118</v>
       </c>
       <c r="N230" s="6">
@@ -13780,16 +13780,16 @@
       <c r="I231" t="s" s="0">
         <v>966</v>
       </c>
-      <c r="J231" t="s">
+      <c r="J231" t="s" s="0">
         <v>1197</v>
       </c>
-      <c r="K231" t="s">
-        <v>243</v>
-      </c>
-      <c r="L231">
-        <v>0</v>
-      </c>
-      <c r="M231">
+      <c r="K231" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L231" s="0">
+        <v>0</v>
+      </c>
+      <c r="M231" s="0">
         <v>125</v>
       </c>
       <c r="N231" s="6">
@@ -13830,16 +13830,16 @@
       <c r="I232" t="s" s="0">
         <v>1200</v>
       </c>
-      <c r="J232" t="s">
+      <c r="J232" t="s" s="0">
         <v>1201</v>
       </c>
-      <c r="K232" t="s">
-        <v>243</v>
-      </c>
-      <c r="L232">
-        <v>0</v>
-      </c>
-      <c r="M232">
+      <c r="K232" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L232" s="0">
+        <v>0</v>
+      </c>
+      <c r="M232" s="0">
         <v>56</v>
       </c>
       <c r="N232" s="6">
@@ -13880,16 +13880,16 @@
       <c r="I233" t="s" s="0">
         <v>971</v>
       </c>
-      <c r="J233" t="s">
+      <c r="J233" t="s" s="0">
         <v>1203</v>
       </c>
-      <c r="K233" t="s">
-        <v>243</v>
-      </c>
-      <c r="L233">
+      <c r="K233" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L233" s="0">
         <v>25</v>
       </c>
-      <c r="M233">
+      <c r="M233" s="0">
         <v>88</v>
       </c>
       <c r="N233" s="6">
@@ -13930,16 +13930,16 @@
       <c r="I234" t="s" s="0">
         <v>1205</v>
       </c>
-      <c r="J234" t="s">
+      <c r="J234" t="s" s="0">
         <v>1206</v>
       </c>
-      <c r="K234" t="s">
-        <v>243</v>
-      </c>
-      <c r="L234">
-        <v>0</v>
-      </c>
-      <c r="M234">
+      <c r="K234" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L234" s="0">
+        <v>0</v>
+      </c>
+      <c r="M234" s="0">
         <v>116</v>
       </c>
       <c r="N234" s="6">
@@ -13980,16 +13980,16 @@
       <c r="I235" t="s" s="0">
         <v>1209</v>
       </c>
-      <c r="J235" t="s">
+      <c r="J235" t="s" s="0">
         <v>1210</v>
       </c>
-      <c r="K235" t="s">
-        <v>243</v>
-      </c>
-      <c r="L235">
-        <v>0</v>
-      </c>
-      <c r="M235">
+      <c r="K235" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L235" s="0">
+        <v>0</v>
+      </c>
+      <c r="M235" s="0">
         <v>31</v>
       </c>
       <c r="N235" s="6">
@@ -14096,16 +14096,16 @@
       <c r="I242" t="s" s="0">
         <v>978</v>
       </c>
-      <c r="J242" t="s">
+      <c r="J242" t="s" s="0">
         <v>1212</v>
       </c>
-      <c r="K242" t="s">
-        <v>243</v>
-      </c>
-      <c r="L242">
-        <v>0</v>
-      </c>
-      <c r="M242">
+      <c r="K242" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L242" s="0">
+        <v>0</v>
+      </c>
+      <c r="M242" s="0">
         <v>17</v>
       </c>
       <c r="N242" s="6">
@@ -14146,16 +14146,16 @@
       <c r="I243" t="s" s="0">
         <v>981</v>
       </c>
-      <c r="J243" t="s">
+      <c r="J243" t="s" s="0">
         <v>1214</v>
       </c>
-      <c r="K243" t="s">
-        <v>243</v>
-      </c>
-      <c r="L243">
+      <c r="K243" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L243" s="0">
         <v>25</v>
       </c>
-      <c r="M243">
+      <c r="M243" s="0">
         <v>52</v>
       </c>
       <c r="N243" s="6">
@@ -14196,16 +14196,16 @@
       <c r="I244" t="s" s="0">
         <v>1217</v>
       </c>
-      <c r="J244" t="s">
+      <c r="J244" t="s" s="0">
         <v>1218</v>
       </c>
-      <c r="K244" t="s">
-        <v>243</v>
-      </c>
-      <c r="L244">
-        <v>0</v>
-      </c>
-      <c r="M244">
+      <c r="K244" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L244" s="0">
+        <v>0</v>
+      </c>
+      <c r="M244" s="0">
         <v>135</v>
       </c>
       <c r="N244" s="6">
@@ -14246,16 +14246,16 @@
       <c r="I245" t="s" s="0">
         <v>1221</v>
       </c>
-      <c r="J245" t="s">
+      <c r="J245" t="s" s="0">
         <v>1222</v>
       </c>
-      <c r="K245" t="s">
-        <v>243</v>
-      </c>
-      <c r="L245">
-        <v>0</v>
-      </c>
-      <c r="M245">
+      <c r="K245" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L245" s="0">
+        <v>0</v>
+      </c>
+      <c r="M245" s="0">
         <v>6</v>
       </c>
       <c r="N245" s="6">
@@ -14296,16 +14296,16 @@
       <c r="I246" t="s" s="0">
         <v>988</v>
       </c>
-      <c r="J246" t="s">
+      <c r="J246" t="s" s="0">
         <v>1224</v>
       </c>
-      <c r="K246" t="s">
-        <v>243</v>
-      </c>
-      <c r="L246">
+      <c r="K246" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L246" s="0">
         <v>25</v>
       </c>
-      <c r="M246">
+      <c r="M246" s="0">
         <v>127</v>
       </c>
       <c r="N246" s="6">
@@ -14566,16 +14566,16 @@
       <c r="I267" t="s" s="0">
         <v>1226</v>
       </c>
-      <c r="J267" t="s">
+      <c r="J267" t="s" s="0">
         <v>1227</v>
       </c>
-      <c r="K267" t="s">
-        <v>243</v>
-      </c>
-      <c r="L267">
-        <v>0</v>
-      </c>
-      <c r="M267">
+      <c r="K267" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L267" s="0">
+        <v>0</v>
+      </c>
+      <c r="M267" s="0">
         <v>95</v>
       </c>
       <c r="N267" s="6">
@@ -14614,16 +14614,16 @@
       <c r="I268" t="s" s="0">
         <v>1230</v>
       </c>
-      <c r="J268" t="s">
+      <c r="J268" t="s" s="0">
         <v>1231</v>
       </c>
-      <c r="K268" t="s">
-        <v>243</v>
-      </c>
-      <c r="L268">
-        <v>0</v>
-      </c>
-      <c r="M268">
+      <c r="K268" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L268" s="0">
+        <v>0</v>
+      </c>
+      <c r="M268" s="0">
         <v>195</v>
       </c>
       <c r="N268" s="6">
@@ -14662,16 +14662,16 @@
       <c r="I269" t="s" s="0">
         <v>992</v>
       </c>
-      <c r="J269" t="s">
+      <c r="J269" t="s" s="0">
         <v>1233</v>
       </c>
-      <c r="K269" t="s">
-        <v>243</v>
-      </c>
-      <c r="L269">
-        <v>0</v>
-      </c>
-      <c r="M269">
+      <c r="K269" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L269" s="0">
+        <v>0</v>
+      </c>
+      <c r="M269" s="0">
         <v>117</v>
       </c>
       <c r="N269" s="6">
@@ -14752,16 +14752,16 @@
       <c r="I271" t="s" s="0">
         <v>996</v>
       </c>
-      <c r="J271" t="s">
+      <c r="J271" t="s" s="0">
         <v>1236</v>
       </c>
-      <c r="K271" t="s">
-        <v>243</v>
-      </c>
-      <c r="L271">
-        <v>0</v>
-      </c>
-      <c r="M271">
+      <c r="K271" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L271" s="0">
+        <v>0</v>
+      </c>
+      <c r="M271" s="0">
         <v>54</v>
       </c>
       <c r="N271" s="6">
@@ -14800,16 +14800,16 @@
       <c r="I272" t="s" s="0">
         <v>999</v>
       </c>
-      <c r="J272" t="s">
+      <c r="J272" t="s" s="0">
         <v>1238</v>
       </c>
-      <c r="K272" t="s">
+      <c r="K272" t="s" s="0">
         <v>373</v>
       </c>
-      <c r="L272">
-        <v>0</v>
-      </c>
-      <c r="M272">
+      <c r="L272" s="0">
+        <v>0</v>
+      </c>
+      <c r="M272" s="0">
         <v>76</v>
       </c>
       <c r="N272" s="6">
@@ -14848,16 +14848,16 @@
       <c r="I273" t="s" s="0">
         <v>1241</v>
       </c>
-      <c r="J273" t="s">
+      <c r="J273" t="s" s="0">
         <v>1242</v>
       </c>
-      <c r="K273" t="s">
-        <v>243</v>
-      </c>
-      <c r="L273">
-        <v>0</v>
-      </c>
-      <c r="M273">
+      <c r="K273" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L273" s="0">
+        <v>0</v>
+      </c>
+      <c r="M273" s="0">
         <v>67</v>
       </c>
       <c r="N273" s="6">
@@ -14896,16 +14896,16 @@
       <c r="I274" t="s" s="0">
         <v>1002</v>
       </c>
-      <c r="J274" t="s">
+      <c r="J274" t="s" s="0">
         <v>1244</v>
       </c>
-      <c r="K274" t="s">
-        <v>243</v>
-      </c>
-      <c r="L274">
+      <c r="K274" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L274" s="0">
         <v>25</v>
       </c>
-      <c r="M274">
+      <c r="M274" s="0">
         <v>110</v>
       </c>
       <c r="N274" s="6">
@@ -14986,16 +14986,16 @@
       <c r="I276" t="s" s="0">
         <v>1248</v>
       </c>
-      <c r="J276" t="s">
+      <c r="J276" t="s" s="0">
         <v>1249</v>
       </c>
-      <c r="K276" t="s">
-        <v>243</v>
-      </c>
-      <c r="L276">
-        <v>0</v>
-      </c>
-      <c r="M276">
+      <c r="K276" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L276" s="0">
+        <v>0</v>
+      </c>
+      <c r="M276" s="0">
         <v>17</v>
       </c>
       <c r="N276" s="6">
@@ -15146,16 +15146,16 @@
       <c r="I291" t="s" s="0">
         <v>773</v>
       </c>
-      <c r="J291" t="s">
+      <c r="J291" t="s" s="0">
         <v>1251</v>
       </c>
-      <c r="K291" t="s">
-        <v>243</v>
-      </c>
-      <c r="L291">
-        <v>0</v>
-      </c>
-      <c r="M291">
+      <c r="K291" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L291" s="0">
+        <v>0</v>
+      </c>
+      <c r="M291" s="0">
         <v>80</v>
       </c>
       <c r="N291" s="6">
@@ -15196,16 +15196,16 @@
       <c r="I292" t="s" s="0">
         <v>776</v>
       </c>
-      <c r="J292" t="s">
+      <c r="J292" t="s" s="0">
         <v>1253</v>
       </c>
-      <c r="K292" t="s">
-        <v>243</v>
-      </c>
-      <c r="L292">
-        <v>0</v>
-      </c>
-      <c r="M292">
+      <c r="K292" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L292" s="0">
+        <v>0</v>
+      </c>
+      <c r="M292" s="0">
         <v>10</v>
       </c>
       <c r="N292" s="6">
@@ -15246,16 +15246,16 @@
       <c r="I293" t="s" s="0">
         <v>1011</v>
       </c>
-      <c r="J293" t="s">
+      <c r="J293" t="s" s="0">
         <v>1255</v>
       </c>
-      <c r="K293" t="s">
-        <v>243</v>
-      </c>
-      <c r="L293">
+      <c r="K293" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L293" s="0">
         <v>50</v>
       </c>
-      <c r="M293">
+      <c r="M293" s="0">
         <v>650</v>
       </c>
       <c r="N293" s="6">
@@ -15340,16 +15340,16 @@
       <c r="I295" t="s" s="0">
         <v>783</v>
       </c>
-      <c r="J295" t="s">
+      <c r="J295" t="s" s="0">
         <v>1258</v>
       </c>
-      <c r="K295" t="s">
-        <v>243</v>
-      </c>
-      <c r="L295">
+      <c r="K295" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L295" s="0">
         <v>25</v>
       </c>
-      <c r="M295">
+      <c r="M295" s="0">
         <v>150</v>
       </c>
       <c r="N295" s="6">
@@ -15390,16 +15390,16 @@
       <c r="I296" t="s" s="0">
         <v>786</v>
       </c>
-      <c r="J296" t="s">
+      <c r="J296" t="s" s="0">
         <v>1260</v>
       </c>
-      <c r="K296" t="s">
-        <v>243</v>
-      </c>
-      <c r="L296">
-        <v>0</v>
-      </c>
-      <c r="M296">
+      <c r="K296" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L296" s="0">
+        <v>0</v>
+      </c>
+      <c r="M296" s="0">
         <v>50</v>
       </c>
       <c r="N296" s="6">
@@ -15440,16 +15440,16 @@
       <c r="I297" t="s" s="0">
         <v>790</v>
       </c>
-      <c r="J297" t="s">
+      <c r="J297" t="s" s="0">
         <v>1262</v>
       </c>
-      <c r="K297" t="s">
-        <v>243</v>
-      </c>
-      <c r="L297">
+      <c r="K297" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L297" s="0">
         <v>25</v>
       </c>
-      <c r="M297">
+      <c r="M297" s="0">
         <v>51</v>
       </c>
       <c r="N297" s="6">
@@ -15490,16 +15490,16 @@
       <c r="I298" t="s" s="0">
         <v>1265</v>
       </c>
-      <c r="J298" t="s">
+      <c r="J298" t="s" s="0">
         <v>1266</v>
       </c>
-      <c r="K298" t="s">
-        <v>243</v>
-      </c>
-      <c r="L298">
-        <v>0</v>
-      </c>
-      <c r="M298">
+      <c r="K298" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L298" s="0">
+        <v>0</v>
+      </c>
+      <c r="M298" s="0">
         <v>137</v>
       </c>
       <c r="N298" s="6">
@@ -15540,16 +15540,16 @@
       <c r="I299" t="s" s="0">
         <v>795</v>
       </c>
-      <c r="J299" t="s">
+      <c r="J299" t="s" s="0">
         <v>1268</v>
       </c>
-      <c r="K299" t="s">
-        <v>243</v>
-      </c>
-      <c r="L299">
-        <v>0</v>
-      </c>
-      <c r="M299">
+      <c r="K299" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L299" s="0">
+        <v>0</v>
+      </c>
+      <c r="M299" s="0">
         <v>43</v>
       </c>
       <c r="N299" s="6">
@@ -15590,16 +15590,16 @@
       <c r="I300" t="s" s="0">
         <v>1270</v>
       </c>
-      <c r="J300" t="s">
+      <c r="J300" t="s" s="0">
         <v>1271</v>
       </c>
-      <c r="K300" t="s">
-        <v>243</v>
-      </c>
-      <c r="L300">
+      <c r="K300" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L300" s="0">
         <v>25</v>
       </c>
-      <c r="M300">
+      <c r="M300" s="0">
         <v>187</v>
       </c>
       <c r="N300" s="6">
@@ -15684,16 +15684,16 @@
       <c r="I302" t="s" s="0">
         <v>1036</v>
       </c>
-      <c r="J302" t="s">
+      <c r="J302" t="s" s="0">
         <v>1274</v>
       </c>
-      <c r="K302" t="s">
-        <v>243</v>
-      </c>
-      <c r="L302">
-        <v>0</v>
-      </c>
-      <c r="M302">
+      <c r="K302" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L302" s="0">
+        <v>0</v>
+      </c>
+      <c r="M302" s="0">
         <v>179</v>
       </c>
       <c r="N302" s="6">
@@ -15734,16 +15734,16 @@
       <c r="I303" t="s" s="0">
         <v>1277</v>
       </c>
-      <c r="J303" t="s">
+      <c r="J303" t="s" s="0">
         <v>1278</v>
       </c>
-      <c r="K303" t="s">
-        <v>243</v>
-      </c>
-      <c r="L303">
+      <c r="K303" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L303" s="0">
         <v>25</v>
       </c>
-      <c r="M303">
+      <c r="M303" s="0">
         <v>48</v>
       </c>
       <c r="N303" s="6">
@@ -15795,16 +15795,16 @@
       <c r="I305" t="s" s="0">
         <v>1040</v>
       </c>
-      <c r="J305" t="s">
+      <c r="J305" t="s" s="0">
         <v>1280</v>
       </c>
-      <c r="K305" t="s">
-        <v>243</v>
-      </c>
-      <c r="L305">
-        <v>0</v>
-      </c>
-      <c r="M305">
+      <c r="K305" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L305" s="0">
+        <v>0</v>
+      </c>
+      <c r="M305" s="0">
         <v>140</v>
       </c>
       <c r="N305" s="6">
@@ -15845,16 +15845,16 @@
       <c r="I306" t="s" s="0">
         <v>1283</v>
       </c>
-      <c r="J306" t="s">
+      <c r="J306" t="s" s="0">
         <v>1284</v>
       </c>
-      <c r="K306" t="s">
-        <v>243</v>
-      </c>
-      <c r="L306">
-        <v>0</v>
-      </c>
-      <c r="M306">
+      <c r="K306" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L306" s="0">
+        <v>0</v>
+      </c>
+      <c r="M306" s="0">
         <v>83</v>
       </c>
       <c r="N306" s="6">
@@ -15895,16 +15895,16 @@
       <c r="I307" t="s" s="0">
         <v>1045</v>
       </c>
-      <c r="J307" t="s">
+      <c r="J307" t="s" s="0">
         <v>1286</v>
       </c>
-      <c r="K307" t="s">
-        <v>243</v>
-      </c>
-      <c r="L307">
-        <v>0</v>
-      </c>
-      <c r="M307">
+      <c r="K307" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L307" s="0">
+        <v>0</v>
+      </c>
+      <c r="M307" s="0">
         <v>122</v>
       </c>
       <c r="N307" s="6">
@@ -15945,16 +15945,16 @@
       <c r="I308" t="s" s="0">
         <v>1048</v>
       </c>
-      <c r="J308" t="s">
+      <c r="J308" t="s" s="0">
         <v>1288</v>
       </c>
-      <c r="K308" t="s">
-        <v>243</v>
-      </c>
-      <c r="L308">
+      <c r="K308" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L308" s="0">
         <v>25</v>
       </c>
-      <c r="M308">
+      <c r="M308" s="0">
         <v>153</v>
       </c>
       <c r="N308" s="6">
@@ -15995,16 +15995,16 @@
       <c r="I309" t="s" s="0">
         <v>1290</v>
       </c>
-      <c r="J309" t="s">
+      <c r="J309" t="s" s="0">
         <v>1291</v>
       </c>
-      <c r="K309" t="s">
-        <v>243</v>
-      </c>
-      <c r="L309">
-        <v>0</v>
-      </c>
-      <c r="M309">
+      <c r="K309" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L309" s="0">
+        <v>0</v>
+      </c>
+      <c r="M309" s="0">
         <v>100</v>
       </c>
       <c r="N309" s="6">
@@ -16045,16 +16045,16 @@
       <c r="I310" t="s" s="0">
         <v>808</v>
       </c>
-      <c r="J310" t="s">
+      <c r="J310" t="s" s="0">
         <v>1292</v>
       </c>
-      <c r="K310" t="s">
-        <v>243</v>
-      </c>
-      <c r="L310">
-        <v>0</v>
-      </c>
-      <c r="M310">
+      <c r="K310" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L310" s="0">
+        <v>0</v>
+      </c>
+      <c r="M310" s="0">
         <v>122</v>
       </c>
       <c r="N310" s="6">
@@ -16092,16 +16092,16 @@
       <c r="I311" t="s" s="0">
         <v>1295</v>
       </c>
-      <c r="J311" t="s">
+      <c r="J311" t="s" s="0">
         <v>1296</v>
       </c>
-      <c r="K311" t="s">
-        <v>243</v>
-      </c>
-      <c r="L311">
+      <c r="K311" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L311" s="0">
         <v>25</v>
       </c>
-      <c r="M311">
+      <c r="M311" s="0">
         <v>74</v>
       </c>
       <c r="N311" s="6">
@@ -16139,16 +16139,16 @@
       <c r="I312" t="s" s="0">
         <v>1298</v>
       </c>
-      <c r="J312" t="s">
+      <c r="J312" t="s" s="0">
         <v>1299</v>
       </c>
-      <c r="K312" t="s">
-        <v>243</v>
-      </c>
-      <c r="L312">
-        <v>0</v>
-      </c>
-      <c r="M312">
+      <c r="K312" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L312" s="0">
+        <v>0</v>
+      </c>
+      <c r="M312" s="0">
         <v>200</v>
       </c>
       <c r="N312" s="6">
@@ -16186,16 +16186,16 @@
       <c r="I313" t="s" s="0">
         <v>814</v>
       </c>
-      <c r="J313" t="s">
+      <c r="J313" t="s" s="0">
         <v>1301</v>
       </c>
-      <c r="K313" t="s">
-        <v>243</v>
-      </c>
-      <c r="L313">
-        <v>0</v>
-      </c>
-      <c r="M313">
+      <c r="K313" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L313" s="0">
+        <v>0</v>
+      </c>
+      <c r="M313" s="0">
         <v>177</v>
       </c>
       <c r="N313" s="6">
@@ -16233,16 +16233,16 @@
       <c r="I314" t="s" s="0">
         <v>1304</v>
       </c>
-      <c r="J314" t="s">
+      <c r="J314" t="s" s="0">
         <v>1305</v>
       </c>
-      <c r="K314" t="s">
-        <v>243</v>
-      </c>
-      <c r="L314">
+      <c r="K314" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L314" s="0">
         <v>25</v>
       </c>
-      <c r="M314">
+      <c r="M314" s="0">
         <v>42</v>
       </c>
       <c r="N314" s="6">
@@ -16294,16 +16294,16 @@
       <c r="I316" t="s" s="0">
         <v>820</v>
       </c>
-      <c r="J316" t="s">
+      <c r="J316" t="s" s="0">
         <v>1307</v>
       </c>
-      <c r="K316" t="s">
-        <v>243</v>
-      </c>
-      <c r="L316">
-        <v>0</v>
-      </c>
-      <c r="M316">
+      <c r="K316" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L316" s="0">
+        <v>0</v>
+      </c>
+      <c r="M316" s="0">
         <v>88</v>
       </c>
       <c r="N316" s="6">
@@ -16344,16 +16344,16 @@
       <c r="I317" t="s" s="0">
         <v>1068</v>
       </c>
-      <c r="J317" t="s">
+      <c r="J317" t="s" s="0">
         <v>1309</v>
       </c>
-      <c r="K317" t="s">
-        <v>243</v>
-      </c>
-      <c r="L317">
+      <c r="K317" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L317" s="0">
         <v>25</v>
       </c>
-      <c r="M317">
+      <c r="M317" s="0">
         <v>101</v>
       </c>
       <c r="N317" s="6">
@@ -16394,16 +16394,16 @@
       <c r="I318" t="s" s="0">
         <v>826</v>
       </c>
-      <c r="J318" t="s">
+      <c r="J318" t="s" s="0">
         <v>1311</v>
       </c>
-      <c r="K318" t="s">
-        <v>243</v>
-      </c>
-      <c r="L318">
-        <v>0</v>
-      </c>
-      <c r="M318">
+      <c r="K318" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L318" s="0">
+        <v>0</v>
+      </c>
+      <c r="M318" s="0">
         <v>10</v>
       </c>
       <c r="N318" s="6">
@@ -16444,16 +16444,16 @@
       <c r="I319" t="s" s="0">
         <v>828</v>
       </c>
-      <c r="J319" t="s">
+      <c r="J319" t="s" s="0">
         <v>1313</v>
       </c>
-      <c r="K319" t="s">
-        <v>243</v>
-      </c>
-      <c r="L319">
-        <v>0</v>
-      </c>
-      <c r="M319">
+      <c r="K319" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L319" s="0">
+        <v>0</v>
+      </c>
+      <c r="M319" s="0">
         <v>78</v>
       </c>
       <c r="N319" s="6">
@@ -16494,16 +16494,16 @@
       <c r="I320" t="s" s="0">
         <v>1076</v>
       </c>
-      <c r="J320" t="s">
+      <c r="J320" t="s" s="0">
         <v>1315</v>
       </c>
-      <c r="K320" t="s">
-        <v>243</v>
-      </c>
-      <c r="L320">
-        <v>0</v>
-      </c>
-      <c r="M320">
+      <c r="K320" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L320" s="0">
+        <v>0</v>
+      </c>
+      <c r="M320" s="0">
         <v>71</v>
       </c>
       <c r="N320" s="6">
@@ -16544,16 +16544,16 @@
       <c r="I321" t="s" s="0">
         <v>834</v>
       </c>
-      <c r="J321" t="s">
+      <c r="J321" t="s" s="0">
         <v>1317</v>
       </c>
-      <c r="K321" t="s">
-        <v>243</v>
-      </c>
-      <c r="L321">
-        <v>0</v>
-      </c>
-      <c r="M321">
+      <c r="K321" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L321" s="0">
+        <v>0</v>
+      </c>
+      <c r="M321" s="0">
         <v>113</v>
       </c>
       <c r="N321" s="6">
@@ -16627,16 +16627,16 @@
       <c r="I325" t="s" s="0">
         <v>838</v>
       </c>
-      <c r="J325" t="s">
+      <c r="J325" t="s" s="0">
         <v>1319</v>
       </c>
-      <c r="K325" t="s">
-        <v>243</v>
-      </c>
-      <c r="L325">
+      <c r="K325" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L325" s="0">
         <v>25</v>
       </c>
-      <c r="M325">
+      <c r="M325" s="0">
         <v>10</v>
       </c>
       <c r="N325" s="6">
@@ -16675,16 +16675,16 @@
       <c r="I326" t="s" s="0">
         <v>842</v>
       </c>
-      <c r="J326" t="s">
+      <c r="J326" t="s" s="0">
         <v>1321</v>
       </c>
-      <c r="K326" t="s">
-        <v>243</v>
-      </c>
-      <c r="L326">
-        <v>0</v>
-      </c>
-      <c r="M326">
+      <c r="K326" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L326" s="0">
+        <v>0</v>
+      </c>
+      <c r="M326" s="0">
         <v>50</v>
       </c>
       <c r="N326" s="6">
@@ -16723,16 +16723,16 @@
       <c r="I327" t="s" s="0">
         <v>1323</v>
       </c>
-      <c r="J327" t="s">
+      <c r="J327" t="s" s="0">
         <v>1324</v>
       </c>
-      <c r="K327" t="s">
-        <v>243</v>
-      </c>
-      <c r="L327">
-        <v>0</v>
-      </c>
-      <c r="M327">
+      <c r="K327" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L327" s="0">
+        <v>0</v>
+      </c>
+      <c r="M327" s="0">
         <v>141</v>
       </c>
       <c r="N327" s="6">
@@ -16771,16 +16771,16 @@
       <c r="I328" t="s" s="0">
         <v>847</v>
       </c>
-      <c r="J328" t="s">
+      <c r="J328" t="s" s="0">
         <v>1326</v>
       </c>
-      <c r="K328" t="s">
-        <v>243</v>
-      </c>
-      <c r="L328">
-        <v>0</v>
-      </c>
-      <c r="M328">
+      <c r="K328" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L328" s="0">
+        <v>0</v>
+      </c>
+      <c r="M328" s="0">
         <v>500</v>
       </c>
       <c r="N328" s="6">
@@ -16819,16 +16819,16 @@
       <c r="I329" t="s" s="0">
         <v>851</v>
       </c>
-      <c r="J329" t="s">
+      <c r="J329" t="s" s="0">
         <v>1328</v>
       </c>
-      <c r="K329" t="s">
-        <v>243</v>
-      </c>
-      <c r="L329">
-        <v>0</v>
-      </c>
-      <c r="M329">
+      <c r="K329" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L329" s="0">
+        <v>0</v>
+      </c>
+      <c r="M329" s="0">
         <v>120</v>
       </c>
       <c r="N329" s="6">
@@ -16867,16 +16867,16 @@
       <c r="I330" t="s" s="0">
         <v>855</v>
       </c>
-      <c r="J330" t="s">
+      <c r="J330" t="s" s="0">
         <v>1330</v>
       </c>
-      <c r="K330" t="s">
-        <v>243</v>
-      </c>
-      <c r="L330">
+      <c r="K330" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L330" s="0">
         <v>50</v>
       </c>
-      <c r="M330">
+      <c r="M330" s="0">
         <v>30</v>
       </c>
       <c r="N330" s="6">
@@ -16915,16 +16915,16 @@
       <c r="I331" t="s" s="0">
         <v>1333</v>
       </c>
-      <c r="J331" t="s">
+      <c r="J331" t="s" s="0">
         <v>1334</v>
       </c>
-      <c r="K331" t="s">
-        <v>243</v>
-      </c>
-      <c r="L331">
-        <v>0</v>
-      </c>
-      <c r="M331">
+      <c r="K331" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L331" s="0">
+        <v>0</v>
+      </c>
+      <c r="M331" s="0">
         <v>118</v>
       </c>
       <c r="N331" s="6">
@@ -16963,16 +16963,16 @@
       <c r="I332" t="s" s="0">
         <v>862</v>
       </c>
-      <c r="J332" t="s">
+      <c r="J332" t="s" s="0">
         <v>1336</v>
       </c>
-      <c r="K332" t="s">
-        <v>243</v>
-      </c>
-      <c r="L332">
-        <v>0</v>
-      </c>
-      <c r="M332">
+      <c r="K332" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L332" s="0">
+        <v>0</v>
+      </c>
+      <c r="M332" s="0">
         <v>154</v>
       </c>
       <c r="N332" s="6">
@@ -17011,16 +17011,16 @@
       <c r="I333" t="s" s="0">
         <v>865</v>
       </c>
-      <c r="J333" t="s">
+      <c r="J333" t="s" s="0">
         <v>1338</v>
       </c>
-      <c r="K333" t="s">
-        <v>243</v>
-      </c>
-      <c r="L333">
-        <v>0</v>
-      </c>
-      <c r="M333">
+      <c r="K333" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L333" s="0">
+        <v>0</v>
+      </c>
+      <c r="M333" s="0">
         <v>57</v>
       </c>
       <c r="N333" s="6">
@@ -17059,16 +17059,16 @@
       <c r="I334" t="s" s="0">
         <v>868</v>
       </c>
-      <c r="J334" t="s">
+      <c r="J334" t="s" s="0">
         <v>1340</v>
       </c>
-      <c r="K334" t="s">
-        <v>243</v>
-      </c>
-      <c r="L334">
-        <v>0</v>
-      </c>
-      <c r="M334">
+      <c r="K334" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L334" s="0">
+        <v>0</v>
+      </c>
+      <c r="M334" s="0">
         <v>99</v>
       </c>
       <c r="N334" s="6">
@@ -17107,16 +17107,16 @@
       <c r="I335" t="s" s="0">
         <v>1343</v>
       </c>
-      <c r="J335" t="s">
+      <c r="J335" t="s" s="0">
         <v>1344</v>
       </c>
-      <c r="K335" t="s">
-        <v>243</v>
-      </c>
-      <c r="L335">
-        <v>0</v>
-      </c>
-      <c r="M335">
+      <c r="K335" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L335" s="0">
+        <v>0</v>
+      </c>
+      <c r="M335" s="0">
         <v>65</v>
       </c>
       <c r="N335" s="6">
@@ -17155,16 +17155,16 @@
       <c r="I336" t="s" s="0">
         <v>874</v>
       </c>
-      <c r="J336" t="s">
+      <c r="J336" t="s" s="0">
         <v>1346</v>
       </c>
-      <c r="K336" t="s">
-        <v>243</v>
-      </c>
-      <c r="L336">
-        <v>0</v>
-      </c>
-      <c r="M336">
+      <c r="K336" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L336" s="0">
+        <v>0</v>
+      </c>
+      <c r="M336" s="0">
         <v>94</v>
       </c>
       <c r="N336" s="6">
@@ -17203,16 +17203,16 @@
       <c r="I337" t="s" s="0">
         <v>877</v>
       </c>
-      <c r="J337" t="s">
+      <c r="J337" t="s" s="0">
         <v>1348</v>
       </c>
-      <c r="K337" t="s">
-        <v>243</v>
-      </c>
-      <c r="L337">
+      <c r="K337" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L337" s="0">
         <v>25</v>
       </c>
-      <c r="M337">
+      <c r="M337" s="0">
         <v>41</v>
       </c>
       <c r="N337" s="6">
@@ -17251,16 +17251,16 @@
       <c r="I338" t="s" s="0">
         <v>880</v>
       </c>
-      <c r="J338" t="s">
+      <c r="J338" t="s" s="0">
         <v>1350</v>
       </c>
-      <c r="K338" t="s">
-        <v>243</v>
-      </c>
-      <c r="L338">
-        <v>0</v>
-      </c>
-      <c r="M338">
+      <c r="K338" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L338" s="0">
+        <v>0</v>
+      </c>
+      <c r="M338" s="0">
         <v>192</v>
       </c>
       <c r="N338" s="6">
@@ -17299,16 +17299,16 @@
       <c r="I339" t="s" s="0">
         <v>1115</v>
       </c>
-      <c r="J339" t="s">
+      <c r="J339" t="s" s="0">
         <v>1352</v>
       </c>
-      <c r="K339" t="s">
-        <v>243</v>
-      </c>
-      <c r="L339">
-        <v>0</v>
-      </c>
-      <c r="M339">
+      <c r="K339" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L339" s="0">
+        <v>0</v>
+      </c>
+      <c r="M339" s="0">
         <v>88</v>
       </c>
       <c r="N339" s="6">
@@ -17347,16 +17347,16 @@
       <c r="I340" t="s" s="0">
         <v>883</v>
       </c>
-      <c r="J340" t="s">
+      <c r="J340" t="s" s="0">
         <v>1353</v>
       </c>
-      <c r="K340" t="s">
-        <v>243</v>
-      </c>
-      <c r="L340">
+      <c r="K340" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L340" s="0">
         <v>25</v>
       </c>
-      <c r="M340">
+      <c r="M340" s="0">
         <v>157</v>
       </c>
       <c r="N340" s="6">
@@ -17437,16 +17437,16 @@
       <c r="I342" t="s" s="0">
         <v>889</v>
       </c>
-      <c r="J342" t="s">
+      <c r="J342" t="s" s="0">
         <v>1356</v>
       </c>
-      <c r="K342" t="s">
-        <v>243</v>
-      </c>
-      <c r="L342">
-        <v>0</v>
-      </c>
-      <c r="M342">
+      <c r="K342" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L342" s="0">
+        <v>0</v>
+      </c>
+      <c r="M342" s="0">
         <v>184</v>
       </c>
       <c r="N342" s="6">
@@ -17485,16 +17485,16 @@
       <c r="I343" t="s" s="0">
         <v>1358</v>
       </c>
-      <c r="J343" t="s">
+      <c r="J343" t="s" s="0">
         <v>1359</v>
       </c>
-      <c r="K343" t="s">
-        <v>243</v>
-      </c>
-      <c r="L343">
+      <c r="K343" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L343" s="0">
         <v>25</v>
       </c>
-      <c r="M343">
+      <c r="M343" s="0">
         <v>76</v>
       </c>
       <c r="N343" s="6">
@@ -17619,16 +17619,16 @@
       <c r="I349" t="s" s="0">
         <v>895</v>
       </c>
-      <c r="J349" t="s">
+      <c r="J349" t="s" s="0">
         <v>1361</v>
       </c>
-      <c r="K349" t="s">
-        <v>243</v>
-      </c>
-      <c r="L349">
-        <v>0</v>
-      </c>
-      <c r="M349">
+      <c r="K349" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L349" s="0">
+        <v>0</v>
+      </c>
+      <c r="M349" s="0">
         <v>27</v>
       </c>
       <c r="N349" s="6">
@@ -17667,16 +17667,16 @@
       <c r="I350" t="s" s="0">
         <v>898</v>
       </c>
-      <c r="J350" t="s">
+      <c r="J350" t="s" s="0">
         <v>1363</v>
       </c>
-      <c r="K350" t="s">
-        <v>243</v>
-      </c>
-      <c r="L350">
-        <v>0</v>
-      </c>
-      <c r="M350">
+      <c r="K350" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L350" s="0">
+        <v>0</v>
+      </c>
+      <c r="M350" s="0">
         <v>167</v>
       </c>
       <c r="N350" s="6">
@@ -17715,16 +17715,16 @@
       <c r="I351" t="s" s="0">
         <v>901</v>
       </c>
-      <c r="J351" t="s">
+      <c r="J351" t="s" s="0">
         <v>1364</v>
       </c>
-      <c r="K351" t="s">
-        <v>243</v>
-      </c>
-      <c r="L351">
+      <c r="K351" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L351" s="0">
         <v>25</v>
       </c>
-      <c r="M351">
+      <c r="M351" s="0">
         <v>82</v>
       </c>
       <c r="N351" s="6">
@@ -17763,16 +17763,16 @@
       <c r="I352" t="s" s="0">
         <v>1367</v>
       </c>
-      <c r="J352" t="s">
+      <c r="J352" t="s" s="0">
         <v>1368</v>
       </c>
-      <c r="K352" t="s">
-        <v>243</v>
-      </c>
-      <c r="L352">
-        <v>0</v>
-      </c>
-      <c r="M352">
+      <c r="K352" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L352" s="0">
+        <v>0</v>
+      </c>
+      <c r="M352" s="0">
         <v>122</v>
       </c>
       <c r="N352" s="6">
@@ -17808,16 +17808,16 @@
       <c r="I353" t="s" s="0">
         <v>907</v>
       </c>
-      <c r="J353" t="s">
+      <c r="J353" t="s" s="0">
         <v>1370</v>
       </c>
-      <c r="K353" t="s">
-        <v>243</v>
-      </c>
-      <c r="L353">
-        <v>0</v>
-      </c>
-      <c r="M353">
+      <c r="K353" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L353" s="0">
+        <v>0</v>
+      </c>
+      <c r="M353" s="0">
         <v>92</v>
       </c>
       <c r="N353" s="6">
@@ -17853,16 +17853,16 @@
       <c r="I354" t="s" s="0">
         <v>910</v>
       </c>
-      <c r="J354" t="s">
+      <c r="J354" t="s" s="0">
         <v>1372</v>
       </c>
-      <c r="K354" t="s">
-        <v>243</v>
-      </c>
-      <c r="L354">
-        <v>0</v>
-      </c>
-      <c r="M354">
+      <c r="K354" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L354" s="0">
+        <v>0</v>
+      </c>
+      <c r="M354" s="0">
         <v>28</v>
       </c>
       <c r="N354" s="6">
@@ -17898,16 +17898,16 @@
       <c r="I355" t="s" s="0">
         <v>913</v>
       </c>
-      <c r="J355" t="s">
+      <c r="J355" t="s" s="0">
         <v>1374</v>
       </c>
-      <c r="K355" t="s">
-        <v>243</v>
-      </c>
-      <c r="L355">
-        <v>0</v>
-      </c>
-      <c r="M355">
+      <c r="K355" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L355" s="0">
+        <v>0</v>
+      </c>
+      <c r="M355" s="0">
         <v>6</v>
       </c>
       <c r="N355" s="6">
@@ -17946,16 +17946,16 @@
       <c r="I356" t="s" s="0">
         <v>1143</v>
       </c>
-      <c r="J356" t="s">
+      <c r="J356" t="s" s="0">
         <v>1376</v>
       </c>
-      <c r="K356" t="s">
-        <v>243</v>
-      </c>
-      <c r="L356">
-        <v>0</v>
-      </c>
-      <c r="M356">
+      <c r="K356" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L356" s="0">
+        <v>0</v>
+      </c>
+      <c r="M356" s="0">
         <v>200</v>
       </c>
       <c r="N356" s="6">
@@ -17994,16 +17994,16 @@
       <c r="I357" t="s" s="0">
         <v>1379</v>
       </c>
-      <c r="J357" t="s">
+      <c r="J357" t="s" s="0">
         <v>1380</v>
       </c>
-      <c r="K357" t="s">
-        <v>243</v>
-      </c>
-      <c r="L357">
-        <v>0</v>
-      </c>
-      <c r="M357">
+      <c r="K357" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L357" s="0">
+        <v>0</v>
+      </c>
+      <c r="M357" s="0">
         <v>23</v>
       </c>
       <c r="N357" s="6">
@@ -18042,16 +18042,16 @@
       <c r="I358" t="s" s="0">
         <v>917</v>
       </c>
-      <c r="J358" t="s">
+      <c r="J358" t="s" s="0">
         <v>1382</v>
       </c>
-      <c r="K358" t="s">
-        <v>243</v>
-      </c>
-      <c r="L358">
+      <c r="K358" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L358" s="0">
         <v>25</v>
       </c>
-      <c r="M358">
+      <c r="M358" s="0">
         <v>183</v>
       </c>
       <c r="N358" s="6">
@@ -18090,16 +18090,16 @@
       <c r="I359" t="s" s="0">
         <v>919</v>
       </c>
-      <c r="J359" t="s">
+      <c r="J359" t="s" s="0">
         <v>1384</v>
       </c>
-      <c r="K359" t="s">
-        <v>243</v>
-      </c>
-      <c r="L359">
-        <v>0</v>
-      </c>
-      <c r="M359">
+      <c r="K359" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L359" s="0">
+        <v>0</v>
+      </c>
+      <c r="M359" s="0">
         <v>73</v>
       </c>
       <c r="N359" s="6">
@@ -18138,16 +18138,16 @@
       <c r="I360" t="s" s="0">
         <v>895</v>
       </c>
-      <c r="J360" t="s">
+      <c r="J360" t="s" s="0">
         <v>1385</v>
       </c>
-      <c r="K360" t="s">
-        <v>243</v>
-      </c>
-      <c r="L360">
-        <v>0</v>
-      </c>
-      <c r="M360">
+      <c r="K360" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L360" s="0">
+        <v>0</v>
+      </c>
+      <c r="M360" s="0">
         <v>180</v>
       </c>
       <c r="N360" s="6">
@@ -18186,16 +18186,16 @@
       <c r="I361" t="s" s="0">
         <v>923</v>
       </c>
-      <c r="J361" t="s">
+      <c r="J361" t="s" s="0">
         <v>1387</v>
       </c>
-      <c r="K361" t="s">
-        <v>243</v>
-      </c>
-      <c r="L361">
-        <v>0</v>
-      </c>
-      <c r="M361">
+      <c r="K361" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L361" s="0">
+        <v>0</v>
+      </c>
+      <c r="M361" s="0">
         <v>187</v>
       </c>
       <c r="N361" s="6">
@@ -18234,16 +18234,16 @@
       <c r="I362" t="s" s="0">
         <v>926</v>
       </c>
-      <c r="J362" t="s">
+      <c r="J362" t="s" s="0">
         <v>1389</v>
       </c>
-      <c r="K362" t="s">
-        <v>243</v>
-      </c>
-      <c r="L362">
-        <v>0</v>
-      </c>
-      <c r="M362">
+      <c r="K362" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L362" s="0">
+        <v>0</v>
+      </c>
+      <c r="M362" s="0">
         <v>18</v>
       </c>
       <c r="N362" s="6">
@@ -18282,16 +18282,16 @@
       <c r="I363" t="s" s="0">
         <v>1392</v>
       </c>
-      <c r="J363" t="s">
+      <c r="J363" t="s" s="0">
         <v>1393</v>
       </c>
-      <c r="K363" t="s">
-        <v>243</v>
-      </c>
-      <c r="L363">
+      <c r="K363" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L363" s="0">
         <v>25</v>
       </c>
-      <c r="M363">
+      <c r="M363" s="0">
         <v>109</v>
       </c>
       <c r="N363" s="6">
@@ -18330,16 +18330,16 @@
       <c r="I364" t="s" s="0">
         <v>932</v>
       </c>
-      <c r="J364" t="s">
+      <c r="J364" t="s" s="0">
         <v>1395</v>
       </c>
-      <c r="K364" t="s">
-        <v>243</v>
-      </c>
-      <c r="L364">
-        <v>0</v>
-      </c>
-      <c r="M364">
+      <c r="K364" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L364" s="0">
+        <v>0</v>
+      </c>
+      <c r="M364" s="0">
         <v>12</v>
       </c>
       <c r="N364" s="6">
@@ -18378,16 +18378,16 @@
       <c r="I365" t="s" s="0">
         <v>935</v>
       </c>
-      <c r="J365" t="s">
+      <c r="J365" t="s" s="0">
         <v>1397</v>
       </c>
-      <c r="K365" t="s">
-        <v>243</v>
-      </c>
-      <c r="L365">
-        <v>0</v>
-      </c>
-      <c r="M365">
+      <c r="K365" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L365" s="0">
+        <v>0</v>
+      </c>
+      <c r="M365" s="0">
         <v>174</v>
       </c>
       <c r="N365" s="6">
@@ -18479,16 +18479,16 @@
       <c r="I368" t="s" s="0">
         <v>938</v>
       </c>
-      <c r="J368" t="s">
+      <c r="J368" t="s" s="0">
         <v>1400</v>
       </c>
-      <c r="K368" t="s">
-        <v>243</v>
-      </c>
-      <c r="L368">
-        <v>0</v>
-      </c>
-      <c r="M368">
+      <c r="K368" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L368" s="0">
+        <v>0</v>
+      </c>
+      <c r="M368" s="0">
         <v>121</v>
       </c>
       <c r="N368" s="6">
@@ -18573,16 +18573,16 @@
       <c r="I370" t="s" s="0">
         <v>943</v>
       </c>
-      <c r="J370" t="s">
+      <c r="J370" t="s" s="0">
         <v>1402</v>
       </c>
-      <c r="K370" t="s">
-        <v>243</v>
-      </c>
-      <c r="L370">
-        <v>0</v>
-      </c>
-      <c r="M370">
+      <c r="K370" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L370" s="0">
+        <v>0</v>
+      </c>
+      <c r="M370" s="0">
         <v>139</v>
       </c>
       <c r="N370" s="6">
@@ -18623,16 +18623,16 @@
       <c r="I371" t="s" s="0">
         <v>946</v>
       </c>
-      <c r="J371" t="s">
+      <c r="J371" t="s" s="0">
         <v>1404</v>
       </c>
-      <c r="K371" t="s">
-        <v>243</v>
-      </c>
-      <c r="L371">
-        <v>0</v>
-      </c>
-      <c r="M371">
+      <c r="K371" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L371" s="0">
+        <v>0</v>
+      </c>
+      <c r="M371" s="0">
         <v>6</v>
       </c>
       <c r="N371" s="6">
@@ -18673,16 +18673,16 @@
       <c r="I372" t="s" s="0">
         <v>1407</v>
       </c>
-      <c r="J372" t="s">
+      <c r="J372" t="s" s="0">
         <v>1408</v>
       </c>
-      <c r="K372" t="s">
-        <v>243</v>
-      </c>
-      <c r="L372">
-        <v>0</v>
-      </c>
-      <c r="M372">
+      <c r="K372" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L372" s="0">
+        <v>0</v>
+      </c>
+      <c r="M372" s="0">
         <v>63</v>
       </c>
       <c r="N372" s="6">
@@ -18775,16 +18775,16 @@
       <c r="I375" t="s" s="0">
         <v>953</v>
       </c>
-      <c r="J375" t="s">
+      <c r="J375" t="s" s="0">
         <v>1411</v>
       </c>
-      <c r="K375" t="s">
-        <v>243</v>
-      </c>
-      <c r="L375">
+      <c r="K375" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L375" s="0">
         <v>25</v>
       </c>
-      <c r="M375">
+      <c r="M375" s="0">
         <v>170</v>
       </c>
       <c r="N375" s="6">
@@ -18825,16 +18825,16 @@
       <c r="I376" t="s" s="0">
         <v>956</v>
       </c>
-      <c r="J376" t="s">
+      <c r="J376" t="s" s="0">
         <v>1413</v>
       </c>
-      <c r="K376" t="s">
-        <v>243</v>
-      </c>
-      <c r="L376">
-        <v>0</v>
-      </c>
-      <c r="M376">
+      <c r="K376" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L376" s="0">
+        <v>0</v>
+      </c>
+      <c r="M376" s="0">
         <v>171</v>
       </c>
       <c r="N376" s="6">
@@ -18875,16 +18875,16 @@
       <c r="I377" t="s" s="0">
         <v>1416</v>
       </c>
-      <c r="J377" t="s">
+      <c r="J377" t="s" s="0">
         <v>1417</v>
       </c>
-      <c r="K377" t="s">
-        <v>243</v>
-      </c>
-      <c r="L377">
-        <v>0</v>
-      </c>
-      <c r="M377">
+      <c r="K377" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L377" s="0">
+        <v>0</v>
+      </c>
+      <c r="M377" s="0">
         <v>93</v>
       </c>
       <c r="N377" s="6">
@@ -18925,16 +18925,16 @@
       <c r="I378" t="s" s="0">
         <v>962</v>
       </c>
-      <c r="J378" t="s">
+      <c r="J378" t="s" s="0">
         <v>1419</v>
       </c>
-      <c r="K378" t="s">
-        <v>243</v>
-      </c>
-      <c r="L378">
-        <v>0</v>
-      </c>
-      <c r="M378">
+      <c r="K378" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L378" s="0">
+        <v>0</v>
+      </c>
+      <c r="M378" s="0">
         <v>40</v>
       </c>
       <c r="N378" s="6">
@@ -18972,16 +18972,16 @@
       <c r="I379" t="s" s="0">
         <v>1194</v>
       </c>
-      <c r="J379" t="s">
+      <c r="J379" t="s" s="0">
         <v>1421</v>
       </c>
-      <c r="K379" t="s">
-        <v>243</v>
-      </c>
-      <c r="L379">
-        <v>0</v>
-      </c>
-      <c r="M379">
+      <c r="K379" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L379" s="0">
+        <v>0</v>
+      </c>
+      <c r="M379" s="0">
         <v>118</v>
       </c>
       <c r="N379" s="6">
@@ -19022,16 +19022,16 @@
       <c r="I380" t="s" s="0">
         <v>966</v>
       </c>
-      <c r="J380" t="s">
+      <c r="J380" t="s" s="0">
         <v>1422</v>
       </c>
-      <c r="K380" t="s">
-        <v>243</v>
-      </c>
-      <c r="L380">
-        <v>0</v>
-      </c>
-      <c r="M380">
+      <c r="K380" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L380" s="0">
+        <v>0</v>
+      </c>
+      <c r="M380" s="0">
         <v>125</v>
       </c>
       <c r="N380" s="6">
@@ -19072,16 +19072,16 @@
       <c r="I381" t="s" s="0">
         <v>968</v>
       </c>
-      <c r="J381" t="s">
+      <c r="J381" t="s" s="0">
         <v>1424</v>
       </c>
-      <c r="K381" t="s">
-        <v>243</v>
-      </c>
-      <c r="L381">
-        <v>0</v>
-      </c>
-      <c r="M381">
+      <c r="K381" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L381" s="0">
+        <v>0</v>
+      </c>
+      <c r="M381" s="0">
         <v>56</v>
       </c>
       <c r="N381" s="6">
@@ -19122,16 +19122,16 @@
       <c r="I382" t="s" s="0">
         <v>971</v>
       </c>
-      <c r="J382" t="s">
+      <c r="J382" t="s" s="0">
         <v>1426</v>
       </c>
-      <c r="K382" t="s">
-        <v>243</v>
-      </c>
-      <c r="L382">
+      <c r="K382" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L382" s="0">
         <v>25</v>
       </c>
-      <c r="M382">
+      <c r="M382" s="0">
         <v>88</v>
       </c>
       <c r="N382" s="6">
@@ -19172,16 +19172,16 @@
       <c r="I383" t="s" s="0">
         <v>1205</v>
       </c>
-      <c r="J383" t="s">
+      <c r="J383" t="s" s="0">
         <v>1428</v>
       </c>
-      <c r="K383" t="s">
-        <v>243</v>
-      </c>
-      <c r="L383">
-        <v>0</v>
-      </c>
-      <c r="M383">
+      <c r="K383" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L383" s="0">
+        <v>0</v>
+      </c>
+      <c r="M383" s="0">
         <v>116</v>
       </c>
       <c r="N383" s="6">
@@ -19222,16 +19222,16 @@
       <c r="I384" t="s" s="0">
         <v>975</v>
       </c>
-      <c r="J384" t="s">
+      <c r="J384" t="s" s="0">
         <v>1430</v>
       </c>
-      <c r="K384" t="s">
-        <v>243</v>
-      </c>
-      <c r="L384">
-        <v>0</v>
-      </c>
-      <c r="M384">
+      <c r="K384" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L384" s="0">
+        <v>0</v>
+      </c>
+      <c r="M384" s="0">
         <v>31</v>
       </c>
       <c r="N384" s="6">
@@ -19338,16 +19338,16 @@
       <c r="I391" t="s" s="0">
         <v>978</v>
       </c>
-      <c r="J391" t="s">
+      <c r="J391" t="s" s="0">
         <v>1432</v>
       </c>
-      <c r="K391" t="s">
-        <v>243</v>
-      </c>
-      <c r="L391">
-        <v>0</v>
-      </c>
-      <c r="M391">
+      <c r="K391" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L391" s="0">
+        <v>0</v>
+      </c>
+      <c r="M391" s="0">
         <v>17</v>
       </c>
       <c r="N391" s="6">
@@ -19428,16 +19428,16 @@
       <c r="I393" t="s" s="0">
         <v>984</v>
       </c>
-      <c r="J393" t="s">
+      <c r="J393" t="s" s="0">
         <v>1435</v>
       </c>
-      <c r="K393" t="s">
-        <v>243</v>
-      </c>
-      <c r="L393">
-        <v>0</v>
-      </c>
-      <c r="M393">
+      <c r="K393" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L393" s="0">
+        <v>0</v>
+      </c>
+      <c r="M393" s="0">
         <v>135</v>
       </c>
       <c r="N393" s="6">
@@ -19476,16 +19476,16 @@
       <c r="I394" t="s" s="0">
         <v>1221</v>
       </c>
-      <c r="J394" t="s">
+      <c r="J394" t="s" s="0">
         <v>1437</v>
       </c>
-      <c r="K394" t="s">
-        <v>243</v>
-      </c>
-      <c r="L394">
-        <v>0</v>
-      </c>
-      <c r="M394">
+      <c r="K394" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="L394" s="0">
+        <v>0</v>
+      </c>
+      <c r="M394" s="0">
         <v>6</v>
       </c>
       <c r="N394" s="6">

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6889" uniqueCount="1439">
   <si>
     <t>Nombre</t>
   </si>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6889" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7126" uniqueCount="1439">
   <si>
     <t>Nombre</t>
   </si>

--- a/resources/SistemasBasura.xlsx
+++ b/resources/SistemasBasura.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6889" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9259" uniqueCount="1439">
   <si>
     <t>Nombre</t>
   </si>
